--- a/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A263"/>
+  <dimension ref="A1:A238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,14 +466,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/sanjay-raut-afflicted-with-political-jaundice-i-know-the-right-medicine-chandrakant-patil-3588266</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-slams-mismanagement-by-institutes-urges-fee-reforms-for-girls-education-101747081287274.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/chandrakant-patil-urges-pmc-to-build-sudhir-phadke-memorial-in-kothrud-101753209522556.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/sanjay-raut-afflicted-with-political-jaundice-i-know-the-right-medicine-chandrakant-patil-3588266</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-slams-mismanagement-by-institutes-urges-fee-reforms-for-girls-education-101747081287274.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/chandrakant-patil-urges-pmc-to-build-sudhir-phadke-memorial-in-kothrud-101753209522556.html</t>
         </is>
       </c>
     </row>
@@ -543,21 +543,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/vishal-patil-turns-down-bjp-ministers-offer-to-join-alliance/articleshow/119084771.cms</t>
+          <t>https://indianexpress.com/article/political-pulse/mva-sanjay-raut-bjp-sena-ubt-9808199/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/100-per-cent-fee-waiver-for-ews-girls-chandrakant-patil-101750360390574.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/vishal-patil-turns-down-bjp-ministers-offer-to-join-alliance/articleshow/119084771.cms</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-of-different-backgrounds-are-bound-to-disagree-in-coalition-govt-chandrakant-patil-23519840</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/100-per-cent-fee-waiver-for-ews-girls-chandrakant-patil-101750360390574.html</t>
         </is>
       </c>
     </row>
@@ -585,63 +585,63 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/schools-in-sangli-district-free-of-tobacco-says-chandrakant-patil/articleshow/120074515.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/rss-holds-two-day-brainstorming-session-with-bjp-allied-outfits-3362607</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/rss-holds-two-day-brainstorming-session-with-bjp-allied-outfits-3362607</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
+          <t>https://www.deccanherald.com/india/dh-evening-brief-bsf-jawan-returns-from-pak-custody-fir-ordered-against-mp-minister-for-remarks-against-col-sofia-qureshi-3540442</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/dh-evening-brief-bsf-jawan-returns-from-pak-custody-fir-ordered-against-mp-minister-for-remarks-against-col-sofia-qureshi-3540442</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/states-tech-edu-minister-reviews-fee-waiver-for-women-students/articleshow/118310028.cms</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/states-tech-edu-minister-reviews-fee-waiver-for-women-students/articleshow/118310028.cms</t>
+          <t>https://thelivenagpur.com/2025/07/27/retirement-age-of-college-principals-raised-to-65-announces-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/07/27/retirement-age-of-college-principals-raised-to-65-announces-minister-chandrakant-patil/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/dpdc-meeting-on-thursday-101738176153028.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/dpdc-meeting-on-thursday-101738176153028.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/sub-centre-of-sppu-slated-to-be-inaugurated-by-may-end-in-nashiks-shivnai-area-chandrakant-patil-instructs-officials-to-expedite-facility/articleshow/121036464.cms</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/sub-centre-of-sppu-slated-to-be-inaugurated-by-may-end-in-nashiks-shivnai-area-chandrakant-patil-instructs-officials-to-expedite-facility/articleshow/121036464.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-asks-pmc-to-acquire-land-on-priority-as-balewadi-wakad-bridge-lies-unused-101751741109744.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-asks-pmc-to-acquire-land-on-priority-as-balewadi-wakad-bridge-lies-unused-101751741109744.html</t>
+          <t>https://punemirror.com/pune-mirror-explore/pune-news-chandrakant-patil-issues-ultimatum-to-pune-municipal-corporation-over-solid-waste-management-project/</t>
         </is>
       </c>
     </row>
@@ -662,84 +662,84 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/wonder-if-some-forces-are-working-to-destabilise-maharashtra:-minister-amid-shaktipeeth-stir/2826353</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-silent-on-bavdhan-garbage-plant-issue-in-pmc-meeting-101745953467654.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-silent-on-bavdhan-garbage-plant-issue-in-pmc-meeting-101745953467654.html</t>
+          <t>https://www.ptinews.com/story/national/maharashtra:-cabinet-sub-committee-on-maratha-quota-reconstituted;-vikhe-patil-new-head/2847184</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra:-cabinet-sub-committee-on-maratha-quota-reconstituted;-vikhe-patil-new-head/2847184</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-adds-fourth-cap-round-for-engineering-admissions-to-curb-costly-pvt-options-101749150825079.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-adds-fourth-cap-round-for-engineering-admissions-to-curb-costly-pvt-options-101749150825079.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-may-halt-admissions-to-pharmacy-colleges-flouting-norms-101753902851567.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-may-halt-admissions-to-pharmacy-colleges-flouting-norms-101753902851567.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ahead-of-jarange-stir-in-mumbai-cabinet-sub-committee-on-maratha-quota-reconstituted-vikhe-patil-now-new-head/articleshow/123460725.cms</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ahead-of-jarange-stir-in-mumbai-cabinet-sub-committee-on-maratha-quota-reconstituted-vikhe-patil-now-new-head/articleshow/123460725.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/pune-civic-body-acts-against-unauthorised-stalls-on-fc-road-101749148183563.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/pune-civic-body-acts-against-unauthorised-stalls-on-fc-road-101749148183563.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-to-restart-withdrawn-services-by-tanker-association-with-police-help-101744571005989.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-to-restart-withdrawn-services-by-tanker-association-with-police-help-101744571005989.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-government-plans-to-grant-university-status-to-jbims-101743881532444.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-government-plans-to-grant-university-status-to-jbims-101743881532444.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/islampur-to-be-renamed-ishwarpur-101752864742122.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/islampur-to-be-renamed-ishwarpur-101752864742122.html</t>
+          <t>https://thelivenagpur.com/2025/06/06/maharashtra-introduces-new-rule-stops-cet-exams-at-centres-outside-the-state/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/22/bes35-mh-maratha-committee.html</t>
+          <t>https://www.ptinews.com/story/national/c-r-patil-takes-charge-as-jal-shakti-minister/1575205</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/06/06/maharashtra-introduces-new-rule-stops-cet-exams-at-centres-outside-the-state/</t>
+          <t>https://punemirror.com/city/civic/chandrakant-patil-takes-action-on-kothrud-s-road-water-and-traffic-issues/</t>
         </is>
       </c>
     </row>
@@ -753,35 +753,35 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2126625</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/police-bust-chain-snatching-gang-two-held-minor-detained-101740078106456.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/cet-for-courses-in-maharashtra-not-be-held-outside-state-prevent-malpractices-minister-chandrakant-patil</t>
+          <t>https://punemirror.com/education/maharashtra-unveils-ambitious-higher-education-reforms/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://indiatechnologynews.in/maharashtra-state-cet-cell-launches-visionary-initiative-cet-atal-module-for-mock-tests/</t>
+          <t>https://zeenews.india.com/india/maharashtra-politics-did-bjp-minister-just-confirm-rift-within-mahayuti-shindes-meeting-with-shah-2886410.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-fee-hike-all-engineering-medical-professional-colleges-fra-charge-3x-fees-for-management-5x-nri-quota-seats</t>
+          <t>https://punemirror.com/city/civic/baner-balewadi-traffic-woes-get-high-level-attention-at-key-pmc-meeting/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/gallery/17-01-2025-governor-presides-61st-annual-convocation-of-shivaji-university/</t>
+          <t>https://news.careers360.com/maharashtra-fee-hike-all-engineering-medical-professional-colleges-fra-charge-3x-fees-for-management-5x-nri-quota-seats</t>
         </is>
       </c>
     </row>
@@ -802,70 +802,70 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-news-chandrakant-patil-urges-citizens-to-stay-vigilant/</t>
+          <t>https://www.mypunepulse.com/pune-major-announcement-for-girls-education-minister-chandrakant-patil-to-inspect-100-colleges-review-fee-waiver-implementation/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-major-announcement-for-girls-education-minister-chandrakant-patil-to-inspect-100-colleges-review-fee-waiver-implementation/</t>
+          <t>https://www.mypunepulse.com/chandrakant-patil-reveals-details-of-vidhan-bhavan-meetings-on-pune-municipal-corporation-budget/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/chandrakant-patil-reveals-details-of-vidhan-bhavan-meetings-on-pune-municipal-corporation-budget/</t>
+          <t>https://www.mypunepulse.com/traffic-congestion-free-kothrud-minister-chandrakant-patil-pushes-for-ai-based-challan-system/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/traffic-congestion-free-kothrud-minister-chandrakant-patil-pushes-for-ai-based-challan-system/</t>
+          <t>https://www.mypunepulse.com/ensure-safety-measures-for-pune-hills-higher-and-technical-education-minister-chandrakant-patils-directives/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-chandrakant-patil-demands-swift-action-on-citys-missing-road-link-projects/</t>
+          <t>https://www.mypunepulse.com/pune-chandrakant-patil-warns-pmc-shut-down-sus-waste-project-or-face-protest/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/global-ganesh-festival-2025-eknath-shinde-to-lead-chandrakant-patil-as-chief-receptionist/</t>
+          <t>https://www.mypunepulse.com/pune-chandrakant-patil-demands-swift-action-on-citys-missing-road-link-projects/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/chandrakant-patil-proposes-safety-measures-to-prevent-fires-on-punes-17-hills/</t>
+          <t>https://www.punekarnews.in/global-ganesh-festival-2025-eknath-shinde-to-lead-chandrakant-patil-as-chief-receptionist/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/minister-chandrakant-patil-orders-comprehensive-report-on-challenges-faced-by-educational-institutions-in-maharashtra/</t>
+          <t>https://www.punekarnews.in/chandrakant-patil-proposes-safety-measures-to-prevent-fires-on-punes-17-hills/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-chandrakant-patil-orders-immediate-measures-to-resolve-baner-balewadi-traffic-woes/</t>
+          <t>https://www.punekarnews.in/minister-chandrakant-patil-orders-comprehensive-report-on-challenges-faced-by-educational-institutions-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-chandrakant-patil-intensifies-efforts-for-girls-fee-waiver-plans-surprise-visits-to-100-colleges/</t>
+          <t>https://www.mypunepulse.com/pune-chandrakant-patil-orders-immediate-measures-to-resolve-baner-balewadi-traffic-woes/</t>
         </is>
       </c>
     </row>
@@ -907,28 +907,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/society-is-responsible-for-keeping-every-person-alive-cm-devendra-fadnavis-at-guinness-world-record-event-in-pune/</t>
+          <t>https://affairscloud.com/union-minister-of-jal-shakti-cr-patil-reviewed-key-projects-of-wii-under-nmcg/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/ahead-of-mumbai-protest-maharashtra-minister-asks-jarange-to-hold-talks-with-govt-9725948</t>
+          <t>https://www.mypunepulse.com/maharashtra-govt-unveils-new-grading-system-to-modernise-public-libraries/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/maharashtra-govt-unveils-new-grading-system-to-modernise-public-libraries/</t>
+          <t>https://www.mypunepulse.com/cet-exams-to-be-held-only-within-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/cet-exams-to-be-held-only-within-maharashtra/</t>
+          <t>https://www.punekarnews.in/society-is-responsible-for-keeping-every-person-alive-cm-devendra-fadnavis-at-guinness-world-record-event-in-pune/</t>
         </is>
       </c>
     </row>
@@ -956,21 +956,21 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-defence-minister-rajnath-singh-likely-to-inaugurate-peshwa-memorial-at-parvati-hill/</t>
+          <t>https://www.hindustanmetro.com/mr-sunjjoy-chaudhri-leads-team-veer-santaji-at-khasdar-celebrity-cricket-league-2025-celebrating-punes-grand-festival-with-support-from-mr-murlidhar-mohol-and-mr-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-minister-orders-compulsory-land-acquisition-to-open-balewadi-wakad-mula-river-bridge/</t>
+          <t>https://www.mypunepulse.com/pune-defence-minister-rajnath-singh-likely-to-inaugurate-peshwa-memorial-at-parvati-hill/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.hindustanmetro.com/maharashtra-state-cet-cell-launches-visionary-initiative-cet-atal-module-for-mock-tests/</t>
+          <t>https://www.punekarnews.in/pune-minister-orders-compulsory-land-acquisition-to-open-balewadi-wakad-mula-river-bridge/</t>
         </is>
       </c>
     </row>
@@ -984,1288 +984,1113 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/minister-chandrakant-patil-offers-to-join-bjp-to-independent-mp-vishal-patil-after-get-offer-vishal-patil-said-if-i-am-getting-an-offer-of-joining-party-i-think-i-am-doing-a-good-job-1349507</t>
+          <t>https://mahasamvad.in/171311/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171311/</t>
+          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-milind-narvekar-and-chandrakant-patil-meet-at-parag-alavani-daughter-wedding-and-discussion-on-yuti-impact-on-maharashtra-politics-1341419</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/chandrakant-patil-criticizes-on-uddhav-thackeray-said-raj-thackeray-is-political-convenience-for-mumbai-municipal-corporation-maharashtra-politics-marathi-news-1368293</t>
+          <t>https://www.loksatta.com/maharashtra/bjp-chandrakant-patil-reaction-on-dhananjay-munde-ministerial-post-says-cm-will-take-decision-on-resignation-kvg-85-4850775/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-milind-narvekar-and-chandrakant-patil-meet-at-parag-alavani-daughter-wedding-and-discussion-on-yuti-impact-on-maharashtra-politics-1341419</t>
+          <t>https://marathi.abplive.com/news/minister-chandrakant-patil-suggestion-after-pratibimb-foundation-take-a-big-step-for-the-career-of-journalists-sons-and-daughters-along-with-health-of-their-families-maharashtra-marathi-news-1355102</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/jalgaon-chandrakant-patil-shiv-sena-on-raksha-khadse-daughter-devendra-fadanvis-marathi-news-abp-majha-1347066</t>
+          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-statement-on-jayant-patil-ncp-sharad-pawar-leader-sangli-politics-marathi-news-1371392</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/minister-chandrakant-patil-suggestion-after-pratibimb-foundation-take-a-big-step-for-the-career-of-journalists-sons-and-daughters-along-with-health-of-their-families-maharashtra-marathi-news-1355102</t>
+          <t>https://mahasamvad.in/176328/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-uday-samant-on-manoj-jarange-patil-over-mumbai-morcha-for-maratha-reservation-marathi-news-1379258</t>
+          <t>https://mahasamvad.in/173280/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170695/</t>
+          <t>https://mahasamvad.in/173478/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/will-ajit-pawar-chandrakant-patil-jayant-patil-rohit-pawar-come-on-the-same-platform-in-sangli-for-saroj-patil-function-1377194</t>
+          <t>https://mahasamvad.in/172941/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-statement-on-jayant-patil-ncp-sharad-pawar-leader-sangli-politics-marathi-news-1371392</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-have-137-mlas-black-magic-will-do-nothing-maharashtra-government-will-run-for-5-years-says-chandrakant-patil-at-kolhapur-1344696</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176328/</t>
+          <t>https://mahasamvad.in/174837/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173280/</t>
+          <t>https://mahasamvad.in/175996/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173478/</t>
+          <t>https://mahasamvad.in/163743/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172941/</t>
+          <t>https://marathi.abplive.com/news/politics/eknath-khadse-vs-chandrakant-patil-how-did-34-acres-of-land-become-100-acres-eknath-khadse-response-to-chandrakant-patil-allegations-jalgaon-maharashtra-politics-marathi-news-1362993</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/extension-of-the-deadline-for-admission-registration-conducted-by-cet-cell-information-from-minister-chandrakant-patil-1368834</t>
+          <t>https://mahasamvad.in/175756/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-have-137-mlas-black-magic-will-do-nothing-maharashtra-government-will-run-for-5-years-says-chandrakant-patil-at-kolhapur-1344696</t>
+          <t>https://mahasamvad.in/176831/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174837/</t>
+          <t>https://mahasamvad.in/176833/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175996/</t>
+          <t>https://mahasamvad.in/169332/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163743/</t>
+          <t>https://mahasamvad.in/176819/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/eknath-khadse-vs-chandrakant-patil-how-did-34-acres-of-land-become-100-acres-eknath-khadse-response-to-chandrakant-patil-allegations-jalgaon-maharashtra-politics-marathi-news-1362993</t>
+          <t>https://marathi.abplive.com/education/college-admission-for-engineers-from-june-28-extension-for-diploma-till-june-30-minister-chandrakant-patil-decision-1366417</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175756/</t>
+          <t>https://www.loksatta.com/maharashtra/minister-chandrakant-patil-appeal-over-tomb-of-tiger-dog-controversy-zws-70-4983085/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176831/</t>
+          <t>https://mahasamvad.in/175217/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176833/</t>
+          <t>https://mahasamvad.in/176754/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169332/</t>
+          <t>https://mahasamvad.in/173059/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sanjay-raut-reaction-on-chandrakant-patil-statement-of-shivsena-bjp-alliance-will-be-golden-moment-sgk-96-4858543/</t>
+          <t>https://marathi.ndtv.com/maharashtra/pune-news-chandrakant-patil-slams-raj-thackeray-uddhav-thackeray-on-hindi-language-controvery-8785417</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176754/</t>
+          <t>https://mahasamvad.in/163261/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176819/</t>
+          <t>https://mahasamvad.in/169326/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/education/college-admission-for-engineers-from-june-28-extension-for-diploma-till-june-30-minister-chandrakant-patil-decision-1366417</t>
+          <t>https://www.mahasamvad.in/169422/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163261/</t>
+          <t>https://mahasamvad.in/161166/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175942/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/minister-chandrakant-patil-new-responsibility-of-professors-for-students-instructions-for-effective-implementation-of-college-schemes/articleshow/121717827.cms</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175217/</t>
+          <t>https://mahasamvad.in/174729/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/why-does-bjp-still-like-other-people-children-raju-shetti-scathing-criticism-of-chandrakant-patil-offer-to-vishal-patil-1349730</t>
+          <t>https://mahasamvad.in/160626/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-says-there-will-soon-be-1000-police-personnel-in-the-pune-police-force-pune-print-news-amy-95-5209449/</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-leader-chandrkant-patil-on-dhananjay-munde-resignation-and-walmik-karad-connection-on-beed-massajog-santosh-deshmukh-case-1340832</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173059/</t>
+          <t>https://www.tv9marathi.com/videos/bjp-leader-minister-chandrakant-patil-big-statement-regarding-ministerial-post-at-sangli-1390006.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/pune-news-chandrakant-patil-slams-raj-thackeray-uddhav-thackeray-on-hindi-language-controvery-8785417</t>
+          <t>https://www.loksatta.com/pune/do-not-bow-to-politicians-says-education-minister-urges-teachers-to-uphold-dignity-of-profession-pune-print-news-ccp-14-ocd-94-5253062/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169326/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/minister-chandrakant-patil-and-farmers-dispute-broke-out-between-in-sangli/articleshow/120792863.cms</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/169422/</t>
+          <t>https://mahasamvad.in/173128/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161166/</t>
+          <t>https://www.msn.com/mr-in/news/other/sangli-news-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%8F%E0%A4%95-%E0%A4%9A-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%AA-%E0%A4%A0-%E0%A4%B5%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A4%97-%E0%A4%A8-%E0%A4%AE-%E0%A4%88-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A0%E0%A4%B0%E0%A4%A3-%E0%A4%B0/ar-AA1KyMam</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-statement-after-ravindra-dhangekar-entry-into-shinde-group-svk-88-amy-95-4945089/</t>
+          <t>https://mahasamvad.in/172372/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/minister-chandrakant-patil-new-responsibility-of-professors-for-students-instructions-for-effective-implementation-of-college-schemes/articleshow/121717827.cms</t>
+          <t>https://mahasamvad.in/176760/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174729/</t>
+          <t>https://mahasamvad.in/164366/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/in-pune-chandrakant-patil-inaugurated-free-medical-aid-through-mobile-clinic-for-warkaris-pune-print-news-tss-19-asj-82-5169425/</t>
+          <t>https://mahasamvad.in/170382/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160626/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-on-rohini-khadse-jalgaon-news-mla-chandrakant-patil-criticizes-rohini-khadse-1379392</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ahilyadevi-holkar-jayanti-2025-bjp-chandrakant-patil-in-solapur-css-98-5126268/</t>
+          <t>https://mahasamvad.in/162964/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-leader-chandrkant-patil-on-dhananjay-munde-resignation-and-walmik-karad-connection-on-beed-massajog-santosh-deshmukh-case-1340832</t>
+          <t>https://mahasamvad.in/154565/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-leader-minister-chandrakant-patil-big-statement-regarding-ministerial-post-at-sangli-1390006.html</t>
+          <t>https://www.msn.com/mr-in/news/other/eps-employees-pension-%E0%A4%88%E0%A4%AA-%E0%A4%8F%E0%A4%B8-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A4%9A-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A8-%E0%A4%B5%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%B5%E0%A5%87%E0%A4%A4%E0%A4%A8-%E0%A4%AE-%E0%A4%B3%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%A0-%E0%A4%AA-%E0%A4%A0%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%B5-%E0%A4%95%E0%A4%B0%E0%A5%82-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2/ar-AA1La4cI</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/minister-chandrakant-patil-and-farmers-dispute-broke-out-between-in-sangli/articleshow/120792863.cms</t>
+          <t>https://mahasamvad.in/161614/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173128/</t>
+          <t>https://mahasamvad.in/158873/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/sangli-news-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%8F%E0%A4%95-%E0%A4%9A-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%AA-%E0%A4%A0-%E0%A4%B5%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A4%97-%E0%A4%A8-%E0%A4%AE-%E0%A4%88-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A0%E0%A4%B0%E0%A4%A3-%E0%A4%B0/ar-AA1KyMam</t>
+          <t>https://mahasamvad.in/173469/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172372/</t>
+          <t>https://mahasamvad.in/157924/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176760/</t>
+          <t>https://www.mymahanagar.com/maharashtra/chandrkant-patil-will-the-farmers-affected-by-shaktipeeth-get-compensation-what-did-chandrakant-patil-say/912426/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/164366/</t>
+          <t>https://deshdoot.com/recruitment-of-4435-posts-of-assistant-professors-soon-information-from-higher-and-technical-education-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-on-rohini-khadse-jalgaon-news-mla-chandrakant-patil-criticizes-rohini-khadse-1379392</t>
+          <t>https://mahasamvad.in/174461/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-admits-errorsin-mht-cet-math-paper-takes-disciplinary-action-pune-print-news-ccp-14-rds-00-5198879/</t>
+          <t>https://marathi.ndtv.com/maharashtra/ndtv-marathi-emerging-business-conclave-chandrakant-patil-rupali-chakankar-on-pune-traffic-rain-issue-8786115</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170382/</t>
+          <t>https://mahasamvad.in/175300/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/162964/</t>
+          <t>https://mahasamvad.in/162538/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/eps-employees-pension-%E0%A4%88%E0%A4%AA-%E0%A4%8F%E0%A4%B8-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A4%9A-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A8-%E0%A4%B5%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%B5%E0%A5%87%E0%A4%A4%E0%A4%A8-%E0%A4%AE-%E0%A4%B3%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%A0-%E0%A4%AA-%E0%A4%A0%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%B5-%E0%A4%95%E0%A4%B0%E0%A5%82-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2/ar-AA1La4cI</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-bharti-new-procedure-announced-for-selection-process-minister-chandrakant-patil/articleshow/118607489.cms</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161614/</t>
+          <t>https://mahasamvad.in/160732/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158873/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-recruitment-2025-college-teachers-bharti-education-minister-chandrakant-patil/articleshow/118924405.cms</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173469/</t>
+          <t>https://mahasamvad.in/173736/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157924/</t>
+          <t>https://mahasamvad.in/169668/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/education/polytechnic-admission-start-from-20-may-and-visit-the-website-for-online-process-chandrakant-patil-appeals-1359951</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/jayshree-patil-to-join-bjp-presence-chief-minister-devendra-fadnavis/articleshow/121881414.cms</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/chandrkant-patil-will-the-farmers-affected-by-shaktipeeth-get-compensation-what-did-chandrakant-patil-say/912426/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/medha-kulkarni-left-bjp-meeting-midway-as-chandrakant-patil-murlidhar-mohol-backs-deenanath-mangeshkar-case-andolan/articleshow/120120230.cms</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/chandrakant-patil-slams-uddhav-thackeray-1439709.html</t>
+          <t>https://mahasamvad.in/153348/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174461/</t>
+          <t>https://mahasamvad.in/163883/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-on-shaktipeeth-expressway-nagpur-goa-highway-claim-some-forces-working-to-disturb-maharashtra-marathi-1377295</t>
+          <t>https://marathi.abplive.com/education/chandrakant-patil-announced-ews-certificate-accepted-for-one-year-economically-weaker-section-student-maharashtra-education-marathi-news-1340514</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/ndtv-marathi-emerging-business-conclave-chandrakant-patil-rupali-chakankar-on-pune-traffic-rain-issue-8786115</t>
+          <t>https://marathi.indiatimes.com/career/career-news/girl-free-education-scheme-in-maharashtra-latest-news-chandrakant-patil-mulina-mofat-shikshan-yojana-maharashtra-2024/articleshow/118265312.cms</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175300/</t>
+          <t>https://www.tarunbharat.com/chandrakant-atial-discussion-with-flood-situated-people-sangli-walwa-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/162538/</t>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5018629/chandrakant-patil-criticized-sanjay-raut-over-maharashtra-politics/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/chandrakant-patil-instructions-to-professors-on-scholarship-implementation-in-colleges-8612913</t>
+          <t>https://news18marathi.com/maharashtra/mahayuti-leaders-ajit-pawar-chandrakant-patil-and-shrikant-shinde-on-mission-sangli-for-damage-maha-vikas-aghadi-1386892.html</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/mht-cet-2025-exam-21-incorrect-questions-in-math-exam-paper-minister-chandrakant-patils-admission/articleshow/122223140.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ajit-pawar-devendra-fadnavis-shares-fun-moment-at-pune-lokmanya-tilak-award-ceremony-with-chandrakant-patil-eknath-shinde/articleshow/123054887.cms</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/minister-chandrakant-patil-announces-teaching-course-on-p-l-deshpande-at-pune-university-pune-print-news-ocd-94-5146646/</t>
+          <t>https://marathi.abplive.com/news/pune/medha-kulkarni-left-the-meeting-chandrakant-patil-murlidhar-mohol-supported-the-deenanath-mangeshkar-case-andolan-tanisha-bhise-death-case-what-exactly-happened-during-the-meeting-1353526</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-bharti-new-procedure-announced-for-selection-process-minister-chandrakant-patil/articleshow/118607489.cms</t>
+          <t>https://agrowon.esakal.com/agro-special/guardian-minister-orders-crop-damage-survey-in-flood-hit-areas-mj18</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169297/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/girls-free-education-in-maharashtra-special-scheme-for-other-fees-assurance-from-chandrakant-patil/articleshow/123376903.cms</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-recruitment-2025-college-teachers-bharti-education-minister-chandrakant-patil/articleshow/118924405.cms</t>
+          <t>https://civicmirror.in/news/action-against-b-ed-colleges-as-per-the-rules-of-the-national-council-for-teacher-education-higher-and-technical/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173736/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-mns-raj-thackeray-uddhav-thackeray-alliance-eknath-shinde-politics-news-in-marathi-aajchya-thalak-batmya-monday-21-april-2025-1388817.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/jayshree-patil-to-join-bjp-presence-chief-minister-devendra-fadnavis/articleshow/121881414.cms</t>
+          <t>https://mahasamvad.in/171768/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169668/</t>
+          <t>https://www.eduvarta.com/Minister-Chandrakant-Patils-instructions-to-conduct-CET-again-for-BBA-BCA</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/medha-kulkarni-left-bjp-meeting-midway-as-chandrakant-patil-murlidhar-mohol-backs-deenanath-mangeshkar-case-andolan/articleshow/120120230.cms</t>
+          <t>https://civicmirror.in/news/bamu-s-big-decision-admissions-to-113-colleges-including-educational-institutions-of-chandrakant-patil-sule-munde/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/solapur/solapur-jayakumar-gore-news-guardian-minister-jayakumar-gore-reaction-to-mla-ranjitsinh-mohite-patil-in-solapur-1361873</t>
+          <t>https://civicmirror.in/news/chandrakant-patil-on-sanjaykaka-patil-and-ones-again-offer-to-vishal-patil-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/ahmednagar/chaundi-ahilyanagar-cabinet-meeting-cancled-31-may-on-ahilyabai-holkar-300th-jayanti-maharashtra-marathi-news-1356056</t>
+          <t>https://policenama.com/chandrakant-patil-sant-puja-and-distribution-of-useful-materials-to-warkari-brothers-on-the-occasion-of-ashadhi-wari/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/153348/</t>
+          <t>https://policenama.com/chandrakant-patil-no-matter-how-much-black-magic-someone-does-it-doesnt-matter-bjp-has-as-many-as-137-mlas-who-is-chandrakant-patal-targeting-so-the-indication-of-bawankules-to-fight-the-upco/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/mp-vishal-patil-sanjay-patil-and-prithviraj-patil-on-the-same-platform-in-sangli-marathi-news-udpate-1377401</t>
+          <t>https://maharashtradesha.com/uddhav-thackerays-party-wants-to-join-the-government-chandrakant-patil-said/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/sangli-district-central-cooperative-bank-vice-president-jayashree-patil-will-join-the-bjp-marathi-news-update-1364524</t>
+          <t>https://civicmirror.in/news/sangli-or-review-the-arms-licenses-in-the-district-to-control-criminal-incidents-guardian-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/education/chandrakant-patil-announced-ews-certificate-accepted-for-one-year-economically-weaker-section-student-maharashtra-education-marathi-news-1340514</t>
+          <t>https://civicmirror.in/news/polytechnic-admissions-2025-or-extension-of-deadline-for-submission-of-applications-for-polytechnic-courses-instructions/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-crime-rave-party-chandrakant-patil-criticizes-rohini-khadse-as-soon-as-her-husband-pranjal-khewalkar-is-arrested-maharashtra-marathi-news-1372935</t>
+          <t>https://civicmirror.in/news/pune-or-heartbroken-to-hear-the-truth-about-the-attack-chandrakant-patil-consoles-ganbote-jagdale-families/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ajit-pawar-funny-comment-on-jayant-patil-in-front-of-rohit-pawar-and-chandrakant-patil-sangli-maharashtra-politics-marathi-news-1377436</t>
+          <t>https://policenama.com/bajirao-peshwa-memorials-on-parvati-hill-development-work-of-bajirao-peshwa-memorial-on-parvati-hill-satisfactory-the-first-phase-will-be-inaugurated-by-union-minister-rajnath-singh-chandrakant-p/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/girl-free-education-scheme-in-maharashtra-latest-news-chandrakant-patil-mulina-mofat-shikshan-yojana-maharashtra-2024/articleshow/118265312.cms</t>
+          <t>https://news24pune.com/congress-suffers-setback-in-sangli-vasantdada-patils-granddaughter-jayashree-patil-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/chandrakant-atial-discussion-with-flood-situated-people-sangli-walwa-marathi-news/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/firata-davakhana-for-warkari-state-minister-chandrakant-patil-inaugurated-in-pune-article-152110556</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/mahayuti-leaders-ajit-pawar-chandrakant-patil-and-shrikant-shinde-on-mission-sangli-for-damage-maha-vikas-aghadi-1386892.html</t>
+          <t>https://www.athawadavishesh.com/34215/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/former-corporator-manoj-sargar-who-played-a-role-in-getting-vishal-patil-elected-is-joining-the-bharatiya-janata-party-on-monday-1375918</t>
+          <t>https://www.marathiebatmya.com/political/ajit-pawar-said-will-see-rohit-pawar-at-home/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/cold-war-between-bjp-leaders-chandrakant-patil-murlidhar-mohol-and-medha-kulkarni-in-pune-on-rise-print-politics-news-mrj-95-5012957/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/big-recruitment-in-the-higher-education-department-of-maharashtra-5500-professors-and-2900-employees-will-be-recruited-article-152339600</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ajit-pawar-devendra-fadnavis-shares-fun-moment-at-pune-lokmanya-tilak-award-ceremony-with-chandrakant-patil-eknath-shinde/articleshow/123054887.cms</t>
+          <t>https://www.dainikprabhat.com/satara-news-disability-certificates-of-17-more-teachers-are-invalid/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/medha-kulkarni-left-the-meeting-chandrakant-patil-murlidhar-mohol-supported-the-deenanath-mangeshkar-case-andolan-tanisha-bhise-death-case-what-exactly-happened-during-the-meeting-1353526</t>
+          <t>https://www.hindustantimes.com/trending/saw-smoke-in-the-eyewitness-at-ahmedabad-airport-describes-air-india-crash-101749727540094.html</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/guardian-minister-orders-crop-damage-survey-in-flood-hit-areas-mj18</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-conduct-second-cet-colleges-worried-about-delay-in-academic-year-101749409146794.html</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/sangli-crime-news-seven-month-pregnant-woman-self-killed-after-alleged-being-tortured-by-in-laws-for-religious-conversion-3-arrested-maharashtra-news-mhs25061200648</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-parties-battling-each-other-during-poaching-spree-101751053618819.html</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/girls-free-education-in-maharashtra-special-scheme-for-other-fees-assurance-from-chandrakant-patil/articleshow/123376903.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/powerloom-body-appeals-to-shun-trade-with-turkiye-azerbaijan/articleshow/121218402.cms</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/congress-mp-vishal-patil-entry-to-bjp-offers-sangli-news-amy-95-4953086/</t>
+          <t>https://www.msn.com/mr-in/news/other/chandrakant-patil-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%95-%E0%A4%97%E0%A4%A6-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%AA%E0%A5%87%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B2-%E0%A4%AC%E0%A4%B8-%E0%A4%B5%E0%A4%82-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%B5-%E0%A4%B9%E0%A4%A8/ar-AA1L414d</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-guardian-minister-chandrakant-patil-oath-against-drugs-school-students-css-98-4912323/</t>
+          <t>https://marathi.ndtv.com/maharashtra/chandrakant-patil-instructions-to-professors-on-scholarship-implementation-in-colleges-8612913</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171768/</t>
+          <t>https://mahasamvad.in/176171/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/gopichand-padalkar-embezzled-34-acres-of-land-of-oundh-devasthan-ram-khade-makes-serious-allegations-by-showing-documents-1350057</t>
+          <t>https://marathi.abplive.com/news/solapur/solapur-jayakumar-gore-news-guardian-minister-jayakumar-gore-reaction-to-mla-ranjitsinh-mohite-patil-in-solapur-1361873</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/indias-first-artificial-intelligence-university-in-maharashtra-order-for-constitution-of-committee-chandrakant-patil/articleshow/117637901.cms</t>
+          <t>https://www.newsonair.gov.in/mr/education-free-for-female-students/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/editor-letters/ajit-pawar-criticizes-chandrakant-patil-125081700011_1.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-double-voting-allegations-chandrakant-patil-accuses-rohini-khadse-of-voting-twice-in-kothali-and-muktainagar-sparks-maharashtra-political-row-1379422</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/police-bust-chain-snatching-gang-two-held-minor-detained-101740078106456.html</t>
+          <t>https://marathi.indiatimes.com/career/career-news/indias-first-artificial-intelligence-university-in-maharashtra-order-for-constitution-of-committee-chandrakant-patil/articleshow/117637901.cms</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/maharashtra-abu-azmi-writes-letter-to-speaker-rahul-narwekar-to-revoke-his-suspension-over-statement-on-aurangzeb-latest-updates-2025-03-07-979620</t>
+          <t>https://www.mymahanagar.com/maharashtra/ravindra-dhangekar-allegation-chandrakant-patil-and-murlidhar-mohol-politics-for-gajanan-marne-arrested/854647/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/maharashtra-politics-did-bjp-minister-just-confirm-rift-within-mahayuti-shindes-meeting-with-shah-2886410.html</t>
+          <t>https://marathi.abplive.com/news/politics/gopichand-padalkar-embezzled-34-acres-of-land-of-oundh-devasthan-ram-khade-makes-serious-allegations-by-showing-documents-1350057</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176171/</t>
+          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-backs-abgi-vision-for-deemed-university-status-rds-00-5268767/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/politics-chandrakant-patil-sanjay-raut-bjp-uddhav-thackeray-narendra-modi-marathi-news-abp-majha-1364424</t>
+          <t>https://policenama.com/chandrakant-patil-news-spontaneous-response-to-the-grain-festival-organized-by-minister-chandrakantdada-patil/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-politics-ajit-pawar-jayant-patil-rohit-pawar-clash-1471655.html</t>
+          <t>https://policenama.com/chandrakant-patil-philosophy-of-thinking-positively-about-others-in-hindu-culture-chandrakantdada-patils-assertion/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/chandrakant-patil-ajit-pawar-on-born-with-golden-spoon/933026</t>
+          <t>https://politicalmaharashtra.in/more-than-1101-couples-perform-collective-rudra-puja-in-pune-97635/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ravindra-dhangekar-allegation-chandrakant-patil-and-murlidhar-mohol-politics-for-gajanan-marne-arrested/854647/</t>
+          <t>https://www.indiatvnews.com/maharashtra/maharashtra-abu-azmi-writes-letter-to-speaker-rahul-narwekar-to-revoke-his-suspension-over-statement-on-aurangzeb-latest-updates-2025-03-07-979620</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.eduvarta.com/Minister-Chandrakant-Patils-instructions-to-conduct-CET-again-for-BBA-BCA</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-11-political-news-in-marathi-931306</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/uddhav-thackeray-and-bjp-leader-chandrakant-patil-meeting-at-a-wedding-article-117713206</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-july-pune-rave-party-raj-thackeray-uddhav-thackeray-latest-news-mumbai-konkan-marathwada-weather-report-today-rain-updates-kolhapur-pandharpur-pmw-88-5267001/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-sant-puja-and-distribution-of-useful-materials-to-warkari-brothers-on-the-occasion-of-ashadhi-wari/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-state-government-halts-new-pharmacy-colleges-understand-the-reasons-behind-decreased-demand/articleshow/120842410.cms</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/chandrakant-patil-on-sanjaykaka-patil-and-ones-again-offer-to-vishal-patil-join-bjp/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-breaking-news-live-in-marathi-1-may-2025-maharashtra-din-kamgar-divas-pahalgam-attack-update-pm-modi-cm-devendra-fadnavis-mumbai-pune-latest-updates/liveblog/120781856.cms</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/bamu-s-big-decision-admissions-to-113-colleges-including-educational-institutions-of-chandrakant-patil-sule-munde/</t>
+          <t>https://mahasamvad.in/158932/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-no-matter-how-much-black-magic-someone-does-it-doesnt-matter-bjp-has-as-many-as-137-mlas-who-is-chandrakant-patal-targeting-so-the-indication-of-bawankules-to-fight-the-upco/</t>
+          <t>https://www.etvbharat.com/mr/!state/kesari-father-in-law-has-been-lost-kesaribhau-patil-passes-away-maharashtra-news-mhs25021502516</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-news-spontaneous-response-to-the-grain-festival-organized-by-minister-chandrakantdada-patil/</t>
+          <t>https://www.etvbharat.com/mr/!state/farmer-loan-waiver-will-be-done-we-will-keep-your-word-assured-cm-devendra-fadnavis-in-pune-yoga-day-2025-maharashtra-news-mhs25062101753</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://news24pune.com/congress-suffers-setback-in-sangli-vasantdada-patils-granddaughter-jayashree-patil-joins-bjp/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-10th-board-exam-result-2025-ssc-hsc-board-nashik-divisional-office-work-of-668-schools-pending/articleshow/118621538.cms</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-philosophy-of-thinking-positively-about-others-in-hindu-culture-chandrakantdada-patils-assertion/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/neet-pg-counselling-2024-reduction-in-cut-off-percentile-medical-council-committee-5-percentile-student-qualify/articleshow/118624987.cms</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/sangli-or-review-the-arms-licenses-in-the-district-to-control-criminal-incidents-guardian-minister-chandrakant-patil/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/notification-regarding-the-conduction-of-additional-cet-for-bca-bba-bms-bbm-cet-2025-state-common-entrance-test-cell/articleshow/121692037.cms</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/firata-davakhana-for-warkari-state-minister-chandrakant-patil-inaugurated-in-pune-article-152110556</t>
+          <t>https://marathi.indiatimes.com/career/career-news/school-bus-rules-and-regulations-for-student-in-marathi-demand-to-charge-bus-fare-for-10-months-instead-of-12/articleshow/118546648.cms</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://policenama.com/bajirao-peshwa-memorials-on-parvati-hill-development-work-of-bajirao-peshwa-memorial-on-parvati-hill-satisfactory-the-first-phase-will-be-inaugurated-by-union-minister-rajnath-singh-chandrakant-p/</t>
+          <t>https://civicmirror.in/news/polytechnic-or-engineering-diploma-admission-application-registration-deadline-extended-new-schedule-announced-minister/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/action-against-b-ed-colleges-as-per-the-rules-of-the-national-council-for-teacher-education-higher-and-technical/</t>
+          <t>https://civicmirror.in/news/loknete-laxman-jagtap-is-an-inspiring-chapter-higher-and-technical-education-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/polytechnic-admissions-2025-or-extension-of-deadline-for-submission-of-applications-for-polytechnic-courses-instructions/</t>
+          <t>https://www.eduvarta.com/Approval-for-recruitment-of-5012-posts-in-the-Assistant-Professor-cadre</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/punekars-still-consider-chandrakant-dada-to-be-from-kolhapur-ajit-pawar-harsh-comment/</t>
+          <t>https://policenama.com/mkcl-devendra-fadnavis-mkcls-silver-jubilee-foundation-day-celebrated-with-excitement-mkcls-success-in-democratizing-the-information-technology-revolution-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/pune-or-heartbroken-to-hear-the-truth-about-the-attack-chandrakant-patil-consoles-ganbote-jagdale-families/</t>
+          <t>https://civicmirror.in/news/pune-or-hadapsar-will-get-a-new-metro-line-connectivity-to-the-main-city-will-make-travel-faster/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/big-recruitment-in-the-higher-education-department-of-maharashtra-5500-professors-and-2900-employees-will-be-recruited-article-152339600</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-top-100-headlines-14-april-2025-marathi-headlines-maharashtra-chandrakant-patil-on-sanjay-raut-1354271</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/satara-news-disability-certificates-of-17-more-teachers-are-invalid/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-be-btech-mba-mms-admission-2025-deadline-extended-till-july-14-final-chance/articleshow/122391899.cms</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://policenama.com/creative-foundation-pune-creative-foundation-and-mukul-madhav-foundation-donate-useful-items-to-various-organizations-chandrakant-patil/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-approves-long-pending-faculty-recruitment-for-state-universities-colleges-101751916450665.html</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.athawadavishesh.com/34215/</t>
+          <t>https://www.hindustantimes.com/india-news/maharashtra-cites-poor-standards-proposes-no-new-pharmacy-colleges-for-5-years-101750656728006.html</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/sangli-politics-congress-suffers-setback-pruthviraj-patil-joins-bjp-with-hundreds-of-supporters/</t>
+          <t>https://www.livehindustan.com/maharashtra/uddhav-in-shinde-out-bjp-is-cooking-up-a-new-plan-in-maharashtra-chandrakant-patil-met-uddhav-201738301481336.html</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/more-than-1101-couples-perform-collective-rudra-puja-in-pune-97635/</t>
+          <t>https://www.mypunepulse.com/maharashtra-govt-approves-100-recruitment-in-engineering-colleges-boosts-higher-education-quality/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-11-political-news-in-marathi-931306</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-17-july-maharashtra-assembly-monsoon-session-2025-devendra-fadnavis-on-tri-bhasha-sutra-ola-uber-rickshaw-taxis-closed-rak-94-5234478/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-july-pune-rave-party-raj-thackeray-uddhav-thackeray-latest-news-mumbai-konkan-marathwada-weather-report-today-rain-updates-kolhapur-pandharpur-pmw-88-5267001/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/water-storage-in-seven-dams-supplying-water-to-mumbai-reaches-50-percent/articleshow/122265724.cms</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-state-government-halts-new-pharmacy-colleges-understand-the-reasons-behind-decreased-demand/articleshow/120842410.cms</t>
+          <t>https://civicmirror.in/news/uddhav-thackeray-has-accepted-the-hindi-mandatory-policy-in-the-state-reveals-minister-uday-samant/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-breaking-news-live-in-marathi-1-may-2025-maharashtra-din-kamgar-divas-pahalgam-attack-update-pm-modi-cm-devendra-fadnavis-mumbai-pune-latest-updates/liveblog/120781856.cms</t>
+          <t>https://civicmirror.in/news/hindi-is-being-forced-to-end-marathi-language-and-culture-we-will-defeat-this-agenda-of-bjp-and-rss-harshvardhan-sapkal/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/farmer-loan-waiver-will-be-done-we-will-keep-your-word-assured-cm-devendra-fadnavis-in-pune-yoga-day-2025-maharashtra-news-mhs25062101753</t>
+          <t>https://civicmirror.in/news/raj-thackeray-announces-grand-march-against-hindi-compulsion/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/jalgaon-news/st-bus-brakes-fail-in-chopda-taluka-newlywed-youth-died-in-accident-cctv-footage/articleshow/121291227.cms</t>
+          <t>https://civicmirror.in/news/jayant-patil-emotional-letter-to-maharashtra-marathi/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-10th-board-exam-result-2025-ssc-hsc-board-nashik-divisional-office-work-of-668-schools-pending/articleshow/118621538.cms</t>
+          <t>https://www.dainikprabhat.com/pune-news-pune-festival-to-begin-on-august-29-inauguration-by-governor/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/neet-pg-counselling-2024-reduction-in-cut-off-percentile-medical-council-committee-5-percentile-student-qualify/articleshow/118624987.cms</t>
+          <t>https://www.hindustantimes.com/trending/dead-bodies-debris-eyewitness-recalls-hearing-massive-sound-during-air-india-plane-crash-101749723280168.html</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/notification-regarding-the-conduction-of-additional-cet-for-bca-bba-bms-bbm-cet-2025-state-common-entrance-test-cell/articleshow/121692037.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/pregnant-womans-dad-accuses-spouse-kin-of-harassment/articleshow/121809105.cms</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/thane-municipal-corporation-fir-against-68-unauthorized-schools-52-crore-fine/articleshow/118617204.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-seek-restoration-of-savarkar-s-barrister-degree-101748373138133.html</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/school-bus-rules-and-regulations-for-student-in-marathi-demand-to-charge-bus-fare-for-10-months-instead-of-12/articleshow/118546648.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/aftermath-of-baby-kidnap-sangli-guardian-minister-chandrakant-patil-announces-enhanced-security-measures-at-miraj-govt-hospital/articleshow/121006495.cms</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/city/pune/big-announcement-for-pune-police-will-get-5-new-police-stations-and-1000-additional-police-force/</t>
+          <t>https://timesofindia.indiatimes.com/education/news/maharashtra-launches-atal-portal-for-entrance-prep-and-career-guidance/articleshow/117296155.cms</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://policenama.com/mkcl-devendra-fadnavis-mkcls-silver-jubilee-foundation-day-celebrated-with-excitement-mkcls-success-in-democratizing-the-information-technology-revolution-devendra-fadnavis/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/days-before-hsc-exam-70-students-get-hall-tickets-with-wrong-subjects/articleshow/118097108.cms</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/pune-or-hadapsar-will-get-a-new-metro-line-connectivity-to-the-main-city-will-make-travel-faster/</t>
+          <t>https://www.newsonair.gov.in/india-emerging-as-global-knowledge-partner-dharmendra-pradhan/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/65971/</t>
+          <t>https://news.careers360.com/mht-cet-pcm-re-test-2025-may-5-for-27837-english-urdu-marathi-21-maths-questions-go-wrong-paper-setters-blacklisted</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-be-btech-mba-mms-admission-2025-deadline-extended-till-july-14-final-chance/articleshow/122391899.cms</t>
+          <t>https://www.punekarnews.in/millennium-national-school-shines-at-invitational-taekwondo-inter-school-competition/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/sangli-news-unseasonal-rain-in-miraj-tasgaon-hits-rabi-winter-crops/articleshow/119493800.cms</t>
+          <t>https://marathi.indiatimes.com/career/career-news/mht-cet-2025-pcm-group-re-exam-on-may-5-exam-canceled-due-to-technical-errors-conducted-on-27-april/articleshow/120769046.cms</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-conduct-second-cet-colleges-worried-about-delay-in-academic-year-101749409146794.html</t>
+          <t>https://civicmirror.in/news/rte-news-preparations-to-boycott-private-english-medium-school-admission-process-due-to-this-reason/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-approves-long-pending-faculty-recruitment-for-state-universities-colleges-101751916450665.html</t>
+          <t>https://marathi.timesnownews.com/maharashtra/mht-cet-2025-reexam-announces-for-pcm-on-may-5-due-to-errors-in-21-questions-read-details-in-marathi-article-151540811</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/uddhav-in-shinde-out-bjp-is-cooking-up-a-new-plan-in-maharashtra-chandrakant-patil-met-uddhav-201738301481336.html</t>
+          <t>https://civicmirror.in/maharashtra/mht-cet-exam-2025-or-technical-glitch-in-mht-cet-2025-pcm-group-exam-re-exam-on-may-5th/cid1746067306.htm</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/video/mla-chandrakant-patil-in-custody-protest-on-the-highway-with-farmers-ytvd-2293913-2025-07-23</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/patankar-and-patil-join-bjp-as-strong-rivals-of-sitting-sena-mlas/articleshow/121762155.cms</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/maharashtra-govt-approves-100-recruitment-in-engineering-colleges-boosts-higher-education-quality/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/former-cm-vasantdada-patils-granddaughter-in-law-joins-bjp/articleshow/121893459.cms</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-17-july-maharashtra-assembly-monsoon-session-2025-devendra-fadnavis-on-tri-bhasha-sutra-ola-uber-rickshaw-taxis-closed-rak-94-5234478/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/congress-sangli-city-prez-prithviraj-patil-to-join-bjp/articleshow/123265799.cms</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/water-storage-in-seven-dams-supplying-water-to-mumbai-reaches-50-percent/articleshow/122265724.cms</t>
+          <t>https://www.indiatoday.in/india/story/sanjay-raut-bjp-shiv-sena-ubt-alliance-maharashtra-mahayuti-mva-devendra-fadnavis-2672702-2025-01-31</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/uddhav-thackeray-has-accepted-the-hindi-mandatory-policy-in-the-state-reveals-minister-uday-samant/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-mlc-first-to-record-statement-in-cm-s-sit-probe-101740079847054.html</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/hindi-is-being-forced-to-end-marathi-language-and-culture-we-will-defeat-this-agenda-of-bjp-and-rss-harshvardhan-sapkal/</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/news/raj-thackeray-announces-grand-march-against-hindi-compulsion/</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/news/jayant-patil-emotional-letter-to-maharashtra-marathi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>https://www.dainikprabhat.com/pune-news-pune-festival-to-begin-on-august-29-inauguration-by-governor/</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/trending/saw-smoke-in-the-eyewitness-at-ahmedabad-airport-describes-air-india-crash-101749727540094.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>https://www.newsonair.gov.in/india-emerging-as-global-knowledge-partner-dharmendra-pradhan/</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/ahilyadevi-holkar-s-legacy-must-be-known-to-youth-cm-101748631369699.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>https://news.careers360.com/mht-cet-pcm-re-test-2025-may-5-for-27837-english-urdu-marathi-21-maths-questions-go-wrong-paper-setters-blacklisted</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-seek-restoration-of-savarkar-s-barrister-degree-101748373138133.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/pregnant-womans-dad-accuses-spouse-kin-of-harassment/articleshow/121809105.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/education/news/maharashtra-launches-atal-portal-for-entrance-prep-and-career-guidance/articleshow/117296155.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/days-before-hsc-exam-70-students-get-hall-tickets-with-wrong-subjects/articleshow/118097108.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/163883/</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/marathi-bhasha-gaurav-din-2025-marathi-schools-on-the-verge-of-shut-down-in-future-in-maharashtra-know-the-reason-maharashtra-news-mhs25022606375</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/career/career-news/mht-cet-2025-pcm-group-re-exam-on-may-5-exam-canceled-due-to-technical-errors-conducted-on-27-april/articleshow/120769046.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/news/rte-news-preparations-to-boycott-private-english-medium-school-admission-process-due-to-this-reason/</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>https://marathi.timesnownews.com/maharashtra/mht-cet-2025-reexam-announces-for-pcm-on-may-5-due-to-errors-in-21-questions-read-details-in-marathi-article-151540811</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/mht-cet-exam-2025-or-technical-glitch-in-mht-cet-2025-pcm-group-exam-re-exam-on-may-5th/cid1746067306.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/patankar-and-patil-join-bjp-as-strong-rivals-of-sitting-sena-mlas/articleshow/121762155.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/former-cm-vasantdada-patils-granddaughter-in-law-joins-bjp/articleshow/121893459.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/congress-sangli-city-prez-prithviraj-patil-to-join-bjp/articleshow/123265799.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-parties-battling-each-other-during-poaching-spree-101751053618819.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-mlc-first-to-record-statement-in-cm-s-sit-probe-101740079847054.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
           <t>https://www.hindustantimes.com/cities/pune-news/bjp-leaders-conduct-back-to-back-separate-review-meetings-at-pmc-oppn-questions-lack-of-results-101751143694920.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>https://www.tarunbharat.com/prithviraj-patil-avoided-joining-the-bjp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>https://www.lokmat.com/sangli/former-chief-minister-vasantdada-patil-granddaughter-jayashreetai-patil-will-join-bjp-a-a746/</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A238"/>
+  <dimension ref="A1:A226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,7 +480,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/outright-kunbi-status-to-will-not-stand-legal-test-chandrakant-patil/articleshow/123487443.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/sangli-guardian-minister-chandrakant-patil-calls-upon-former-bjp-mp-sanjaykaka-patil-urges-him-to-return-to-bjp/articleshow/119609029.cms</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/bjp-mantris-remark-sparks-buzz-of-patch-up-with-shiv-sena-ubt/articleshow/117754765.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/movie-phule-depicts-discrimination-of-bygone-era-no-need-to-oppose-it-chandrakant-patil/articleshow/120288218.cms</t>
         </is>
       </c>
     </row>
@@ -508,273 +508,273 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/sangli-guardian-minister-chandrakant-patil-calls-upon-former-bjp-mp-sanjaykaka-patil-urges-him-to-return-to-bjp/articleshow/119609029.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/after-kulkarni-s-criticism-mohol-and-chandrakant-patil-come-out-in-support-of-bjp-workers-101744225445616.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/after-kulkarni-s-criticism-mohol-and-chandrakant-patil-come-out-in-support-of-bjp-workers-101744225445616.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/1000-new-personnel-to-join-pune-police-force-chandrakant-patil-101751829456309.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/movie-phule-depicts-discrimination-of-bygone-era-no-need-to-oppose-it-chandrakant-patil/articleshow/120288218.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/may-become-minister-in-future-either-joining-congress-or-any-other-party-says-vishal-patil-weeks-after-chandrakant-patils-offer-to-join-bjp/articleshow/120171254.cms</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/may-become-minister-in-future-either-joining-congress-or-any-other-party-says-vishal-patil-weeks-after-chandrakant-patils-offer-to-join-bjp/articleshow/120171254.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/vishal-patil-turns-down-bjp-ministers-offer-to-join-alliance/articleshow/119084771.cms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/1000-new-personnel-to-join-pune-police-force-chandrakant-patil-101751829456309.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/100-per-cent-fee-waiver-for-ews-girls-chandrakant-patil-101750360390574.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/mva-sanjay-raut-bjp-sena-ubt-9808199/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/outright-kunbi-status-to-will-not-stand-legal-test-chandrakant-patil/articleshow/123487443.cms</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/vishal-patil-turns-down-bjp-ministers-offer-to-join-alliance/articleshow/119084771.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-of-different-backgrounds-are-bound-to-disagree-in-coalition-govt-chandrakant-patil-23519840</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/100-per-cent-fee-waiver-for-ews-girls-chandrakant-patil-101750360390574.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-tells-officials-to-expedite-land-acquisition-for-roads-in-kothrud-101745865957490.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-tells-officials-to-expedite-land-acquisition-for-roads-in-kothrud-101745865957490.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/grateful-minister-urges-edu-trust-to-go-autonomous-101752002033361.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/grateful-minister-urges-edu-trust-to-go-autonomous-101752002033361.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-ministers-golden-moment-remark-sparks-buzz-of-uddhav-thackeray-bjp-patch-up/articleshow/117769125.cms</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-ministers-golden-moment-remark-sparks-buzz-of-uddhav-thackeray-bjp-patch-up/articleshow/117769125.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/congress-sangli-city-prez-prithviraj-patil-to-join-bjp/articleshow/123265799.cms</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/rss-holds-two-day-brainstorming-session-with-bjp-allied-outfits-3362607</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/aftermath-of-baby-kidnap-sangli-guardian-minister-chandrakant-patil-announces-enhanced-security-measures-at-miraj-govt-hospital/articleshow/121006495.cms</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/former-cm-vasantdada-patils-granddaughter-in-law-joins-bjp/articleshow/121893459.cms</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/dh-evening-brief-bsf-jawan-returns-from-pak-custody-fir-ordered-against-mp-minister-for-remarks-against-col-sofia-qureshi-3540442</t>
+          <t>https://www.hindustantimes.com/trending/saw-smoke-in-the-eyewitness-at-ahmedabad-airport-describes-air-india-crash-101749727540094.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/states-tech-edu-minister-reviews-fee-waiver-for-women-students/articleshow/118310028.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/if-some-leader-leaves-not-necessarily-people-join-him-vishwajeet-kadam/articleshow/123289946.cms</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/07/27/retirement-age-of-college-principals-raised-to-65-announces-minister-chandrakant-patil/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/rss-holds-two-day-brainstorming-session-with-bjp-allied-outfits-3362607</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/dpdc-meeting-on-thursday-101738176153028.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/sub-centre-of-sppu-slated-to-be-inaugurated-by-may-end-in-nashiks-shivnai-area-chandrakant-patil-instructs-officials-to-expedite-facility/articleshow/121036464.cms</t>
+          <t>https://www.deccanherald.com/india/dh-evening-brief-bsf-jawan-returns-from-pak-custody-fir-ordered-against-mp-minister-for-remarks-against-col-sofia-qureshi-3540442</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-asks-pmc-to-acquire-land-on-priority-as-balewadi-wakad-bridge-lies-unused-101751741109744.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/states-tech-edu-minister-reviews-fee-waiver-for-women-students/articleshow/118310028.cms</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://punemirror.com/pune-mirror-explore/pune-news-chandrakant-patil-issues-ultimatum-to-pune-municipal-corporation-over-solid-waste-management-project/</t>
+          <t>https://thelivenagpur.com/2025/07/27/retirement-age-of-college-principals-raised-to-65-announces-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/def-min-likely-to-inaugurate-peshwa-memorial-at-parvati-101736539722952.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/dpdc-meeting-on-thursday-101738176153028.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/three-week-monsoon-session-of-maharashtra-assembly-to-begin-on-monday-1887745</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/sub-centre-of-sppu-slated-to-be-inaugurated-by-may-end-in-nashiks-shivnai-area-chandrakant-patil-instructs-officials-to-expedite-facility/articleshow/121036464.cms</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-silent-on-bavdhan-garbage-plant-issue-in-pmc-meeting-101745953467654.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-asks-pmc-to-acquire-land-on-priority-as-balewadi-wakad-bridge-lies-unused-101751741109744.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra:-cabinet-sub-committee-on-maratha-quota-reconstituted;-vikhe-patil-new-head/2847184</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/no-cet-outside-maharashtra-minister-101749151005604.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-adds-fourth-cap-round-for-engineering-admissions-to-curb-costly-pvt-options-101749150825079.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-conduct-second-cet-colleges-worried-about-delay-in-academic-year-101749409146794.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-may-halt-admissions-to-pharmacy-colleges-flouting-norms-101753902851567.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/def-min-likely-to-inaugurate-peshwa-memorial-at-parvati-101736539722952.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ahead-of-jarange-stir-in-mumbai-cabinet-sub-committee-on-maratha-quota-reconstituted-vikhe-patil-now-new-head/articleshow/123460725.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-parties-battling-each-other-during-poaching-spree-101751053618819.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/pune-civic-body-acts-against-unauthorised-stalls-on-fc-road-101749148183563.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ahead-of-jarange-stir-in-mumbai-cabinet-sub-committee-on-maratha-quota-reconstituted-vikhe-patil-now-new-head/articleshow/123460725.cms</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-to-restart-withdrawn-services-by-tanker-association-with-police-help-101744571005989.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-deputy-chief-minister-ajit-pawar-vows-swift-action-to-restore-obc-quota/articleshow/120525973.cms</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-government-plans-to-grant-university-status-to-jbims-101743881532444.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-silent-on-bavdhan-garbage-plant-issue-in-pmc-meeting-101745953467654.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/islampur-to-be-renamed-ishwarpur-101752864742122.html</t>
+          <t>https://www.ptinews.com/story/national/maharashtra:-cabinet-sub-committee-on-maratha-quota-reconstituted;-vikhe-patil-new-head/2847184</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/06/06/maharashtra-introduces-new-rule-stops-cet-exams-at-centres-outside-the-state/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-adds-fourth-cap-round-for-engineering-admissions-to-curb-costly-pvt-options-101749150825079.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/c-r-patil-takes-charge-as-jal-shakti-minister/1575205</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/state-committed-to-opposing-almatti-height-rise-says-minister-vikhe-patil/articleshow/118652829.cms</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/civic/chandrakant-patil-takes-action-on-kothrud-s-road-water-and-traffic-issues/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/protesters-oppose-name-expansion-proposal-of-shivaji-university-in-kolhapur/articleshow/119544233.cms</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://education.economictimes.indiatimes.com/news/higher-education/marathwada-varsity-stops-pg-admissions-in-113-colleges-after-irregularities-come-to-fore/122912620</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-government-plans-to-grant-university-status-to-jbims-101743881532444.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/police-bust-chain-snatching-gang-two-held-minor-detained-101740078106456.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/islampur-to-be-renamed-ishwarpur-101752864742122.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://punemirror.com/education/maharashtra-unveils-ambitious-higher-education-reforms/</t>
+          <t>https://thelivenagpur.com/2025/06/06/maharashtra-introduces-new-rule-stops-cet-exams-at-centres-outside-the-state/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/maharashtra-politics-did-bjp-minister-just-confirm-rift-within-mahayuti-shindes-meeting-with-shah-2886410.html</t>
+          <t>https://education.economictimes.indiatimes.com/news/higher-education/marathwada-varsity-stops-pg-admissions-in-113-colleges-after-irregularities-come-to-fore/122912620</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/civic/baner-balewadi-traffic-woes-get-high-level-attention-at-key-pmc-meeting/</t>
+          <t>https://news.careers360.com/cet-for-courses-in-maharashtra-not-be-held-outside-state-prevent-malpractices-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
@@ -802,238 +802,238 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-major-announcement-for-girls-education-minister-chandrakant-patil-to-inspect-100-colleges-review-fee-waiver-implementation/</t>
+          <t>https://news.careers360.com/maharashtra-state-cet-cell-launches-cet-atal-module-for-mock-tests</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/chandrakant-patil-reveals-details-of-vidhan-bhavan-meetings-on-pune-municipal-corporation-budget/</t>
+          <t>https://www.mypunepulse.com/pune-news-chandrakant-patil-urges-citizens-to-stay-vigilant/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/traffic-congestion-free-kothrud-minister-chandrakant-patil-pushes-for-ai-based-challan-system/</t>
+          <t>https://www.mypunepulse.com/pune-major-announcement-for-girls-education-minister-chandrakant-patil-to-inspect-100-colleges-review-fee-waiver-implementation/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/ensure-safety-measures-for-pune-hills-higher-and-technical-education-minister-chandrakant-patils-directives/</t>
+          <t>https://www.mypunepulse.com/chandrakant-patil-reveals-details-of-vidhan-bhavan-meetings-on-pune-municipal-corporation-budget/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-chandrakant-patil-warns-pmc-shut-down-sus-waste-project-or-face-protest/</t>
+          <t>https://www.mypunepulse.com/traffic-congestion-free-kothrud-minister-chandrakant-patil-pushes-for-ai-based-challan-system/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-chandrakant-patil-demands-swift-action-on-citys-missing-road-link-projects/</t>
+          <t>https://www.mypunepulse.com/ensure-safety-measures-for-pune-hills-higher-and-technical-education-minister-chandrakant-patils-directives/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/global-ganesh-festival-2025-eknath-shinde-to-lead-chandrakant-patil-as-chief-receptionist/</t>
+          <t>https://www.mypunepulse.com/pune-chandrakant-patil-warns-pmc-shut-down-sus-waste-project-or-face-protest/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/chandrakant-patil-proposes-safety-measures-to-prevent-fires-on-punes-17-hills/</t>
+          <t>https://www.mypunepulse.com/pune-chandrakant-patil-demands-swift-action-on-citys-missing-road-link-projects/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/minister-chandrakant-patil-orders-comprehensive-report-on-challenges-faced-by-educational-institutions-in-maharashtra/</t>
+          <t>https://www.punekarnews.in/global-ganesh-festival-2025-eknath-shinde-to-lead-chandrakant-patil-as-chief-receptionist/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-chandrakant-patil-orders-immediate-measures-to-resolve-baner-balewadi-traffic-woes/</t>
+          <t>https://www.punekarnews.in/minister-chandrakant-patil-orders-comprehensive-report-on-challenges-faced-by-educational-institutions-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-chandrakant-patil-flags-pmc-misgovernance-amid-delayed-elections-high-level-meeting-with-ajit-pawar-likely/</t>
+          <t>https://www.mypunepulse.com/pune-chandrakant-patil-orders-immediate-measures-to-resolve-baner-balewadi-traffic-woes/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-chandrakant-patil-promises-full-support-for-women-empowerment-and-girls-education-in-mulshi-taluka/</t>
+          <t>https://www.punekarnews.in/pune-high-level-meeting-held-to-resolve-baner-balewadi-traffic-woes-minister-chandrakant-patil-orders-immediate-action/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-high-level-meeting-held-to-resolve-baner-balewadi-traffic-woes-minister-chandrakant-patil-orders-immediate-action/</t>
+          <t>https://www.punekarnews.in/1000-new-cops-to-join-pune-police-force-as-city-expands-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/1000-new-cops-to-join-pune-police-force-as-city-expands-chandrakant-patil/</t>
+          <t>https://www.mypunepulse.com/cet-exams-to-be-held-only-within-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/delay-in-punes-equal-water-supply-scheme-sparks-public-discontent-mla-chandrakant-patil-criticizes-pmc/</t>
+          <t>https://www.punekarnews.in/maharashtra-government-implements-new-transparent-recruitment-process-for-university-faculty/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://affairscloud.com/union-minister-of-jal-shakti-cr-patil-reviewed-key-projects-of-wii-under-nmcg/</t>
+          <t>https://www.mypunepulse.com/maharashtra-govt-approves-100-recruitment-in-engineering-colleges-boosts-higher-education-quality/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/maharashtra-govt-unveils-new-grading-system-to-modernise-public-libraries/</t>
+          <t>https://www.punekarnews.in/pune-hosts-grand-warkari-bhaktiyog-2025-on-international-yoga-day/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/cet-exams-to-be-held-only-within-maharashtra/</t>
+          <t>https://affairscloud.com/union-minister-of-jal-shakti-cr-patil-reviewed-key-projects-of-wii-under-nmcg/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/society-is-responsible-for-keeping-every-person-alive-cm-devendra-fadnavis-at-guinness-world-record-event-in-pune/</t>
+          <t>https://www.hindustanmetro.com/mr-sunjjoy-chaudhri-leads-team-veer-santaji-at-khasdar-celebrity-cricket-league-2025-celebrating-punes-grand-festival-with-support-from-mr-murlidhar-mohol-and-mr-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/maharashtra-government-implements-new-transparent-recruitment-process-for-university-faculty/</t>
+          <t>https://www.punekarnews.in/pune-minister-orders-compulsory-land-acquisition-to-open-balewadi-wakad-mula-river-bridge/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/cap-maharashtra-to-introduce-four-rounds-in-centralised-engineering-admissions-stricter-seat-allotment-rules-planned/</t>
+          <t>https://www.hindustanmetro.com/maharashtra-state-cet-cell-launches-visionary-initiative-cet-atal-module-for-mock-tests/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-hosts-grand-warkari-bhaktiyog-2025-on-international-yoga-day/</t>
+          <t>https://mahasamvad.in/171311/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.hindustanmetro.com/mr-sunjjoy-chaudhri-leads-team-veer-santaji-at-khasdar-celebrity-cricket-league-2025-celebrating-punes-grand-festival-with-support-from-mr-murlidhar-mohol-and-mr-chandrakant-patil/</t>
+          <t>https://www.tv9marathi.com/maharashtra/raksha-khadse-daughter-harassed-reaction-of-mla-chandrakant-patil-1359186.html</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-defence-minister-rajnath-singh-likely-to-inaugurate-peshwa-memorial-at-parvati-hill/</t>
+          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-milind-narvekar-and-chandrakant-patil-meet-at-parag-alavani-daughter-wedding-and-discussion-on-yuti-impact-on-maharashtra-politics-1341419</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-minister-orders-compulsory-land-acquisition-to-open-balewadi-wakad-mula-river-bridge/</t>
+          <t>https://marathi.abplive.com/videos/news/jalgaon-chandrakant-patil-shiv-sena-on-raksha-khadse-daughter-devendra-fadanvis-marathi-news-abp-majha-1347066</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-06-2025-%E0%A4%89%E0%A4%9A%E0%A5%8D%E0%A4%9A-%E0%A4%B5-%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A4%BF%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D/</t>
+          <t>https://mahasamvad.in/176328/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171311/</t>
+          <t>https://mahasamvad.in/173280/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-milind-narvekar-and-chandrakant-patil-meet-at-parag-alavani-daughter-wedding-and-discussion-on-yuti-impact-on-maharashtra-politics-1341419</t>
+          <t>https://marathi.abplive.com/news/maharashtra/extension-of-the-deadline-for-admission-registration-conducted-by-cet-cell-information-from-minister-chandrakant-patil-1368834</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-chandrakant-patil-reaction-on-dhananjay-munde-ministerial-post-says-cm-will-take-decision-on-resignation-kvg-85-4850775/</t>
+          <t>https://marathi.abplive.com/news/politics/eknath-khadse-vs-chandrakant-patil-how-did-34-acres-of-land-become-100-acres-eknath-khadse-response-to-chandrakant-patil-allegations-jalgaon-maharashtra-politics-marathi-news-1362993</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/minister-chandrakant-patil-suggestion-after-pratibimb-foundation-take-a-big-step-for-the-career-of-journalists-sons-and-daughters-along-with-health-of-their-families-maharashtra-marathi-news-1355102</t>
+          <t>https://mahasamvad.in/176819/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-statement-on-jayant-patil-ncp-sharad-pawar-leader-sangli-politics-marathi-news-1371392</t>
+          <t>https://mahasamvad.in/176831/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176328/</t>
+          <t>https://mahasamvad.in/176833/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173280/</t>
+          <t>https://mahasamvad.in/169332/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173478/</t>
+          <t>https://www.loksatta.com/maharashtra/sanjay-raut-reaction-on-chandrakant-patil-statement-of-shivsena-bjp-alliance-will-be-golden-moment-sgk-96-4858543/</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-have-137-mlas-black-magic-will-do-nothing-maharashtra-government-will-run-for-5-years-says-chandrakant-patil-at-kolhapur-1344696</t>
+          <t>https://mahasamvad.in/173478/</t>
         </is>
       </c>
     </row>
@@ -1061,1036 +1061,952 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175996/</t>
+          <t>https://mahasamvad.in/163743/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163743/</t>
+          <t>https://mahasamvad.in/175756/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/eknath-khadse-vs-chandrakant-patil-how-did-34-acres-of-land-become-100-acres-eknath-khadse-response-to-chandrakant-patil-allegations-jalgaon-maharashtra-politics-marathi-news-1362993</t>
+          <t>https://mahasamvad.in/176171/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175756/</t>
+          <t>https://www.loksatta.com/maharashtra/shivaji-university-s-sub-centre-in-khanapur-says-chandrakant-patil-zws-70-4960985/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176831/</t>
+          <t>https://mahasamvad.in/173059/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176833/</t>
+          <t>https://mahasamvad.in/176754/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169332/</t>
+          <t>https://marathi.ndtv.com/maharashtra/pune-news-chandrakant-patil-slams-raj-thackeray-uddhav-thackeray-on-hindi-language-controvery-8785417</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176819/</t>
+          <t>https://mahasamvad.in/163261/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/education/college-admission-for-engineers-from-june-28-extension-for-diploma-till-june-30-minister-chandrakant-patil-decision-1366417</t>
+          <t>https://mahasamvad.in/160007/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/minister-chandrakant-patil-appeal-over-tomb-of-tiger-dog-controversy-zws-70-4983085/</t>
+          <t>https://mahasamvad.in/169326/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175217/</t>
+          <t>https://www.mahasamvad.in/169422/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176754/</t>
+          <t>https://mahasamvad.in/175217/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173059/</t>
+          <t>https://mahasamvad.in/161166/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/pune-news-chandrakant-patil-slams-raj-thackeray-uddhav-thackeray-on-hindi-language-controvery-8785417</t>
+          <t>https://marathi.indiatimes.com/career/career-news/minister-chandrakant-patil-new-responsibility-of-professors-for-students-instructions-for-effective-implementation-of-college-schemes/articleshow/121717827.cms</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163261/</t>
+          <t>https://mahasamvad.in/174729/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169326/</t>
+          <t>https://mahasamvad.in/160626/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/169422/</t>
+          <t>https://www.tv9marathi.com/videos/bjp-leader-minister-chandrakant-patil-big-statement-regarding-ministerial-post-at-sangli-1390006.html</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161166/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/minister-chandrakant-patil-and-farmers-dispute-broke-out-between-in-sangli/articleshow/120792863.cms</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/minister-chandrakant-patil-new-responsibility-of-professors-for-students-instructions-for-effective-implementation-of-college-schemes/articleshow/121717827.cms</t>
+          <t>https://mahasamvad.in/173128/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174729/</t>
+          <t>https://mahasamvad.in/173013/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160626/</t>
+          <t>https://www.msn.com/mr-in/news/other/sangli-news-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%8F%E0%A4%95-%E0%A4%9A-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%AA-%E0%A4%A0-%E0%A4%B5%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A4%97-%E0%A4%A8-%E0%A4%AE-%E0%A4%88-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A0%E0%A4%B0%E0%A4%A3-%E0%A4%B0/ar-AA1KyMam</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-leader-chandrkant-patil-on-dhananjay-munde-resignation-and-walmik-karad-connection-on-beed-massajog-santosh-deshmukh-case-1340832</t>
+          <t>https://mahasamvad.in/172372/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-leader-minister-chandrakant-patil-big-statement-regarding-ministerial-post-at-sangli-1390006.html</t>
+          <t>https://mahasamvad.in/164366/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/do-not-bow-to-politicians-says-education-minister-urges-teachers-to-uphold-dignity-of-profession-pune-print-news-ccp-14-ocd-94-5253062/</t>
+          <t>https://mahasamvad.in/170382/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/minister-chandrakant-patil-and-farmers-dispute-broke-out-between-in-sangli/articleshow/120792863.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-on-rohini-khadse-jalgaon-news-mla-chandrakant-patil-criticizes-rohini-khadse-1379392</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173128/</t>
+          <t>https://mahasamvad.in/176760/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/sangli-news-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%8F%E0%A4%95-%E0%A4%9A-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%AA-%E0%A4%A0-%E0%A4%B5%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A4%97-%E0%A4%A8-%E0%A4%AE-%E0%A4%88-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A0%E0%A4%B0%E0%A4%A3-%E0%A4%B0/ar-AA1KyMam</t>
+          <t>https://www.loksatta.com/mumbai/engineering-admission-process-revision-four-cap-rounds-says-chandrakant-patil-mumbai-print-news-zws-70-5137735/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172372/</t>
+          <t>https://mahasamvad.in/162964/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176760/</t>
+          <t>https://mahasamvad.in/161614/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/164366/</t>
+          <t>https://mahasamvad.in/158873/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170382/</t>
+          <t>https://mahasamvad.in/173469/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-on-rohini-khadse-jalgaon-news-mla-chandrakant-patil-criticizes-rohini-khadse-1379392</t>
+          <t>https://deshdoot.com/recruitment-of-4435-posts-of-assistant-professors-soon-information-from-higher-and-technical-education-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/162964/</t>
+          <t>https://www.tv9marathi.com/videos/chandrakant-patil-slams-uddhav-thackeray-1439709.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154565/</t>
+          <t>https://mahasamvad.in/157924/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/eps-employees-pension-%E0%A4%88%E0%A4%AA-%E0%A4%8F%E0%A4%B8-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A4%9A-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A8-%E0%A4%B5%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%B5%E0%A5%87%E0%A4%A4%E0%A4%A8-%E0%A4%AE-%E0%A4%B3%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%A0-%E0%A4%AA-%E0%A4%A0%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%B5-%E0%A4%95%E0%A4%B0%E0%A5%82-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2/ar-AA1La4cI</t>
+          <t>https://mahasamvad.in/174461/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161614/</t>
+          <t>https://www.tv9marathi.com/maharashtra/rohit-pawar-praised-chandrakant-patil-and-taunts-gopichand-padalkar-know-what-he-said-1470906.html</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158873/</t>
+          <t>https://marathi.ndtv.com/maharashtra/ndtv-marathi-emerging-business-conclave-chandrakant-patil-rupali-chakankar-on-pune-traffic-rain-issue-8786115</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173469/</t>
+          <t>https://mahasamvad.in/175300/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157924/</t>
+          <t>https://marathi.ndtv.com/maharashtra/chandrakant-patil-instructions-to-professors-on-scholarship-implementation-in-colleges-8612913</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/chandrkant-patil-will-the-farmers-affected-by-shaktipeeth-get-compensation-what-did-chandrakant-patil-say/912426/</t>
+          <t>https://www.tv9marathi.com/videos/bjp-chandrakant-patil-suggestion-to-mns-raj-thackeray-over-hindi-compulsory-in-maharashtra-school-1429353.html</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/recruitment-of-4435-posts-of-assistant-professors-soon-information-from-higher-and-technical-education-minister-chandrakant-patil/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-bharti-new-procedure-announced-for-selection-process-minister-chandrakant-patil/articleshow/118607489.cms</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174461/</t>
+          <t>https://mahasamvad.in/160732/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/ndtv-marathi-emerging-business-conclave-chandrakant-patil-rupali-chakankar-on-pune-traffic-rain-issue-8786115</t>
+          <t>https://mahasamvad.in/162538/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175300/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-recruitment-2025-college-teachers-bharti-education-minister-chandrakant-patil/articleshow/118924405.cms</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/162538/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/jayshree-patil-to-join-bjp-presence-chief-minister-devendra-fadnavis/articleshow/121881414.cms</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-bharti-new-procedure-announced-for-selection-process-minister-chandrakant-patil/articleshow/118607489.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/medha-kulkarni-left-bjp-meeting-midway-as-chandrakant-patil-murlidhar-mohol-backs-deenanath-mangeshkar-case-andolan/articleshow/120120230.cms</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160732/</t>
+          <t>https://www.bbc.com/marathi/live/c3e4qkvvdkvt?page=2</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-recruitment-2025-college-teachers-bharti-education-minister-chandrakant-patil/articleshow/118924405.cms</t>
+          <t>https://marathi.abplive.com/news/solapur/solapur-jayakumar-gore-news-guardian-minister-jayakumar-gore-reaction-to-mla-ranjitsinh-mohite-patil-in-solapur-1361873</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173736/</t>
+          <t>https://www.newsonair.gov.in/mr/education-free-for-female-students/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169668/</t>
+          <t>https://marathi.abplive.com/news/pune/pune-digital-media-social-work-honoured-in-pune-ikshan-pratishthan-for-the-children-of-journalists-ceremony-in-the-presence-of-chandrakant-patil-1360276</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/jayshree-patil-to-join-bjp-presence-chief-minister-devendra-fadnavis/articleshow/121881414.cms</t>
+          <t>https://mahasamvad.in/153348/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/medha-kulkarni-left-bjp-meeting-midway-as-chandrakant-patil-murlidhar-mohol-backs-deenanath-mangeshkar-case-andolan/articleshow/120120230.cms</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-government-made-changes-in-maratha-reservation-sub-committee-rahadhakrishna-vikhe-patil-will-ne-president-1379124</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/153348/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/girl-free-education-scheme-in-maharashtra-latest-news-chandrakant-patil-mulina-mofat-shikshan-yojana-maharashtra-2024/articleshow/118265312.cms</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163883/</t>
+          <t>https://civicmirror.in/news/pune-or-heartbroken-to-hear-the-truth-about-the-attack-chandrakant-patil-consoles-ganbote-jagdale-families/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/education/chandrakant-patil-announced-ews-certificate-accepted-for-one-year-economically-weaker-section-student-maharashtra-education-marathi-news-1340514</t>
+          <t>https://www.tarunbharat.com/chandrakant-atial-discussion-with-flood-situated-people-sangli-walwa-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/girl-free-education-scheme-in-maharashtra-latest-news-chandrakant-patil-mulina-mofat-shikshan-yojana-maharashtra-2024/articleshow/118265312.cms</t>
+          <t>https://civicmirror.in/news/polytechnic-admissions-2025-or-extension-of-deadline-for-submission-of-applications-for-polytechnic-courses-instructions/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/chandrakant-atial-discussion-with-flood-situated-people-sangli-walwa-marathi-news/</t>
+          <t>https://news18marathi.com/maharashtra/mahayuti-leaders-ajit-pawar-chandrakant-patil-and-shrikant-shinde-on-mission-sangli-for-damage-maha-vikas-aghadi-1386892.html</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/videos/vishesh-vartankan/5018629/chandrakant-patil-criticized-sanjay-raut-over-maharashtra-politics/</t>
+          <t>https://www.mymahanagar.com/maharashtra/ravindra-dhangekar-allegation-chandrakant-patil-and-murlidhar-mohol-politics-for-gajanan-marne-arrested/854647/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/mahayuti-leaders-ajit-pawar-chandrakant-patil-and-shrikant-shinde-on-mission-sangli-for-damage-maha-vikas-aghadi-1386892.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ajit-pawar-devendra-fadnavis-shares-fun-moment-at-pune-lokmanya-tilak-award-ceremony-with-chandrakant-patil-eknath-shinde/articleshow/123054887.cms</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ajit-pawar-devendra-fadnavis-shares-fun-moment-at-pune-lokmanya-tilak-award-ceremony-with-chandrakant-patil-eknath-shinde/articleshow/123054887.cms</t>
+          <t>https://civicmirror.in/news/action-against-b-ed-colleges-as-per-the-rules-of-the-national-council-for-teacher-education-higher-and-technical/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/medha-kulkarni-left-the-meeting-chandrakant-patil-murlidhar-mohol-supported-the-deenanath-mangeshkar-case-andolan-tanisha-bhise-death-case-what-exactly-happened-during-the-meeting-1353526</t>
+          <t>https://marathi.abplive.com/education/chandrakant-patil-announced-ews-certificate-accepted-for-one-year-economically-weaker-section-student-maharashtra-education-marathi-news-1340514</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/guardian-minister-orders-crop-damage-survey-in-flood-hit-areas-mj18</t>
+          <t>https://www.etvbharat.com/mr/!state/sangli-crime-news-seven-month-pregnant-woman-self-killed-after-alleged-being-tortured-by-in-laws-for-religious-conversion-3-arrested-maharashtra-news-mhs25061200648</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/girls-free-education-in-maharashtra-special-scheme-for-other-fees-assurance-from-chandrakant-patil/articleshow/123376903.cms</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-politics-ajit-pawar-jayant-patil-rohit-pawar-clash-1471655.html</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/action-against-b-ed-colleges-as-per-the-rules-of-the-national-council-for-teacher-education-higher-and-technical/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-mns-raj-thackeray-uddhav-thackeray-alliance-eknath-shinde-politics-news-in-marathi-aajchya-thalak-batmya-monday-21-april-2025-1388817.html</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-mns-raj-thackeray-uddhav-thackeray-alliance-eknath-shinde-politics-news-in-marathi-aajchya-thalak-batmya-monday-21-april-2025-1388817.html</t>
+          <t>https://www.nagpurtoday.in/grand-recruitment-in-higher-education-sector-in-the-state-appointment-notice-for-8400-posts-for-professors-and-employees/07251413</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171768/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/indias-first-artificial-intelligence-university-in-maharashtra-order-for-constitution-of-committee-chandrakant-patil/articleshow/117637901.cms</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.eduvarta.com/Minister-Chandrakant-Patils-instructions-to-conduct-CET-again-for-BBA-BCA</t>
+          <t>https://marathi.indiatimes.com/career/career-news/dte-maharashtra-polytechnic-admissions-2025-deadline-extended-for-applications-until-june-26/articleshow/121889185.cms</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/bamu-s-big-decision-admissions-to-113-colleges-including-educational-institutions-of-chandrakant-patil-sule-munde/</t>
+          <t>https://www.punekarnews.in/chandrakant-patil-proposes-safety-measures-to-prevent-fires-on-punes-17-hills/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/chandrakant-patil-on-sanjaykaka-patil-and-ones-again-offer-to-vishal-patil-join-bjp/</t>
+          <t>https://www.mypunepulse.com/maharashtra-govt-unveils-new-grading-system-to-modernise-public-libraries/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-sant-puja-and-distribution-of-useful-materials-to-warkari-brothers-on-the-occasion-of-ashadhi-wari/</t>
+          <t>https://www.msn.com/mr-in/news/other/chandrakant-patil-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%95-%E0%A4%97%E0%A4%A6-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%AA%E0%A5%87%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B2-%E0%A4%AC%E0%A4%B8-%E0%A4%B5%E0%A4%82-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%B5-%E0%A4%B9%E0%A4%A8/ar-AA1L414d</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-no-matter-how-much-black-magic-someone-does-it-doesnt-matter-bjp-has-as-many-as-137-mlas-who-is-chandrakant-patal-targeting-so-the-indication-of-bawankules-to-fight-the-upco/</t>
+          <t>https://marathi.ndtv.com/maharashtra/carry-on-scheme-unfortunate-for-maharashtra-says-abvp-on-chandrakant-patil-decision-7648590</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/uddhav-thackerays-party-wants-to-join-the-government-chandrakant-patil-said/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/girls-free-education-in-maharashtra-special-scheme-for-other-fees-assurance-from-chandrakant-patil/articleshow/123376903.cms</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/sangli-or-review-the-arms-licenses-in-the-district-to-control-criminal-incidents-guardian-minister-chandrakant-patil/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-double-voting-allegations-chandrakant-patil-accuses-rohini-khadse-of-voting-twice-in-kothali-and-muktainagar-sparks-maharashtra-political-row-1379422</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/polytechnic-admissions-2025-or-extension-of-deadline-for-submission-of-applications-for-polytechnic-courses-instructions/</t>
+          <t>https://agrowon.esakal.com/agro-special/guardian-minister-orders-crop-damage-survey-in-flood-hit-areas-mj18</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/pune-or-heartbroken-to-hear-the-truth-about-the-attack-chandrakant-patil-consoles-ganbote-jagdale-families/</t>
+          <t>https://www.eduvarta.com/Minister-Chandrakant-Patils-instructions-to-conduct-CET-again-for-BBA-BCA</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://policenama.com/bajirao-peshwa-memorials-on-parvati-hill-development-work-of-bajirao-peshwa-memorial-on-parvati-hill-satisfactory-the-first-phase-will-be-inaugurated-by-union-minister-rajnath-singh-chandrakant-p/</t>
+          <t>https://policenama.com/chandrakant-patil-sant-puja-and-distribution-of-useful-materials-to-warkari-brothers-on-the-occasion-of-ashadhi-wari/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://news24pune.com/congress-suffers-setback-in-sangli-vasantdada-patils-granddaughter-jayashree-patil-joins-bjp/</t>
+          <t>https://civicmirror.in/news/bamu-s-big-decision-admissions-to-113-colleges-including-educational-institutions-of-chandrakant-patil-sule-munde/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/firata-davakhana-for-warkari-state-minister-chandrakant-patil-inaugurated-in-pune-article-152110556</t>
+          <t>https://civicmirror.in/news/chandrakant-patil-on-sanjaykaka-patil-and-ones-again-offer-to-vishal-patil-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.athawadavishesh.com/34215/</t>
+          <t>https://policenama.com/chandrakant-patil-no-matter-how-much-black-magic-someone-does-it-doesnt-matter-bjp-has-as-many-as-137-mlas-who-is-chandrakant-patal-targeting-so-the-indication-of-bawankules-to-fight-the-upco/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ajit-pawar-said-will-see-rohit-pawar-at-home/</t>
+          <t>https://policenama.com/chandrakant-patil-news-spontaneous-response-to-the-grain-festival-organized-by-minister-chandrakantdada-patil/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/big-recruitment-in-the-higher-education-department-of-maharashtra-5500-professors-and-2900-employees-will-be-recruited-article-152339600</t>
+          <t>https://policenama.com/chandrakant-patil-philosophy-of-thinking-positively-about-others-in-hindu-culture-chandrakantdada-patils-assertion/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/satara-news-disability-certificates-of-17-more-teachers-are-invalid/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/firata-davakhana-for-warkari-state-minister-chandrakant-patil-inaugurated-in-pune-article-152110556</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/trending/saw-smoke-in-the-eyewitness-at-ahmedabad-airport-describes-air-india-crash-101749727540094.html</t>
+          <t>https://civicmirror.in/news/sangli-or-review-the-arms-licenses-in-the-district-to-control-criminal-incidents-guardian-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-conduct-second-cet-colleges-worried-about-delay-in-academic-year-101749409146794.html</t>
+          <t>https://policenama.com/bajirao-peshwa-memorials-on-parvati-hill-development-work-of-bajirao-peshwa-memorial-on-parvati-hill-satisfactory-the-first-phase-will-be-inaugurated-by-union-minister-rajnath-singh-chandrakant-p/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-parties-battling-each-other-during-poaching-spree-101751053618819.html</t>
+          <t>https://maharashtradesha.com/uddhav-thackerays-party-wants-to-join-the-government-chandrakant-patil-said/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/powerloom-body-appeals-to-shun-trade-with-turkiye-azerbaijan/articleshow/121218402.cms</t>
+          <t>https://civicmirror.in/news/polytechnic-or-engineering-diploma-admission-application-registration-deadline-extended-new-schedule-announced-minister/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/chandrakant-patil-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%95-%E0%A4%97%E0%A4%A6-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%AA%E0%A5%87%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B2-%E0%A4%AC%E0%A4%B8-%E0%A4%B5%E0%A4%82-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%B5-%E0%A4%B9%E0%A4%A8/ar-AA1L414d</t>
+          <t>https://marathi.timesnownews.com/maharashtra/big-recruitment-in-the-higher-education-department-of-maharashtra-5500-professors-and-2900-employees-will-be-recruited-article-152339600</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/chandrakant-patil-instructions-to-professors-on-scholarship-implementation-in-colleges-8612913</t>
+          <t>https://www.dainikprabhat.com/satara-news-disability-certificates-of-17-more-teachers-are-invalid/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176171/</t>
+          <t>https://www.athawadavishesh.com/34215/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/solapur/solapur-jayakumar-gore-news-guardian-minister-jayakumar-gore-reaction-to-mla-ranjitsinh-mohite-patil-in-solapur-1361873</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/sangli-politics-congress-suffers-setback-pruthviraj-patil-joins-bjp-with-hundreds-of-supporters/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/education-free-for-female-students/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/police-bust-chain-snatching-gang-two-held-minor-detained-101740078106456.html</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-double-voting-allegations-chandrakant-patil-accuses-rohini-khadse-of-voting-twice-in-kothali-and-muktainagar-sparks-maharashtra-political-row-1379422</t>
+          <t>https://www.punekarnews.in/pune-chandrakant-patil-flags-pmc-misgovernance-amid-delayed-elections-high-level-meeting-with-ajit-pawar-likely/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/indias-first-artificial-intelligence-university-in-maharashtra-order-for-constitution-of-committee-chandrakant-patil/articleshow/117637901.cms</t>
+          <t>https://www.punekarnews.in/delay-in-punes-equal-water-supply-scheme-sparks-public-discontent-mla-chandrakant-patil-criticizes-pmc/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ravindra-dhangekar-allegation-chandrakant-patil-and-murlidhar-mohol-politics-for-gajanan-marne-arrested/854647/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-11-political-news-in-marathi-931306</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/gopichand-padalkar-embezzled-34-acres-of-land-of-oundh-devasthan-ram-khade-makes-serious-allegations-by-showing-documents-1350057</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-july-pune-rave-party-raj-thackeray-uddhav-thackeray-latest-news-mumbai-konkan-marathwada-weather-report-today-rain-updates-kolhapur-pandharpur-pmw-88-5267001/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-backs-abgi-vision-for-deemed-university-status-rds-00-5268767/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-state-government-halts-new-pharmacy-colleges-understand-the-reasons-behind-decreased-demand/articleshow/120842410.cms</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-news-spontaneous-response-to-the-grain-festival-organized-by-minister-chandrakantdada-patil/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-breaking-news-live-in-marathi-1-may-2025-maharashtra-din-kamgar-divas-pahalgam-attack-update-pm-modi-cm-devendra-fadnavis-mumbai-pune-latest-updates/liveblog/120781856.cms</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-philosophy-of-thinking-positively-about-others-in-hindu-culture-chandrakantdada-patils-assertion/</t>
+          <t>https://www.etvbharat.com/mr/!state/public-universities-recruitment-of-vacancies-in-non-colleges-will-be-accelerated-100-percent-recruitment-in-engineering-institutions-maharashtra-news-mhs25070802041</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/more-than-1101-couples-perform-collective-rudra-puja-in-pune-97635/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/neet-pg-counselling-2024-reduction-in-cut-off-percentile-medical-council-committee-5-percentile-student-qualify/articleshow/118624987.cms</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/maharashtra-abu-azmi-writes-letter-to-speaker-rahul-narwekar-to-revoke-his-suspension-over-statement-on-aurangzeb-latest-updates-2025-03-07-979620</t>
+          <t>https://civicmirror.in/news/pune-or-hadapsar-will-get-a-new-metro-line-connectivity-to-the-main-city-will-make-travel-faster/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-11-political-news-in-marathi-931306</t>
+          <t>https://marathi.indiatimes.com/career/career-news/thane-municipal-corporation-fir-against-68-unauthorized-schools-52-crore-fine/articleshow/118617204.cms</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-july-pune-rave-party-raj-thackeray-uddhav-thackeray-latest-news-mumbai-konkan-marathwada-weather-report-today-rain-updates-kolhapur-pandharpur-pmw-88-5267001/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/school-bus-rules-and-regulations-for-student-in-marathi-demand-to-charge-bus-fare-for-10-months-instead-of-12/articleshow/118546648.cms</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-state-government-halts-new-pharmacy-colleges-understand-the-reasons-behind-decreased-demand/articleshow/120842410.cms</t>
+          <t>https://civicmirror.in/news/loknete-laxman-jagtap-is-an-inspiring-chapter-higher-and-technical-education-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-breaking-news-live-in-marathi-1-may-2025-maharashtra-din-kamgar-divas-pahalgam-attack-update-pm-modi-cm-devendra-fadnavis-mumbai-pune-latest-updates/liveblog/120781856.cms</t>
+          <t>https://www.eduvarta.com/Approval-for-recruitment-of-5012-posts-in-the-Assistant-Professor-cadre</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158932/</t>
+          <t>https://newstown.in/samvidhan-gaurav-mahotsav-in-6-thousand-colleges-in-maharashtra-to-be-held-in-feburary-2025/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/kesari-father-in-law-has-been-lost-kesaribhau-patil-passes-away-maharashtra-news-mhs25021502516</t>
+          <t>https://marathi.abplive.com/news/sangli/mp-vishal-patil-sanjay-patil-and-prithviraj-patil-on-the-same-platform-in-sangli-marathi-news-udpate-1377401</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/farmer-loan-waiver-will-be-done-we-will-keep-your-word-assured-cm-devendra-fadnavis-in-pune-yoga-day-2025-maharashtra-news-mhs25062101753</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-be-btech-mba-mms-admission-2025-deadline-extended-till-july-14-final-chance/articleshow/122391899.cms</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-10th-board-exam-result-2025-ssc-hsc-board-nashik-divisional-office-work-of-668-schools-pending/articleshow/118621538.cms</t>
+          <t>https://marathi.latestly.com/socially/maharashtra/ramabai-ambedkar-punyatithi-2025-ajit-pawar-to-prakash-ambedkar-pays-tribute-to-ramai-on-her-death-anniversary-590799.html</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/neet-pg-counselling-2024-reduction-in-cut-off-percentile-medical-council-committee-5-percentile-student-qualify/articleshow/118624987.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-may-halt-admissions-to-pharmacy-colleges-flouting-norms-101753902851567.html</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/notification-regarding-the-conduction-of-additional-cet-for-bca-bba-bms-bbm-cet-2025-state-common-entrance-test-cell/articleshow/121692037.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-approves-long-pending-faculty-recruitment-for-state-universities-colleges-101751916450665.html</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/school-bus-rules-and-regulations-for-student-in-marathi-demand-to-charge-bus-fare-for-10-months-instead-of-12/articleshow/118546648.cms</t>
+          <t>https://www.amarujala.com/india-news/mere-speculation-chandrakant-patil-on-rumours-about-likely-merger-of-ncp-factions-news-in-hindi-2025-05-14</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/polytechnic-or-engineering-diploma-admission-application-registration-deadline-extended-new-schedule-announced-minister/</t>
+          <t>https://www.livehindustan.com/maharashtra/uddhav-in-shinde-out-bjp-is-cooking-up-a-new-plan-in-maharashtra-chandrakant-patil-met-uddhav-201738301481336.html</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/loknete-laxman-jagtap-is-an-inspiring-chapter-higher-and-technical-education-minister-chandrakant-patil/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-17-july-maharashtra-assembly-monsoon-session-2025-devendra-fadnavis-on-tri-bhasha-sutra-ola-uber-rickshaw-taxis-closed-rak-94-5234478/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.eduvarta.com/Approval-for-recruitment-of-5012-posts-in-the-Assistant-Professor-cadre</t>
+          <t>https://marathi.ndtv.com/politics/effectively-implement-the-free-higher-education-scheme-for-girls-orders-chandrakant-patil-8702210</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://policenama.com/mkcl-devendra-fadnavis-mkcls-silver-jubilee-foundation-day-celebrated-with-excitement-mkcls-success-in-democratizing-the-information-technology-revolution-devendra-fadnavis/</t>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-hindi-imposition-protest-uddhav-thackeray-and-raj-thackeray-unite-massive-rally-against-mama-chandrakant-vaidya-reaction-1432755.html</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/pune-or-hadapsar-will-get-a-new-metro-line-connectivity-to-the-main-city-will-make-travel-faster/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/water-storage-in-seven-dams-supplying-water-to-mumbai-reaches-50-percent/articleshow/122265724.cms</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-top-100-headlines-14-april-2025-marathi-headlines-maharashtra-chandrakant-patil-on-sanjay-raut-1354271</t>
+          <t>https://civicmirror.in/news/uddhav-thackeray-has-accepted-the-hindi-mandatory-policy-in-the-state-reveals-minister-uday-samant/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-be-btech-mba-mms-admission-2025-deadline-extended-till-july-14-final-chance/articleshow/122391899.cms</t>
+          <t>https://civicmirror.in/news/hindi-is-being-forced-to-end-marathi-language-and-culture-we-will-defeat-this-agenda-of-bjp-and-rss-harshvardhan-sapkal/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-approves-long-pending-faculty-recruitment-for-state-universities-colleges-101751916450665.html</t>
+          <t>https://civicmirror.in/news/raj-thackeray-announces-grand-march-against-hindi-compulsion/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/maharashtra-cites-poor-standards-proposes-no-new-pharmacy-colleges-for-5-years-101750656728006.html</t>
+          <t>https://www.dainikprabhat.com/pune-news-pune-festival-to-begin-on-august-29-inauguration-by-governor/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/uddhav-in-shinde-out-bjp-is-cooking-up-a-new-plan-in-maharashtra-chandrakant-patil-met-uddhav-201738301481336.html</t>
+          <t>https://zeenews.india.com/india/maharashtra-politics-did-bjp-minister-just-confirm-rift-within-mahayuti-shindes-meeting-with-shah-2886410.html</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/maharashtra-govt-approves-100-recruitment-in-engineering-colleges-boosts-higher-education-quality/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/ahilyadevi-holkar-s-legacy-must-be-known-to-youth-cm-101748631369699.html</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-17-july-maharashtra-assembly-monsoon-session-2025-devendra-fadnavis-on-tri-bhasha-sutra-ola-uber-rickshaw-taxis-closed-rak-94-5234478/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-seek-restoration-of-savarkar-s-barrister-degree-101748373138133.html</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/water-storage-in-seven-dams-supplying-water-to-mumbai-reaches-50-percent/articleshow/122265724.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/pregnant-womans-dad-accuses-spouse-kin-of-harassment/articleshow/121809105.cms</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/uddhav-thackeray-has-accepted-the-hindi-mandatory-policy-in-the-state-reveals-minister-uday-samant/</t>
+          <t>https://timesofindia.indiatimes.com/education/news/maharashtra-launches-atal-portal-for-entrance-prep-and-career-guidance/articleshow/117296155.cms</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/hindi-is-being-forced-to-end-marathi-language-and-culture-we-will-defeat-this-agenda-of-bjp-and-rss-harshvardhan-sapkal/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/days-before-hsc-exam-70-students-get-hall-tickets-with-wrong-subjects/articleshow/118097108.cms</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/raj-thackeray-announces-grand-march-against-hindi-compulsion/</t>
+          <t>https://www.newsonair.gov.in/india-emerging-as-global-knowledge-partner-dharmendra-pradhan/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/jayant-patil-emotional-letter-to-maharashtra-marathi/</t>
+          <t>https://mahasamvad.in/163883/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-pune-festival-to-begin-on-august-29-inauguration-by-governor/</t>
+          <t>https://civicmirror.in/maharashtra/mht-cet-exam-2025-or-technical-glitch-in-mht-cet-2025-pcm-group-exam-re-exam-on-may-5th/cid1746067306.htm</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/trending/dead-bodies-debris-eyewitness-recalls-hearing-massive-sound-during-air-india-plane-crash-101749723280168.html</t>
+          <t>https://marathi.timesnownews.com/maharashtra/mht-cet-2025-reexam-announces-for-pcm-on-may-5-due-to-errors-in-21-questions-read-details-in-marathi-article-151540811</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/pregnant-womans-dad-accuses-spouse-kin-of-harassment/articleshow/121809105.cms</t>
+          <t>https://civicmirror.in/news/rte-news-preparations-to-boycott-private-english-medium-school-admission-process-due-to-this-reason/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-seek-restoration-of-savarkar-s-barrister-degree-101748373138133.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/patankar-and-patil-join-bjp-as-strong-rivals-of-sitting-sena-mlas/articleshow/121762155.cms</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/aftermath-of-baby-kidnap-sangli-guardian-minister-chandrakant-patil-announces-enhanced-security-measures-at-miraj-govt-hospital/articleshow/121006495.cms</t>
+          <t>https://timesofindia.indiatimes.com/india/bjp-mantris-remark-sparks-buzz-of-patch-up-with-shiv-sena-ubt/articleshow/117754765.cms</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/education/news/maharashtra-launches-atal-portal-for-entrance-prep-and-career-guidance/articleshow/117296155.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-mlc-first-to-record-statement-in-cm-s-sit-probe-101740079847054.html</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/days-before-hsc-exam-70-students-get-hall-tickets-with-wrong-subjects/articleshow/118097108.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/bjp-leaders-conduct-back-to-back-separate-review-meetings-at-pmc-oppn-questions-lack-of-results-101751143694920.html</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/india-emerging-as-global-knowledge-partner-dharmendra-pradhan/</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>https://news.careers360.com/mht-cet-pcm-re-test-2025-may-5-for-27837-english-urdu-marathi-21-maths-questions-go-wrong-paper-setters-blacklisted</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>https://www.punekarnews.in/millennium-national-school-shines-at-invitational-taekwondo-inter-school-competition/</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/career/career-news/mht-cet-2025-pcm-group-re-exam-on-may-5-exam-canceled-due-to-technical-errors-conducted-on-27-april/articleshow/120769046.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/news/rte-news-preparations-to-boycott-private-english-medium-school-admission-process-due-to-this-reason/</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>https://marathi.timesnownews.com/maharashtra/mht-cet-2025-reexam-announces-for-pcm-on-may-5-due-to-errors-in-21-questions-read-details-in-marathi-article-151540811</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/mht-cet-exam-2025-or-technical-glitch-in-mht-cet-2025-pcm-group-exam-re-exam-on-may-5th/cid1746067306.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/patankar-and-patil-join-bjp-as-strong-rivals-of-sitting-sena-mlas/articleshow/121762155.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/former-cm-vasantdada-patils-granddaughter-in-law-joins-bjp/articleshow/121893459.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/congress-sangli-city-prez-prithviraj-patil-to-join-bjp/articleshow/123265799.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>https://www.indiatoday.in/india/story/sanjay-raut-bjp-shiv-sena-ubt-alliance-maharashtra-mahayuti-mva-devendra-fadnavis-2672702-2025-01-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-mlc-first-to-record-statement-in-cm-s-sit-probe-101740079847054.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/bjp-leaders-conduct-back-to-back-separate-review-meetings-at-pmc-oppn-questions-lack-of-results-101751143694920.html</t>
+          <t>https://www.tarunbharat.com/prithviraj-patil-avoided-joining-the-bjp/</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A226"/>
+  <dimension ref="A1:A238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,7 +480,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/sangli-guardian-minister-chandrakant-patil-calls-upon-former-bjp-mp-sanjaykaka-patil-urges-him-to-return-to-bjp/articleshow/119609029.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/outright-kunbi-status-to-will-not-stand-legal-test-chandrakant-patil/articleshow/123487443.cms</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/movie-phule-depicts-discrimination-of-bygone-era-no-need-to-oppose-it-chandrakant-patil/articleshow/120288218.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/sangli-guardian-minister-chandrakant-patil-calls-upon-former-bjp-mp-sanjaykaka-patil-urges-him-to-return-to-bjp/articleshow/119609029.cms</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/after-kulkarni-s-criticism-mohol-and-chandrakant-patil-come-out-in-support-of-bjp-workers-101744225445616.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/movie-phule-depicts-discrimination-of-bygone-era-no-need-to-oppose-it-chandrakant-patil/articleshow/120288218.cms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/1000-new-personnel-to-join-pune-police-force-chandrakant-patil-101751829456309.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/after-kulkarni-s-criticism-mohol-and-chandrakant-patil-come-out-in-support-of-bjp-workers-101744225445616.html</t>
         </is>
       </c>
     </row>
@@ -529,35 +529,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/vishal-patil-turns-down-bjp-ministers-offer-to-join-alliance/articleshow/119084771.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/100-per-cent-fee-waiver-for-ews-girls-chandrakant-patil-101750360390574.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/100-per-cent-fee-waiver-for-ews-girls-chandrakant-patil-101750360390574.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/vishal-patil-turns-down-bjp-ministers-offer-to-join-alliance/articleshow/119084771.cms</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/outright-kunbi-status-to-will-not-stand-legal-test-chandrakant-patil/articleshow/123487443.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-of-different-backgrounds-are-bound-to-disagree-in-coalition-govt-chandrakant-patil-23519840</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-of-different-backgrounds-are-bound-to-disagree-in-coalition-govt-chandrakant-patil-23519840</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-tells-officials-to-expedite-land-acquisition-for-roads-in-kothrud-101745865957490.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-tells-officials-to-expedite-land-acquisition-for-roads-in-kothrud-101745865957490.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/engg-admission-soon-four-caps-and-seat-confirmation-by-round-3/articleshow/121657513.cms</t>
         </is>
       </c>
     </row>
@@ -592,28 +592,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/former-cm-vasantdada-patils-granddaughter-in-law-joins-bjp/articleshow/121893459.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/if-some-leader-leaves-not-necessarily-people-join-him-vishwajeet-kadam/articleshow/123289946.cms</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/trending/saw-smoke-in-the-eyewitness-at-ahmedabad-airport-describes-air-india-crash-101749727540094.html</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/fadnavis-will-seek-dhananjay-mundes-resignation-if-he-is-linked-to-beed-sarpanch-murder-bjps-chandrakant-pati/article69146499.ece</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/if-some-leader-leaves-not-necessarily-people-join-him-vishwajeet-kadam/articleshow/123289946.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/former-cm-vasantdada-patils-granddaughter-in-law-joins-bjp/articleshow/121893459.cms</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/rss-holds-two-day-brainstorming-session-with-bjp-allied-outfits-3362607</t>
+          <t>https://www.hindustantimes.com/trending/saw-smoke-in-the-eyewitness-at-ahmedabad-airport-describes-air-india-crash-101749727540094.html</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/states-tech-edu-minister-reviews-fee-waiver-for-women-students/articleshow/118310028.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/patankar-and-patil-join-bjp-as-strong-rivals-of-sitting-sena-mlas/articleshow/121762155.cms</t>
         </is>
       </c>
     </row>
@@ -648,1363 +648,1447 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/dpdc-meeting-on-thursday-101738176153028.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/states-tech-edu-minister-reviews-fee-waiver-for-women-students/articleshow/118310028.cms</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/sub-centre-of-sppu-slated-to-be-inaugurated-by-may-end-in-nashiks-shivnai-area-chandrakant-patil-instructs-officials-to-expedite-facility/articleshow/121036464.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/dpdc-meeting-on-thursday-101738176153028.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-asks-pmc-to-acquire-land-on-priority-as-balewadi-wakad-bridge-lies-unused-101751741109744.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/sub-centre-of-sppu-slated-to-be-inaugurated-by-may-end-in-nashiks-shivnai-area-chandrakant-patil-instructs-officials-to-expedite-facility/articleshow/121036464.cms</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/no-cet-outside-maharashtra-minister-101749151005604.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-asks-pmc-to-acquire-land-on-priority-as-balewadi-wakad-bridge-lies-unused-101751741109744.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-conduct-second-cet-colleges-worried-about-delay-in-academic-year-101749409146794.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/no-cet-outside-maharashtra-minister-101749151005604.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/def-min-likely-to-inaugurate-peshwa-memorial-at-parvati-101736539722952.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-conduct-second-cet-colleges-worried-about-delay-in-academic-year-101749409146794.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-parties-battling-each-other-during-poaching-spree-101751053618819.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/azmi-is-suspended-yogi-says-send-him-to-up-for-treatment/articleshow/118742113.cms</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ahead-of-jarange-stir-in-mumbai-cabinet-sub-committee-on-maratha-quota-reconstituted-vikhe-patil-now-new-head/articleshow/123460725.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/def-min-likely-to-inaugurate-peshwa-memorial-at-parvati-101736539722952.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-deputy-chief-minister-ajit-pawar-vows-swift-action-to-restore-obc-quota/articleshow/120525973.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-parties-battling-each-other-during-poaching-spree-101751053618819.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-silent-on-bavdhan-garbage-plant-issue-in-pmc-meeting-101745953467654.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-deputy-chief-minister-ajit-pawar-vows-swift-action-to-restore-obc-quota/articleshow/120525973.cms</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra:-cabinet-sub-committee-on-maratha-quota-reconstituted;-vikhe-patil-new-head/2847184</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-silent-on-bavdhan-garbage-plant-issue-in-pmc-meeting-101745953467654.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-adds-fourth-cap-round-for-engineering-admissions-to-curb-costly-pvt-options-101749150825079.html</t>
+          <t>https://www.ptinews.com/story/national/maharashtra:-cabinet-sub-committee-on-maratha-quota-reconstituted;-vikhe-patil-new-head/2847184</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/state-committed-to-opposing-almatti-height-rise-says-minister-vikhe-patil/articleshow/118652829.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-adds-fourth-cap-round-for-engineering-admissions-to-curb-costly-pvt-options-101749150825079.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/protesters-oppose-name-expansion-proposal-of-shivaji-university-in-kolhapur/articleshow/119544233.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ahead-of-jarange-stir-in-mumbai-cabinet-sub-committee-on-maratha-quota-reconstituted-vikhe-patil-now-new-head/articleshow/123460725.cms</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-government-plans-to-grant-university-status-to-jbims-101743881532444.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-announces-new-recruitment-process-for-university-teachers-101740684012522.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/islampur-to-be-renamed-ishwarpur-101752864742122.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/protesters-oppose-name-expansion-proposal-of-shivaji-university-in-kolhapur/articleshow/119544233.cms</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/06/06/maharashtra-introduces-new-rule-stops-cet-exams-at-centres-outside-the-state/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/state-committed-to-opposing-almatti-height-rise-says-minister-vikhe-patil/articleshow/118652829.cms</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://education.economictimes.indiatimes.com/news/higher-education/marathwada-varsity-stops-pg-admissions-in-113-colleges-after-irregularities-come-to-fore/122912620</t>
+          <t>https://theprint.in/india/cet-for-courses-in-maharashtra-not-to-be-held-outside-state-to-prevent-malpractices-minister/2649554/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/cet-for-courses-in-maharashtra-not-be-held-outside-state-prevent-malpractices-minister-chandrakant-patil</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-government-plans-to-grant-university-status-to-jbims-101743881532444.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-fee-hike-all-engineering-medical-professional-colleges-fra-charge-3x-fees-for-management-5x-nri-quota-seats</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/islampur-to-be-renamed-ishwarpur-101752864742122.html</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/mht-cet-2025-cap-counselling-expanded-four-rounds-new-rule-round-1-btech-mbbs-pharmacy-admissions-whats-changed</t>
+          <t>https://thelivenagpur.com/2025/06/06/maharashtra-introduces-new-rule-stops-cet-exams-at-centres-outside-the-state/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-university-faculty-recruitment-resume-new-evaluation-rules-academics-research-teaching-interview</t>
+          <t>https://www.businesstoday.in/india/story/many-in-bjp-want-alliance-with-uddhav-thackeray-sena-ubts-sanjay-raut-stirs-speculation-462645-2025-01-30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-state-cet-cell-launches-cet-atal-module-for-mock-tests</t>
+          <t>https://punemirror.com/city/civic/chandrakant-patil-takes-action-on-kothrud-s-road-water-and-traffic-issues/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-news-chandrakant-patil-urges-citizens-to-stay-vigilant/</t>
+          <t>https://education.economictimes.indiatimes.com/news/higher-education/marathwada-varsity-stops-pg-admissions-in-113-colleges-after-irregularities-come-to-fore/122912620</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-major-announcement-for-girls-education-minister-chandrakant-patil-to-inspect-100-colleges-review-fee-waiver-implementation/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2126625</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/chandrakant-patil-reveals-details-of-vidhan-bhavan-meetings-on-pune-municipal-corporation-budget/</t>
+          <t>https://news.careers360.com/cet-for-courses-in-maharashtra-not-be-held-outside-state-prevent-malpractices-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/traffic-congestion-free-kothrud-minister-chandrakant-patil-pushes-for-ai-based-challan-system/</t>
+          <t>https://news.careers360.com/maharashtra-fee-hike-all-engineering-medical-professional-colleges-fra-charge-3x-fees-for-management-5x-nri-quota-seats</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/ensure-safety-measures-for-pune-hills-higher-and-technical-education-minister-chandrakant-patils-directives/</t>
+          <t>https://news.careers360.com/mht-cet-2025-cap-counselling-expanded-four-rounds-new-rule-round-1-btech-mbbs-pharmacy-admissions-whats-changed</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-chandrakant-patil-warns-pmc-shut-down-sus-waste-project-or-face-protest/</t>
+          <t>https://news.careers360.com/maharashtra-state-cet-cell-launches-cet-atal-module-for-mock-tests</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-chandrakant-patil-demands-swift-action-on-citys-missing-road-link-projects/</t>
+          <t>https://www.mypunepulse.com/pune-major-announcement-for-girls-education-minister-chandrakant-patil-to-inspect-100-colleges-review-fee-waiver-implementation/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/global-ganesh-festival-2025-eknath-shinde-to-lead-chandrakant-patil-as-chief-receptionist/</t>
+          <t>https://www.mypunepulse.com/traffic-congestion-free-kothrud-minister-chandrakant-patil-pushes-for-ai-based-challan-system/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/minister-chandrakant-patil-orders-comprehensive-report-on-challenges-faced-by-educational-institutions-in-maharashtra/</t>
+          <t>https://www.mypunepulse.com/ensure-safety-measures-for-pune-hills-higher-and-technical-education-minister-chandrakant-patils-directives/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-chandrakant-patil-orders-immediate-measures-to-resolve-baner-balewadi-traffic-woes/</t>
+          <t>https://www.mypunepulse.com/pune-chandrakant-patil-warns-pmc-shut-down-sus-waste-project-or-face-protest/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-high-level-meeting-held-to-resolve-baner-balewadi-traffic-woes-minister-chandrakant-patil-orders-immediate-action/</t>
+          <t>https://www.mypunepulse.com/pune-chandrakant-patil-demands-swift-action-on-citys-missing-road-link-projects/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/1000-new-cops-to-join-pune-police-force-as-city-expands-chandrakant-patil/</t>
+          <t>https://www.punekarnews.in/global-ganesh-festival-2025-eknath-shinde-to-lead-chandrakant-patil-as-chief-receptionist/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/cet-exams-to-be-held-only-within-maharashtra/</t>
+          <t>https://www.punekarnews.in/chandrakant-patil-proposes-safety-measures-to-prevent-fires-on-punes-17-hills/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/maharashtra-government-implements-new-transparent-recruitment-process-for-university-faculty/</t>
+          <t>https://www.punekarnews.in/minister-chandrakant-patil-orders-comprehensive-report-on-challenges-faced-by-educational-institutions-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/maharashtra-govt-approves-100-recruitment-in-engineering-colleges-boosts-higher-education-quality/</t>
+          <t>https://www.punekarnews.in/pune-high-level-meeting-held-to-resolve-baner-balewadi-traffic-woes-minister-chandrakant-patil-orders-immediate-action/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-hosts-grand-warkari-bhaktiyog-2025-on-international-yoga-day/</t>
+          <t>https://www.punekarnews.in/1000-new-cops-to-join-pune-police-force-as-city-expands-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://affairscloud.com/union-minister-of-jal-shakti-cr-patil-reviewed-key-projects-of-wii-under-nmcg/</t>
+          <t>https://www.punekarnews.in/maharashtra-government-implements-new-transparent-recruitment-process-for-university-faculty/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.hindustanmetro.com/mr-sunjjoy-chaudhri-leads-team-veer-santaji-at-khasdar-celebrity-cricket-league-2025-celebrating-punes-grand-festival-with-support-from-mr-murlidhar-mohol-and-mr-chandrakant-patil/</t>
+          <t>https://www.punekarnews.in/pune-hosts-grand-warkari-bhaktiyog-2025-on-international-yoga-day/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-minister-orders-compulsory-land-acquisition-to-open-balewadi-wakad-mula-river-bridge/</t>
+          <t>https://affairscloud.com/union-minister-of-jal-shakti-cr-patil-reviewed-key-projects-of-wii-under-nmcg/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.hindustanmetro.com/maharashtra-state-cet-cell-launches-visionary-initiative-cet-atal-module-for-mock-tests/</t>
+          <t>https://www.hindustanmetro.com/mr-sunjjoy-chaudhri-leads-team-veer-santaji-at-khasdar-celebrity-cricket-league-2025-celebrating-punes-grand-festival-with-support-from-mr-murlidhar-mohol-and-mr-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171311/</t>
+          <t>https://www.punekarnews.in/pune-minister-orders-compulsory-land-acquisition-to-open-balewadi-wakad-mula-river-bridge/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/raksha-khadse-daughter-harassed-reaction-of-mla-chandrakant-patil-1359186.html</t>
+          <t>https://www.hindustanmetro.com/maharashtra-state-cet-cell-launches-visionary-initiative-cet-atal-module-for-mock-tests/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-milind-narvekar-and-chandrakant-patil-meet-at-parag-alavani-daughter-wedding-and-discussion-on-yuti-impact-on-maharashtra-politics-1341419</t>
+          <t>https://marathi.abplive.com/news/sangli/minister-chandrakant-patil-offers-to-join-bjp-to-independent-mp-vishal-patil-after-get-offer-vishal-patil-said-if-i-am-getting-an-offer-of-joining-party-i-think-i-am-doing-a-good-job-1349507</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/jalgaon-chandrakant-patil-shiv-sena-on-raksha-khadse-daughter-devendra-fadanvis-marathi-news-abp-majha-1347066</t>
+          <t>https://mahasamvad.in/171311/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176328/</t>
+          <t>https://marathi.abplive.com/news/chandrakant-patil-criticizes-on-uddhav-thackeray-said-raj-thackeray-is-political-convenience-for-mumbai-municipal-corporation-maharashtra-politics-marathi-news-1368293</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173280/</t>
+          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-milind-narvekar-and-chandrakant-patil-meet-at-parag-alavani-daughter-wedding-and-discussion-on-yuti-impact-on-maharashtra-politics-1341419</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/extension-of-the-deadline-for-admission-registration-conducted-by-cet-cell-information-from-minister-chandrakant-patil-1368834</t>
+          <t>https://marathi.abplive.com/videos/news/jalgaon-chandrakant-patil-shiv-sena-on-raksha-khadse-daughter-devendra-fadanvis-marathi-news-abp-majha-1347066</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/eknath-khadse-vs-chandrakant-patil-how-did-34-acres-of-land-become-100-acres-eknath-khadse-response-to-chandrakant-patil-allegations-jalgaon-maharashtra-politics-marathi-news-1362993</t>
+          <t>https://marathi.abplive.com/news/minister-chandrakant-patil-suggestion-after-pratibimb-foundation-take-a-big-step-for-the-career-of-journalists-sons-and-daughters-along-with-health-of-their-families-maharashtra-marathi-news-1355102</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176819/</t>
+          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-statement-on-jayant-patil-ncp-sharad-pawar-leader-sangli-politics-marathi-news-1371392</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176831/</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-have-137-mlas-black-magic-will-do-nothing-maharashtra-government-will-run-for-5-years-says-chandrakant-patil-at-kolhapur-1344696</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176833/</t>
+          <t>https://mahasamvad.in/176328/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169332/</t>
+          <t>https://mahasamvad.in/173280/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sanjay-raut-reaction-on-chandrakant-patil-statement-of-shivsena-bjp-alliance-will-be-golden-moment-sgk-96-4858543/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/extension-of-the-deadline-for-admission-registration-conducted-by-cet-cell-information-from-minister-chandrakant-patil-1368834</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172941/</t>
+          <t>https://mahasamvad.in/176819/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173478/</t>
+          <t>https://mahasamvad.in/176831/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174837/</t>
+          <t>https://marathi.abplive.com/news/politics/eknath-khadse-vs-chandrakant-patil-how-did-34-acres-of-land-become-100-acres-eknath-khadse-response-to-chandrakant-patil-allegations-jalgaon-maharashtra-politics-marathi-news-1362993</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163743/</t>
+          <t>https://mahasamvad.in/169332/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175756/</t>
+          <t>https://mahasamvad.in/172941/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176171/</t>
+          <t>https://marathi.abplive.com/news/sangli/will-ajit-pawar-chandrakant-patil-jayant-patil-rohit-pawar-come-on-the-same-platform-in-sangli-for-saroj-patil-function-1377194</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/shivaji-university-s-sub-centre-in-khanapur-says-chandrakant-patil-zws-70-4960985/</t>
+          <t>https://mahasamvad.in/173478/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173059/</t>
+          <t>https://mahasamvad.in/174837/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176754/</t>
+          <t>https://mahasamvad.in/163743/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/pune-news-chandrakant-patil-slams-raj-thackeray-uddhav-thackeray-on-hindi-language-controvery-8785417</t>
+          <t>https://mahasamvad.in/175756/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163261/</t>
+          <t>https://marathi.abplive.com/education/college-admission-for-engineers-from-june-28-extension-for-diploma-till-june-30-minister-chandrakant-patil-decision-1366417</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160007/</t>
+          <t>https://mahasamvad.in/176833/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169326/</t>
+          <t>https://mahasamvad.in/176171/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/169422/</t>
+          <t>https://marathi.abplive.com/news/politics/why-does-bjp-still-like-other-people-children-raju-shetti-scathing-criticism-of-chandrakant-patil-offer-to-vishal-patil-1349730</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175217/</t>
+          <t>https://mahasamvad.in/176754/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161166/</t>
+          <t>https://marathi.ndtv.com/maharashtra/pune-news-chandrakant-patil-slams-raj-thackeray-uddhav-thackeray-on-hindi-language-controvery-8785417</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/minister-chandrakant-patil-new-responsibility-of-professors-for-students-instructions-for-effective-implementation-of-college-schemes/articleshow/121717827.cms</t>
+          <t>https://mahasamvad.in/160007/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174729/</t>
+          <t>https://mahasamvad.in/163261/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160626/</t>
+          <t>https://mahasamvad.in/169326/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-leader-minister-chandrakant-patil-big-statement-regarding-ministerial-post-at-sangli-1390006.html</t>
+          <t>https://mahasamvad.in/175217/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/minister-chandrakant-patil-and-farmers-dispute-broke-out-between-in-sangli/articleshow/120792863.cms</t>
+          <t>https://mahasamvad.in/173059/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173128/</t>
+          <t>https://www.loksatta.com/maharashtra/guardian-minister-chandrakant-patil-reacted-to-jayant-patil-while-interacting-with-the-media-phm-00-5244552/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173013/</t>
+          <t>https://mahasamvad.in/161166/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/sangli-news-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%8F%E0%A4%95-%E0%A4%9A-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%AA-%E0%A4%A0-%E0%A4%B5%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A4%97-%E0%A4%A8-%E0%A4%AE-%E0%A4%88-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A0%E0%A4%B0%E0%A4%A3-%E0%A4%B0/ar-AA1KyMam</t>
+          <t>https://marathi.indiatimes.com/career/career-news/minister-chandrakant-patil-new-responsibility-of-professors-for-students-instructions-for-effective-implementation-of-college-schemes/articleshow/121717827.cms</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172372/</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-leader-chandrkant-patil-on-dhananjay-munde-resignation-and-walmik-karad-connection-on-beed-massajog-santosh-deshmukh-case-1340832</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/164366/</t>
+          <t>https://www.tv9marathi.com/videos/bjp-leader-minister-chandrakant-patil-big-statement-regarding-ministerial-post-at-sangli-1390006.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170382/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/minister-chandrakant-patil-and-farmers-dispute-broke-out-between-in-sangli/articleshow/120792863.cms</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-on-rohini-khadse-jalgaon-news-mla-chandrakant-patil-criticizes-rohini-khadse-1379392</t>
+          <t>https://mahasamvad.in/174729/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176760/</t>
+          <t>https://mahasamvad.in/173128/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/engineering-admission-process-revision-four-cap-rounds-says-chandrakant-patil-mumbai-print-news-zws-70-5137735/</t>
+          <t>https://marathi.ndtv.com/politics/effectively-implement-the-free-higher-education-scheme-for-girls-orders-chandrakant-patil-8702210</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/162964/</t>
+          <t>https://mahasamvad.in/173013/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161614/</t>
+          <t>https://mahasamvad.in/160626/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158873/</t>
+          <t>https://www.msn.com/mr-in/news/other/sangli-news-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%8F%E0%A4%95-%E0%A4%9A-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%AA-%E0%A4%A0-%E0%A4%B5%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A4%97-%E0%A4%A8-%E0%A4%AE-%E0%A4%88-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A0%E0%A4%B0%E0%A4%A3-%E0%A4%B0/ar-AA1KyMam</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173469/</t>
+          <t>https://mahasamvad.in/164366/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/recruitment-of-4435-posts-of-assistant-professors-soon-information-from-higher-and-technical-education-minister-chandrakant-patil/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-on-rohini-khadse-jalgaon-news-mla-chandrakant-patil-criticizes-rohini-khadse-1379392</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/chandrakant-patil-slams-uddhav-thackeray-1439709.html</t>
+          <t>https://mahasamvad.in/172372/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157924/</t>
+          <t>https://mahasamvad.in/170382/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174461/</t>
+          <t>https://mahasamvad.in/176760/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/rohit-pawar-praised-chandrakant-patil-and-taunts-gopichand-padalkar-know-what-he-said-1470906.html</t>
+          <t>https://mahasamvad.in/168333/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/ndtv-marathi-emerging-business-conclave-chandrakant-patil-rupali-chakankar-on-pune-traffic-rain-issue-8786115</t>
+          <t>https://marathi.ndtv.com/politics/minister-and-bjp-leader-chandrakant-patil-offered-sangli-mp-vishal-patil-to-join-bjp-7935097</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175300/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/chandrakant-patil-and-farmers-came-face-to-face-over-shaktipith-highway/903727</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/chandrakant-patil-instructions-to-professors-on-scholarship-implementation-in-colleges-8612913</t>
+          <t>https://mahasamvad.in/162964/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-chandrakant-patil-suggestion-to-mns-raj-thackeray-over-hindi-compulsory-in-maharashtra-school-1429353.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/carry-on-scheme-unfortunate-for-maharashtra-says-abvp-on-chandrakant-patil-decision-7648590</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-bharti-new-procedure-announced-for-selection-process-minister-chandrakant-patil/articleshow/118607489.cms</t>
+          <t>https://mahasamvad.in/173469/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160732/</t>
+          <t>https://mahasamvad.in/161614/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/162538/</t>
+          <t>https://mahasamvad.in/158873/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-recruitment-2025-college-teachers-bharti-education-minister-chandrakant-patil/articleshow/118924405.cms</t>
+          <t>https://marathi.abplive.com/education/polytechnic-admission-start-from-20-may-and-visit-the-website-for-online-process-chandrakant-patil-appeals-1359951</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/jayshree-patil-to-join-bjp-presence-chief-minister-devendra-fadnavis/articleshow/121881414.cms</t>
+          <t>https://deshdoot.com/recruitment-of-4435-posts-of-assistant-professors-soon-information-from-higher-and-technical-education-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/medha-kulkarni-left-bjp-meeting-midway-as-chandrakant-patil-murlidhar-mohol-backs-deenanath-mangeshkar-case-andolan/articleshow/120120230.cms</t>
+          <t>https://mahasamvad.in/157924/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/marathi/live/c3e4qkvvdkvt?page=2</t>
+          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-on-shaktipeeth-expressway-nagpur-goa-highway-claim-some-forces-working-to-disturb-maharashtra-marathi-1377295</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/solapur/solapur-jayakumar-gore-news-guardian-minister-jayakumar-gore-reaction-to-mla-ranjitsinh-mohite-patil-in-solapur-1361873</t>
+          <t>https://marathi.ndtv.com/maharashtra/ndtv-marathi-emerging-business-conclave-chandrakant-patil-rupali-chakankar-on-pune-traffic-rain-issue-8786115</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/education-free-for-female-students/</t>
+          <t>https://mahasamvad.in/174461/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-digital-media-social-work-honoured-in-pune-ikshan-pratishthan-for-the-children-of-journalists-ceremony-in-the-presence-of-chandrakant-patil-1360276</t>
+          <t>https://marathi.ndtv.com/maharashtra/chandrakant-patil-instructions-to-professors-on-scholarship-implementation-in-colleges-8612913</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/153348/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-bharti-new-procedure-announced-for-selection-process-minister-chandrakant-patil/articleshow/118607489.cms</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-government-made-changes-in-maratha-reservation-sub-committee-rahadhakrishna-vikhe-patil-will-ne-president-1379124</t>
+          <t>https://mahasamvad.in/175300/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/girl-free-education-scheme-in-maharashtra-latest-news-chandrakant-patil-mulina-mofat-shikshan-yojana-maharashtra-2024/articleshow/118265312.cms</t>
+          <t>https://mahasamvad.in/160732/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/pune-or-heartbroken-to-hear-the-truth-about-the-attack-chandrakant-patil-consoles-ganbote-jagdale-families/</t>
+          <t>https://mahasamvad.in/162538/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/chandrakant-atial-discussion-with-flood-situated-people-sangli-walwa-marathi-news/</t>
+          <t>https://civicmirror.in/news/sangli-or-review-the-arms-licenses-in-the-district-to-control-criminal-incidents-guardian-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/polytechnic-admissions-2025-or-extension-of-deadline-for-submission-of-applications-for-polytechnic-courses-instructions/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-recruitment-2025-college-teachers-bharti-education-minister-chandrakant-patil/articleshow/118924405.cms</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/mahayuti-leaders-ajit-pawar-chandrakant-patil-and-shrikant-shinde-on-mission-sangli-for-damage-maha-vikas-aghadi-1386892.html</t>
+          <t>https://mahasamvad.in/169668/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ravindra-dhangekar-allegation-chandrakant-patil-and-murlidhar-mohol-politics-for-gajanan-marne-arrested/854647/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/jayshree-patil-to-join-bjp-presence-chief-minister-devendra-fadnavis/articleshow/121881414.cms</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ajit-pawar-devendra-fadnavis-shares-fun-moment-at-pune-lokmanya-tilak-award-ceremony-with-chandrakant-patil-eknath-shinde/articleshow/123054887.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/medha-kulkarni-left-bjp-meeting-midway-as-chandrakant-patil-murlidhar-mohol-backs-deenanath-mangeshkar-case-andolan/articleshow/120120230.cms</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/action-against-b-ed-colleges-as-per-the-rules-of-the-national-council-for-teacher-education-higher-and-technical/</t>
+          <t>https://mahasamvad.in/173736/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/education/chandrakant-patil-announced-ews-certificate-accepted-for-one-year-economically-weaker-section-student-maharashtra-education-marathi-news-1340514</t>
+          <t>https://marathi.abplive.com/news/politics/manoj-jarange-patil-mumbai-morcha-radhakrishna-vikhe-patil-was-elected-as-the-chairman-of-the-maratha-community-sub-committee-1379179</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/sangli-crime-news-seven-month-pregnant-woman-self-killed-after-alleged-being-tortured-by-in-laws-for-religious-conversion-3-arrested-maharashtra-news-mhs25061200648</t>
+          <t>https://marathi.abplive.com/news/politics/raksha-khadse-daughter-molestation-case-after-cm-devendra-fadnavis-statement-accused-belonged-to-specific-party-rohini-khadse-claimed-accused-was-supporters-of-shiv-sena-shinde-faction-mla-chandrakant-patil-1347053</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-politics-ajit-pawar-jayant-patil-rohit-pawar-clash-1471655.html</t>
+          <t>https://marathi.abplive.com/news/solapur/solapur-jayakumar-gore-news-guardian-minister-jayakumar-gore-reaction-to-mla-ranjitsinh-mohite-patil-in-solapur-1361873</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-mns-raj-thackeray-uddhav-thackeray-alliance-eknath-shinde-politics-news-in-marathi-aajchya-thalak-batmya-monday-21-april-2025-1388817.html</t>
+          <t>https://www.newsonair.gov.in/mr/education-free-for-female-students/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/grand-recruitment-in-higher-education-sector-in-the-state-appointment-notice-for-8400-posts-for-professors-and-employees/07251413</t>
+          <t>https://marathi.abplive.com/news/ahmednagar/chaundi-ahilyanagar-cabinet-meeting-cancled-31-may-on-ahilyabai-holkar-300th-jayanti-maharashtra-marathi-news-1356056</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/indias-first-artificial-intelligence-university-in-maharashtra-order-for-constitution-of-committee-chandrakant-patil/articleshow/117637901.cms</t>
+          <t>https://marathi.abplive.com/news/pune/pune-digital-media-social-work-honoured-in-pune-ikshan-pratishthan-for-the-children-of-journalists-ceremony-in-the-presence-of-chandrakant-patil-1360276</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/dte-maharashtra-polytechnic-admissions-2025-deadline-extended-for-applications-until-june-26/articleshow/121889185.cms</t>
+          <t>https://mahasamvad.in/153348/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/chandrakant-patil-proposes-safety-measures-to-prevent-fires-on-punes-17-hills/</t>
+          <t>https://marathi.abplive.com/education/chandrakant-patil-announced-ews-certificate-accepted-for-one-year-economically-weaker-section-student-maharashtra-education-marathi-news-1340514</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/maharashtra-govt-unveils-new-grading-system-to-modernise-public-libraries/</t>
+          <t>https://marathi.abplive.com/news/sangli/sangli-district-central-cooperative-bank-vice-president-jayashree-patil-will-join-the-bjp-marathi-news-update-1364524</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/chandrakant-patil-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%95-%E0%A4%97%E0%A4%A6-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%AA%E0%A5%87%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B2-%E0%A4%AC%E0%A4%B8-%E0%A4%B5%E0%A4%82-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%B5-%E0%A4%B9%E0%A4%A8/ar-AA1L414d</t>
+          <t>https://marathi.indiatimes.com/career/career-news/girl-free-education-scheme-in-maharashtra-latest-news-chandrakant-patil-mulina-mofat-shikshan-yojana-maharashtra-2024/articleshow/118265312.cms</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/carry-on-scheme-unfortunate-for-maharashtra-says-abvp-on-chandrakant-patil-decision-7648590</t>
+          <t>https://marathi.abplive.com/news/pune/pune-crime-rave-party-chandrakant-patil-criticizes-rohini-khadse-as-soon-as-her-husband-pranjal-khewalkar-is-arrested-maharashtra-marathi-news-1372935</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/girls-free-education-in-maharashtra-special-scheme-for-other-fees-assurance-from-chandrakant-patil/articleshow/123376903.cms</t>
+          <t>https://civicmirror.in/news/pune-or-heartbroken-to-hear-the-truth-about-the-attack-chandrakant-patil-consoles-ganbote-jagdale-families/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-double-voting-allegations-chandrakant-patil-accuses-rohini-khadse-of-voting-twice-in-kothali-and-muktainagar-sparks-maharashtra-political-row-1379422</t>
+          <t>https://www.tarunbharat.com/chandrakant-atial-discussion-with-flood-situated-people-sangli-walwa-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/guardian-minister-orders-crop-damage-survey-in-flood-hit-areas-mj18</t>
+          <t>https://civicmirror.in/news/polytechnic-admissions-2025-or-extension-of-deadline-for-submission-of-applications-for-polytechnic-courses-instructions/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.eduvarta.com/Minister-Chandrakant-Patils-instructions-to-conduct-CET-again-for-BBA-BCA</t>
+          <t>https://news18marathi.com/maharashtra/mahayuti-leaders-ajit-pawar-chandrakant-patil-and-shrikant-shinde-on-mission-sangli-for-damage-maha-vikas-aghadi-1386892.html</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-sant-puja-and-distribution-of-useful-materials-to-warkari-brothers-on-the-occasion-of-ashadhi-wari/</t>
+          <t>https://marathi.abplive.com/news/politics/ajit-pawar-funny-comment-on-jayant-patil-in-front-of-rohit-pawar-and-chandrakant-patil-sangli-maharashtra-politics-marathi-news-1377436</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/bamu-s-big-decision-admissions-to-113-colleges-including-educational-institutions-of-chandrakant-patil-sule-munde/</t>
+          <t>https://marathi.abplive.com/news/sangli/former-corporator-manoj-sargar-who-played-a-role-in-getting-vishal-patil-elected-is-joining-the-bharatiya-janata-party-on-monday-1375918</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/chandrakant-patil-on-sanjaykaka-patil-and-ones-again-offer-to-vishal-patil-join-bjp/</t>
+          <t>https://www.mymahanagar.com/maharashtra/ravindra-dhangekar-allegation-chandrakant-patil-and-murlidhar-mohol-politics-for-gajanan-marne-arrested/854647/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-no-matter-how-much-black-magic-someone-does-it-doesnt-matter-bjp-has-as-many-as-137-mlas-who-is-chandrakant-patal-targeting-so-the-indication-of-bawankules-to-fight-the-upco/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ajit-pawar-devendra-fadnavis-shares-fun-moment-at-pune-lokmanya-tilak-award-ceremony-with-chandrakant-patil-eknath-shinde/articleshow/123054887.cms</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-news-spontaneous-response-to-the-grain-festival-organized-by-minister-chandrakantdada-patil/</t>
+          <t>https://mahasamvad.in/166808/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-philosophy-of-thinking-positively-about-others-in-hindu-culture-chandrakantdada-patils-assertion/</t>
+          <t>https://agrowon.esakal.com/agro-special/guardian-minister-orders-crop-damage-survey-in-flood-hit-areas-mj18</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/firata-davakhana-for-warkari-state-minister-chandrakant-patil-inaugurated-in-pune-article-152110556</t>
+          <t>https://marathi.abplive.com/news/pune/medha-kulkarni-left-the-meeting-chandrakant-patil-murlidhar-mohol-supported-the-deenanath-mangeshkar-case-andolan-tanisha-bhise-death-case-what-exactly-happened-during-the-meeting-1353526</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/sangli-or-review-the-arms-licenses-in-the-district-to-control-criminal-incidents-guardian-minister-chandrakant-patil/</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-politics-ajit-pawar-jayant-patil-rohit-pawar-clash-1471655.html</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://policenama.com/bajirao-peshwa-memorials-on-parvati-hill-development-work-of-bajirao-peshwa-memorial-on-parvati-hill-satisfactory-the-first-phase-will-be-inaugurated-by-union-minister-rajnath-singh-chandrakant-p/</t>
+          <t>https://civicmirror.in/news/action-against-b-ed-colleges-as-per-the-rules-of-the-national-council-for-teacher-education-higher-and-technical/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/uddhav-thackerays-party-wants-to-join-the-government-chandrakant-patil-said/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-may-halt-admissions-to-pharmacy-colleges-flouting-norms-101753902851567.html</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/polytechnic-or-engineering-diploma-admission-application-registration-deadline-extended-new-schedule-announced-minister/</t>
+          <t>https://www.ptinews.com/story/national/Ahead-of-Mumbai-protest--Maharashtra-minister-asks-Jarange-to-hold-talks-with-govt/2848338</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/big-recruitment-in-the-higher-education-department-of-maharashtra-5500-professors-and-2900-employees-will-be-recruited-article-152339600</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-to-restart-withdrawn-services-by-tanker-association-with-police-help-101744571005989.html</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/satara-news-disability-certificates-of-17-more-teachers-are-invalid/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/police-bust-chain-snatching-gang-two-held-minor-detained-101740078106456.html</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.athawadavishesh.com/34215/</t>
+          <t>https://www.indiatvnews.com/maharashtra/maharashtra-abu-azmi-writes-letter-to-speaker-rahul-narwekar-to-revoke-his-suspension-over-statement-on-aurangzeb-latest-updates-2025-03-07-979620</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/sangli-politics-congress-suffers-setback-pruthviraj-patil-joins-bjp-with-hundreds-of-supporters/</t>
+          <t>https://zeenews.india.com/india/maharashtra-politics-did-bjp-minister-just-confirm-rift-within-mahayuti-shindes-meeting-with-shah-2886410.html</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/police-bust-chain-snatching-gang-two-held-minor-detained-101740078106456.html</t>
+          <t>https://news.careers360.com/maharashtra-university-faculty-recruitment-resume-new-evaluation-rules-academics-research-teaching-interview</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-chandrakant-patil-flags-pmc-misgovernance-amid-delayed-elections-high-level-meeting-with-ajit-pawar-likely/</t>
+          <t>https://www.mypunepulse.com/maharashtra-govt-unveils-new-grading-system-to-modernise-public-libraries/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/delay-in-punes-equal-water-supply-scheme-sparks-public-discontent-mla-chandrakant-patil-criticizes-pmc/</t>
+          <t>https://www.msn.com/mr-in/news/other/chandrakant-patil-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%95-%E0%A4%97%E0%A4%A6-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%AA%E0%A5%87%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B2-%E0%A4%AC%E0%A4%B8-%E0%A4%B5%E0%A4%82-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%B5-%E0%A4%B9%E0%A4%A8/ar-AA1L414d</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-11-political-news-in-marathi-931306</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-mns-raj-thackeray-uddhav-thackeray-alliance-eknath-shinde-politics-news-in-marathi-aajchya-thalak-batmya-monday-21-april-2025-1388817.html</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-july-pune-rave-party-raj-thackeray-uddhav-thackeray-latest-news-mumbai-konkan-marathwada-weather-report-today-rain-updates-kolhapur-pandharpur-pmw-88-5267001/</t>
+          <t>https://marathi.abplive.com/videos/news/politics-chandrakant-patil-sanjay-raut-bjp-uddhav-thackeray-narendra-modi-marathi-news-abp-majha-1364424</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-state-government-halts-new-pharmacy-colleges-understand-the-reasons-behind-decreased-demand/articleshow/120842410.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-double-voting-allegations-chandrakant-patil-accuses-rohini-khadse-of-voting-twice-in-kothali-and-muktainagar-sparks-maharashtra-political-row-1379422</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-breaking-news-live-in-marathi-1-may-2025-maharashtra-din-kamgar-divas-pahalgam-attack-update-pm-modi-cm-devendra-fadnavis-mumbai-pune-latest-updates/liveblog/120781856.cms</t>
+          <t>https://marathi.indiatimes.com/career/career-news/indias-first-artificial-intelligence-university-in-maharashtra-order-for-constitution-of-committee-chandrakant-patil/articleshow/117637901.cms</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/public-universities-recruitment-of-vacancies-in-non-colleges-will-be-accelerated-100-percent-recruitment-in-engineering-institutions-maharashtra-news-mhs25070802041</t>
+          <t>https://marathi.indiatimes.com/career/career-news/girls-free-education-in-maharashtra-special-scheme-for-other-fees-assurance-from-chandrakant-patil/articleshow/123376903.cms</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/neet-pg-counselling-2024-reduction-in-cut-off-percentile-medical-council-committee-5-percentile-student-qualify/articleshow/118624987.cms</t>
+          <t>https://marathi.timesnownews.com/maharashtra/shiv-sena-mla-chandrakant-patil-taken-into-custody-by-police-article-152324476</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/pune-or-hadapsar-will-get-a-new-metro-line-connectivity-to-the-main-city-will-make-travel-faster/</t>
+          <t>https://www.eduvarta.com/Minister-Chandrakant-Patils-instructions-to-conduct-CET-again-for-BBA-BCA</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/thane-municipal-corporation-fir-against-68-unauthorized-schools-52-crore-fine/articleshow/118617204.cms</t>
+          <t>https://policenama.com/chandrakant-patil-sant-puja-and-distribution-of-useful-materials-to-warkari-brothers-on-the-occasion-of-ashadhi-wari/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/school-bus-rules-and-regulations-for-student-in-marathi-demand-to-charge-bus-fare-for-10-months-instead-of-12/articleshow/118546648.cms</t>
+          <t>https://civicmirror.in/news/bamu-s-big-decision-admissions-to-113-colleges-including-educational-institutions-of-chandrakant-patil-sule-munde/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/loknete-laxman-jagtap-is-an-inspiring-chapter-higher-and-technical-education-minister-chandrakant-patil/</t>
+          <t>https://www.eduvarta.com/Higher-Education-Minister-Chandrakant-Patil-insists-on-the-recruitment-of-professors-11-thousand-87-posts-are-vacant-in-the-state</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.eduvarta.com/Approval-for-recruitment-of-5012-posts-in-the-Assistant-Professor-cadre</t>
+          <t>https://policenama.com/chandrakant-patil-no-matter-how-much-black-magic-someone-does-it-doesnt-matter-bjp-has-as-many-as-137-mlas-who-is-chandrakant-patal-targeting-so-the-indication-of-bawankules-to-fight-the-upco/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://newstown.in/samvidhan-gaurav-mahotsav-in-6-thousand-colleges-in-maharashtra-to-be-held-in-feburary-2025/</t>
+          <t>https://policenama.com/chandrakant-patil-news-spontaneous-response-to-the-grain-festival-organized-by-minister-chandrakantdada-patil/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/mp-vishal-patil-sanjay-patil-and-prithviraj-patil-on-the-same-platform-in-sangli-marathi-news-udpate-1377401</t>
+          <t>https://policenama.com/chandrakant-patil-philosophy-of-thinking-positively-about-others-in-hindu-culture-chandrakantdada-patils-assertion/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-be-btech-mba-mms-admission-2025-deadline-extended-till-july-14-final-chance/articleshow/122391899.cms</t>
+          <t>https://marathi.timesnownews.com/maharashtra/firata-davakhana-for-warkari-state-minister-chandrakant-patil-inaugurated-in-pune-article-152110556</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://marathi.latestly.com/socially/maharashtra/ramabai-ambedkar-punyatithi-2025-ajit-pawar-to-prakash-ambedkar-pays-tribute-to-ramai-on-her-death-anniversary-590799.html</t>
+          <t>https://policenama.com/bajirao-peshwa-memorials-on-parvati-hill-development-work-of-bajirao-peshwa-memorial-on-parvati-hill-satisfactory-the-first-phase-will-be-inaugurated-by-union-minister-rajnath-singh-chandrakant-p/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-may-halt-admissions-to-pharmacy-colleges-flouting-norms-101753902851567.html</t>
+          <t>https://www.marathi.hindusthanpost.com/social/mumbai-university-relief-for-87-compassionately-appointed-employees-minister-chandrakant-patils-decision-to-regularize-services/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-approves-long-pending-faculty-recruitment-for-state-universities-colleges-101751916450665.html</t>
+          <t>https://maharashtradesha.com/uddhav-thackerays-party-wants-to-join-the-government-chandrakant-patil-said/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/mere-speculation-chandrakant-patil-on-rumours-about-likely-merger-of-ncp-factions-news-in-hindi-2025-05-14</t>
+          <t>https://marathi.timesnownews.com/maharashtra/big-recruitment-in-the-higher-education-department-of-maharashtra-5500-professors-and-2900-employees-will-be-recruited-article-152339600</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/uddhav-in-shinde-out-bjp-is-cooking-up-a-new-plan-in-maharashtra-chandrakant-patil-met-uddhav-201738301481336.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-march-05-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-890636</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-17-july-maharashtra-assembly-monsoon-session-2025-devendra-fadnavis-on-tri-bhasha-sutra-ola-uber-rickshaw-taxis-closed-rak-94-5234478/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-breaking-news-live-in-marathi-1-may-2025-maharashtra-din-kamgar-divas-pahalgam-attack-update-pm-modi-cm-devendra-fadnavis-mumbai-pune-latest-updates/liveblog/120781856.cms</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/effectively-implement-the-free-higher-education-scheme-for-girls-orders-chandrakant-patil-8702210</t>
+          <t>https://civicmirror.in/city/pune/big-announcement-for-pune-police-will-get-5-new-police-stations-and-1000-additional-police-force/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/maharashtra-hindi-imposition-protest-uddhav-thackeray-and-raj-thackeray-unite-massive-rally-against-mama-chandrakant-vaidya-reaction-1432755.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/jalgaon-news/st-bus-brakes-fail-in-chopda-taluka-newlywed-youth-died-in-accident-cctv-footage/articleshow/121291227.cms</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/water-storage-in-seven-dams-supplying-water-to-mumbai-reaches-50-percent/articleshow/122265724.cms</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-10th-board-exam-result-2025-ssc-hsc-board-nashik-divisional-office-work-of-668-schools-pending/articleshow/118621538.cms</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/uddhav-thackeray-has-accepted-the-hindi-mandatory-policy-in-the-state-reveals-minister-uday-samant/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/school-bus-rules-and-regulations-for-student-in-marathi-demand-to-charge-bus-fare-for-10-months-instead-of-12/articleshow/118546648.cms</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/hindi-is-being-forced-to-end-marathi-language-and-culture-we-will-defeat-this-agenda-of-bjp-and-rss-harshvardhan-sapkal/</t>
+          <t>https://www.eduvarta.com/Approval-for-recruitment-of-5012-posts-in-the-Assistant-Professor-cadre</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/raj-thackeray-announces-grand-march-against-hindi-compulsion/</t>
+          <t>https://policenama.com/mkcl-devendra-fadnavis-mkcls-silver-jubilee-foundation-day-celebrated-with-excitement-mkcls-success-in-democratizing-the-information-technology-revolution-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-pune-festival-to-begin-on-august-29-inauguration-by-governor/</t>
+          <t>https://www.dainikprabhat.com/ig-news-list-of-guardian-ministers-announced/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/maharashtra-politics-did-bjp-minister-just-confirm-rift-within-mahayuti-shindes-meeting-with-shah-2886410.html</t>
+          <t>https://marathi.latestly.com/socially/maharashtra/ramabai-ambedkar-punyatithi-2025-ajit-pawar-to-prakash-ambedkar-pays-tribute-to-ramai-on-her-death-anniversary-590799.html</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/ahilyadevi-holkar-s-legacy-must-be-known-to-youth-cm-101748631369699.html</t>
+          <t>https://www.livehindustan.com/maharashtra/uddhav-in-shinde-out-bjp-is-cooking-up-a-new-plan-in-maharashtra-chandrakant-patil-met-uddhav-201738301481336.html</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-seek-restoration-of-savarkar-s-barrister-degree-101748373138133.html</t>
+          <t>https://www.aajtak.in/india/news/video/mla-chandrakant-patil-in-custody-protest-on-the-highway-with-farmers-ytvd-2293913-2025-07-23</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/pregnant-womans-dad-accuses-spouse-kin-of-harassment/articleshow/121809105.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-approves-long-pending-faculty-recruitment-for-state-universities-colleges-101751916450665.html</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/education/news/maharashtra-launches-atal-portal-for-entrance-prep-and-career-guidance/articleshow/117296155.cms</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-17-july-maharashtra-assembly-monsoon-session-2025-devendra-fadnavis-on-tri-bhasha-sutra-ola-uber-rickshaw-taxis-closed-rak-94-5234478/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/days-before-hsc-exam-70-students-get-hall-tickets-with-wrong-subjects/articleshow/118097108.cms</t>
+          <t>https://civicmirror.in/news/hindi-is-being-forced-to-end-marathi-language-and-culture-we-will-defeat-this-agenda-of-bjp-and-rss-harshvardhan-sapkal/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/india-emerging-as-global-knowledge-partner-dharmendra-pradhan/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/water-storage-in-seven-dams-supplying-water-to-mumbai-reaches-50-percent/articleshow/122265724.cms</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163883/</t>
+          <t>https://civicmirror.in/news/uddhav-thackeray-has-accepted-the-hindi-mandatory-policy-in-the-state-reveals-minister-uday-samant/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/mht-cet-exam-2025-or-technical-glitch-in-mht-cet-2025-pcm-group-exam-re-exam-on-may-5th/cid1746067306.htm</t>
+          <t>https://civicmirror.in/news/raj-thackeray-announces-grand-march-against-hindi-compulsion/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/mht-cet-2025-reexam-announces-for-pcm-on-may-5-due-to-errors-in-21-questions-read-details-in-marathi-article-151540811</t>
+          <t>https://www.dainikprabhat.com/pune-news-pune-festival-to-begin-on-august-29-inauguration-by-governor/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/rte-news-preparations-to-boycott-private-english-medium-school-admission-process-due-to-this-reason/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/ahilyadevi-holkar-s-legacy-must-be-known-to-youth-cm-101748631369699.html</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/patankar-and-patil-join-bjp-as-strong-rivals-of-sitting-sena-mlas/articleshow/121762155.cms</t>
+          <t>https://www.hindustantimes.com/trending/dead-bodies-debris-eyewitness-recalls-hearing-massive-sound-during-air-india-plane-crash-101749723280168.html</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/bjp-mantris-remark-sparks-buzz-of-patch-up-with-shiv-sena-ubt/articleshow/117754765.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/pregnant-womans-dad-accuses-spouse-kin-of-harassment/articleshow/121809105.cms</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-mlc-first-to-record-statement-in-cm-s-sit-probe-101740079847054.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-seek-restoration-of-savarkar-s-barrister-degree-101748373138133.html</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/bjp-leaders-conduct-back-to-back-separate-review-meetings-at-pmc-oppn-questions-lack-of-results-101751143694920.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/days-before-hsc-exam-70-students-get-hall-tickets-with-wrong-subjects/articleshow/118097108.cms</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/education/news/maharashtra-launches-atal-portal-for-entrance-prep-and-career-guidance/articleshow/117296155.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>https://www.newsonair.gov.in/india-emerging-as-global-knowledge-partner-dharmendra-pradhan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>https://news.careers360.com/mht-cet-pcm-re-test-2025-may-5-for-27837-english-urdu-marathi-21-maths-questions-go-wrong-paper-setters-blacklisted</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>https://www.punekarnews.in/millennium-national-school-shines-at-invitational-taekwondo-inter-school-competition/</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>https://civicmirror.in/news/rte-news-preparations-to-boycott-private-english-medium-school-admission-process-due-to-this-reason/</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/163883/</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/career/career-news/mht-cet-2025-pcm-group-re-exam-on-may-5-exam-canceled-due-to-technical-errors-conducted-on-27-april/articleshow/120769046.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>https://civicmirror.in/maharashtra/mht-cet-exam-2025-or-technical-glitch-in-mht-cet-2025-pcm-group-exam-re-exam-on-may-5th/cid1746067306.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>https://marathi.timesnownews.com/maharashtra/mht-cet-2025-reexam-announces-for-pcm-on-may-5-due-to-errors-in-21-questions-read-details-in-marathi-article-151540811</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/bjp-mantris-remark-sparks-buzz-of-patch-up-with-shiv-sena-ubt/articleshow/117754765.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-mlc-first-to-record-statement-in-cm-s-sit-probe-101740079847054.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>https://www.indiaherald.com/Politics/Read/994827843/BJP-leaders-statement-on-Raj-Thackeray-Like-one-who-predicts</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
         <is>
           <t>https://www.tarunbharat.com/prithviraj-patil-avoided-joining-the-bjp/</t>
         </is>

--- a/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A63"/>
+  <dimension ref="A1:A85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,434 +438,588 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-directs-universities-to-hire-contractual-professors-after-drop-in-nirf-rankings-101757788998645.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/no-repeated-paperwork-for-professional-course-scholarships-minister-101758221398673.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
+          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-March-2026-says-minister-Chandrakant-Patil/2934478</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/autonomy-vital-for-researchers-to-pursue-innovation-says-cm-fadnavis-101757875592362-amp.html</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-starts-direct-transfer-of-grants-to-over-10-000-public-libraries/2930525</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/naredco-mahi-launches-pune-chapter-at-pune-growth-conclave-2025/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/higher-edu-dept-to-host-lecture-series-vikasit-bharat-sanvad-from-sept-17-101757963146391.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178164/</t>
+          <t>https://www.ptinews.com/story/national/india-targets-5-pc-share-in-global-shipbuilding-market-by-2030-minister/2916379</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/ajinkya-dilip-patil-demands-chandrakant-patil-to-be-the-chairman-of-maratha-sub-committee/videoshow/123844027.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%B5-%E0%A4%B0-%E0%A4%A7%E0%A4%95-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%9F-%E0%A4%95/vi-AA1MAx0W?ocid=hpmsn</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/short-videos/trending/chandrakant-patil-new-gr-on-maratha-reservation-shocks-obcs-chandrakant-patil-spoke-directly-n18s-1074225.html</t>
+          <t>https://mahasamvad.in/179160/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/provide-funding-for-the-coep-organization-chief-minister-devendra-fadnavis-assured-chandrakant-patil/939239</t>
+          <t>https://www.instagram.com/p/DO3HFhNjGpE/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178123/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/chandrakant-patil-assures-to-follow-up-at-the-ministerial-level-135978085.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/lifestyle/topstories/%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%A7%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A4%95%E0%A4%B9-%E0%A4%95%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9F-%E0%A4%89%E0%A4%9A%E0%A5%8D%E0%A4%9A-%E0%A4%B5-%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%B6-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%A4-%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A5%81%E0%A4%B0%E0%A4%A4-%E0%A4%89%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A5%8D%E0%A4%A5%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A4%B5-%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%8D%E0%A4%A8%E0%A4%9A-%E0%A4%A8%E0%A5%8D%E0%A4%B9/ar-AA1MsMTN</t>
+          <t>https://mahasamvad.in/178560/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-contractual-assistant-professor-bharti-2025-nirf-ranking-higher-education-minister-chandrakant-patil/articleshow/123864684.cms</t>
+          <t>https://mahasamvad.in/178569/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/pune-news-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B2-%E0%A4%95%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%89%E0%A4%AE%E0%A5%87%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%B8-%E0%A4%A0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B5%E0%A4%9C%E0%A4%A8-%E0%A4%85%E0%A4%B8%E0%A4%A3-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%87%E0%A4%9A%E0%A5%8D%E0%A4%9B%E0%A5%81%E0%A4%95-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AB%E0%A5%87%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%A2%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%B9-%E0%A4%95-%E0%A4%A3/ar-AA1MacYV</t>
+          <t>https://zeenews.india.com/marathi/video/minister-chandrakant-patil-criticized-the-opposition/939518</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-manoj-jarange-demands-accepted-patil-advice-implementation-135893272.html</t>
+          <t>https://mahasamvad.in/178557/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/pune-news-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%AE-%E0%A4%AB%E0%A4%A4-%E0%A4%AC%E0%A4%B8-%E0%A4%B8%E0%A5%87%E0%A4%B5-%E0%A4%95%E0%A5%81%E0%A4%A0%E0%A5%82%E0%A4%A8-%E0%A4%95%E0%A5%81%E0%A4%A0%E0%A5%87-%E0%A4%A7-%E0%A4%B5%E0%A4%A3-%E0%A4%B0-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%B6%E0%A4%A8%E0%A4%AA-%E0%A4%B8%E0%A5%82%E0%A4%A8-%E0%A4%98%E0%A4%B0-%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA%E0%A5%88%E0%A4%B6-%E0%A4%82%E0%A4%B8%E0%A4%B9-%E0%A4%B5%E0%A5%87%E0%A4%B3%E0%A5%87%E0%A4%9A-%E0%A4%B9-%E0%A4%AC%E0%A4%9A%E0%A4%A4-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0/ar-AA1Mv10g</t>
+          <t>https://www.msn.com/mr-in/lifestyle/topstories/ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%9C-%E0%A4%A3%E0%A5%82%E0%A4%A8-%E0%A4%98%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%89%E0%A4%9A%E0%A5%8D%E0%A4%9A-%E0%A4%B5-%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%B6-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2/ar-AA1x59Ez?cvid=E5D2FC4919EC403B89F2CDD45BDCA942&amp;ocid=TIYLnav&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maratha-reservation-gr-will-not-be-withdrawn-vikhe-patil-rat16</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-social-fabric-minister-chandrakant-patil-expresses-concern-over-state-s-social-disintegration-citing-caste-issues-and-impact-on-development-1385630</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/pune/latest-marathi-news-punekar-get-free-bus-transportation-from-station-to-home-convenient-and-cost-effective-local18-1479628.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/pune-free-shuttle-bus-service-to-metro-station-in-kothrud/articleshow/123877790.cms</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/gadkari-water-conservation-key-to-abundant-irrigation-and-farmer-as-energy-contributor-mj18</t>
+          <t>https://divyamarathi.bhaskar.com/amp/local/maharashtra/jalgaon/news/demand-for-200-crores-for-deepening-drains-and-protective-walls-in-the-affected-areas-inspection-by-guardian-minister-gulabrao-patil-and-minister-savkare-135956811.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/onion-growers-launch-phone-karo-movement-to-demand-price-hike-sai29</t>
+          <t>https://policenama.com/pm-modi-birthday-news-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-amol-balwadkar-foundation-launched-the-mission-nirmal-cleanliness-campaign-by-higher-technical-education-chan/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://mondaytomondaynews.com/camp-organized-at-kochur-on-the-occasion-of-a-chandrakant-patils-birthday/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/government-will-issue-a-white-paper-on-kunbi-registration-minister-patils-statement/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/chandrakant-patil-criticized-of-rahul-gandhi/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://policenama.com/swargate-metro-station-swargate-metro-station-will-become-a-multimodal-hub-for-punekars-for-travel-as-well-as-corporate-in-the-future-chandrakantdada-patil-has-confidence/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891/amp</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://mondaytomondaynews.com/at-muktainagar-a-chandrakantbhau-patil-was-showered-with-good-wishes-a-crowd-of-workers-came-to-wish-him/</t>
+          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-free-bus-service-from-home-to-metro-station-started-in-kothrud-know-the-schedule-and-route/</t>
+          <t>https://dainikekmat.com/income-certificate-now-available-only-once-scholarship-will-be-available-till-completion-of-course/117645/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/now-implement-kolhapur-gazetteer-immediately-maratha-community-demands/</t>
+          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/09/Scholarship-distribution-on-auto-system.html</t>
+          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379/amp</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/593-new-colleges-in-maharashtra-major-announcement-by-chief-minister-devendra-fadnavis/articleshow/123815581.cms</t>
+          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477/amp</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%B8-%E0%A4%A0-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%A3-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/ar-AA1L2jvO?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/gang-war-in-kolhapur-youth-kills-23-year-old-mahesh-rakh-shocking-facts-from-cctv-footage/articleshow/123865866.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://theclearnews.com/three-men-sitting-in-a-rickshaw-stole-cash-from-a-passengers-pocket/</t>
+          <t>https://saamtv.esakal.com/amp/story/national-international/uttar-pradesh-gorakhpur-crime-wife-caught-her-husband-red-handed-with-his-girlfriend-in-a-hotel-bdk97</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/silent-treatment-during-ganesh-immersion-sparks-speculation-of-friendly-contest-between-bjp-ncp-in-civic-polls-101757359369693.html</t>
+          <t>https://marathi.indiatimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178464/</t>
+          <t>https://saamtv.esakal.com/amp/story/sports/shahid-afridi-irfan-pathan-2006-pakistan-tour-dog-meat-remark-controversy-cricket-feud-ind-vs-pak-viral-video-latest-marathi-news-yps99</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/minister-chandrakant-patil-met-vice-chancellors-to-address-criticism-over-states-educational-decline-pune-print-news-sud-02-5367659/lite/</t>
+          <t>https://ahmednagarlive24.com/spacial/educational-news-now-students-will-have-to-provide-income-proof-only-once/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maratha-reservation-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%B2-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%AC-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%A3%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A4%A7-%E0%A4%AA-%E0%A4%B8%E0%A5%82%E0%A4%A8-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%B5-%E0%A4%96%E0%A5%87-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A4%97%E0%A4%B3%E0%A4%82-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%B2%E0%A4%82-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1Mc2LQ</t>
+          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500/amp</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-11-september-2025-marathi-news-solapur-govind-barge-case-pune-mumbai-monsoon-2025-maharashtra-latest-updates/liveblog/123820930.cms</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-student-mahadbt-scholarship-simplified-chandrakant-patil-mumbai-print-news-ocd-94-5381828/lite/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/mahadevi-madhuri-elephant-rehabilitation-important-hearing-held-in-supreme-court/articleshow/123849295.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-social-fabric-minister-chandrakant-patil-expresses-concern-over-state-s-social-disintegration-citing-caste-issues-and-impact-on-development-1385630/amp</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/savitribai-phule-pune-university-vacancy-of-238-professors-sppu-nirf-ranking-2025-down/articleshow/123844742.cms</t>
+          <t>https://www.lokmat.com/maharashtra/action-will-be-taken-fancy-number-plate-co-operative-fan/?utm_source=Lokmat.com&amp;utm_medium=app_banner_amp_AfterArticle&amp;launch_url=https://www.lokmat.com/maharashtra/action-will-be-taken-fancy-number-plate-co-operative-fan/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/82-minor-girls-returned-to-their-parents-under-operation-muskan-in-ahilyanagar-ssb-93-5366771/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/permission-for-private-universities-to-offer-medical-education-in-maharashtra-invest-seize-the-opportunity/articleshow/123842558.cms</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-demand-for-subsidy-for-miraj-balgandharva-theatre-ssb-93-5386538/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/government-renames-ideal-state-teacher-award-after-renowned-educationist-dr-j-p-naik-101757443983298.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-cm-fadnavis-stresses-autonomy-for-higher-education-institutions-at-coep-event/</t>
+          <t>https://www.loksatta.com/pune/pune-thieves-broke-lock-of-flat-in-bibwewadi-kondhwa-area-and-stole-valuables-worth-over-rs-5-lakh-pune-print-news-sud-02-5389067/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178050/</t>
+          <t>https://www.loksatta.com/maharashtra/satara-electric-vehicles-will-now-run-on-the-kas-plateau-ssb-93-5386502/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/amp/maharashtra-news/mumbai-suburban/kurla/mumbai-sub-discussion-on-important-issue-related-to-border-question-15377439</t>
+          <t>https://saamtv.esakal.com/amp/story/maharashtra/navratri-festival-extra-msrtc-buses-to-saptashrungi-gad-msrtc-to-run-additional-buses-bbj88</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/cm-devendra-fadnavis-directs-to-prepare-a-format-for-scholarship-distribution-on-auto-system/</t>
+          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077/amp</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/rising-demand-for-foreign-students-in-engineering-colleges-in-maharashtra-special-preference-for-coep/articleshow/123827313.cms</t>
+          <t>https://saralnama.in/education/16002/maharashtra-to-hire-5-500-assistant-professors-by-march-2026/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/lifestyle/topstories/new-colleges-in-maharashtra-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A5%AB%E0%A5%AF%E0%A5%A9-%E0%A4%A8%E0%A4%B5-%E0%A4%AE%E0%A4%B9-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B2%E0%A4%AF%E0%A5%87-%E0%A4%B6-%E0%A4%B7%E0%A5%8D%E0%A4%AF%E0%A4%B5%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%9A-%E0%A4%B9-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A5%82%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%A0%E0%A5%8D%E0%A4%AF-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1Mjk3m?cvid=cb3b3cbb29134e49acf9060e129ca2a8</t>
+          <t>https://jantaserishta.com/amp/local/maharashtra/no-one-will-support-padalkars-language-chandrakant-patil-clearly-stated-4277808</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-educational-institutions-will-be-autonomous-but-within-the-framework-of-rules-chief-minister-fadnavis/</t>
+          <t>https://www.moneycontrol.com/education/maharashtra-to-recruit-5500-assistant-professors-by-2026-announces-minister-chandrakant-patil-article-13563810.html/amp</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/advanced-technology-and-agro-industries-key-to-preventing-farmer-suicides-gadkari/</t>
+          <t>https://news.careers360.com/karnataka-sslc-puc-2-time-table-2026-out-on-kseab-karnataka-gov-in-submit-objections-october-9-class-10-12-exam/amp</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/amp/en/!entertainment/nana-patekar-speaks-against-india-pak-asia-cup-clash-enn25091403520</t>
+          <t>https://www.hindustantimes.com/cities/chandigarh-news/inld-and-jjp-both-proxies-of-the-bjp-haryana-ex-cm-hooda-101758134956254.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B8%E0%A4%BE%E0%A4%A4%E0%A4%BE%E0%A4%B0%E0%A4%BE-%E0%A4%97%E0%A5%85%E0%A4%9D%E0%A5%87%E0%A4%9F%E0%A5%8D%E0%A4%B8%E0%A4%B8%E0%A4%BE%E0%A4%A0%E0%A5%80-%E0%A4%B9%E0%A4%BE%E0%A4%B2%E0%A4%9A%E0%A4%BE/116591/</t>
+          <t>https://www.lokmat.com/topics/election/page/1537/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/cash-crops-boosted-the-economy-article-on-agrowon-rat16</t>
+          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/autonomy-vital-for-researchers-to-pursue-innovation-says-cm-fadnavis-101757875592362.html</t>
+          <t>https://m.economictimes.com/news/india/maharashtra-starts-direct-transfer-of-grants-to-over-10000-public-libraries/amp_articleshow/123999758.cms</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/coep-tech-to-celebrate-engineer-s-day-101757702158316.html</t>
+          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/lifestyle/topstories/medical-study-in-maharashtra-%E0%A4%B5%E0%A5%88%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%95-%E0%A4%AF%E0%A4%9A-%E0%A4%B5-%E0%A4%9F-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%96-%E0%A4%B8%E0%A4%97-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%A0-%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%B5%E0%A5%88%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%95-%E0%A4%AF-%E0%A4%85%E0%A4%AD%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A4%B0%E0%A4%B5-%E0%A4%A8%E0%A4%97/ar-AA1MoE4b</t>
+          <t>https://www.ptinews.com/detail/national/5-500-assistant-professors-to-be-recruited-before-March-2026-says-minister-Chandrakant-Patil/2934478</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/women-delaying-motherhood-increases-uterine-cancer-risk-experts-warn-pune-print-news-amy-95-5372589/</t>
+          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maratha-reservation-good-news-for-western-maharashtra-minister-shivendraraje-bhosale-meeting-with-pune-divisional-commissioner/articleshow/123864953.cms</t>
+          <t>https://jantaserishta.com/local/maharashtra/no-one-will-support-padalkars-language-chandrakant-patil-clearly-stated-4277808</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-directs-universities-to-hire-contractual-professors-after-drop-in-nirf-rankings-101757788998645-amp.html</t>
+          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/dte-stays-admissions-to-174-pharmacy-colleges-across-state-101757358773270.html</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-plans-to-allow-private-varsities-to-grant-medical-degrees-101757531417862.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/lifestyle/topstories/new-colleges-in-maharashtra-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A5%AB%E0%A5%AF%E0%A5%A9-%E0%A4%A8%E0%A4%B5-%E0%A4%AE%E0%A4%B9-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B2%E0%A4%AF%E0%A5%87-%E0%A4%B6-%E0%A4%B7%E0%A5%8D%E0%A4%AF%E0%A4%B5%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%9A-%E0%A4%B9-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A5%82%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%A0%E0%A5%8D%E0%A4%AF-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1Mjk3m</t>
+          <t>https://www.dainikprabhat.com/why-did-the-family-split-and-become-separated-finally-ajit-pawar-revealed-the-true-chapter/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/ten-day-long-ganesh-chaturthi-festival-to-culminate-today-with-immersion-of-lord-ganeshs-idols/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://annews.co.in/16393/</t>
+          <t>http://www.msn.com/en-in/news/India/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/ar-AA1MKOoA?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/education/exam-results/sc-allows-prosecutors-to-provisionally-appear-for-chhattisgarh-judicial-services-exam-101758289734023.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263-amp.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/education/news/govt-plans-to-introduce-skill-based-learning-in-class-11-12-curriculum-pradhan-101758507200271.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%A6-%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%82%E0%A4%A4-%E0%A4%B8%E0%A4%AE-%E0%A4%B0%E0%A4%82%E0%A4%AD-%E0%A4%A4-11-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%AA%E0%A4%A6%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6-%E0%A4%A8/ar-AA1MQWcn</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-18-101758160005114.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-17-101758074170050.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil/2934478</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>https://www.timesnownews.com/education/maharashtra-to-recruit-5500-assistant-professors-in-senior-colleges-by-march-2026-sarkari-naukri-article-152864646/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/education-jobs/maharashtra-professor-recruitment-2025-6200-teaching-vacancies-eligibility-application-details-mms21</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>https://www.dainikprabhat.com/big-relief-for-students-now-income-certificate-will-be-required-only-once-scholarship-will-be-available-till-completion-of-course/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/education/3635306-paving-the-way-for-skill-based-learning-a-new-era-in-education?amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/education/3633673-mizoram-chief-ministers-call-to-action-for-mizo-students?amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>https://deshonnati.com/in-the-ubatha-meeting-contest-kalmanuri-np-election/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>https://annews.co.in/16508/</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A85"/>
+  <dimension ref="A1:A74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,378 +438,378 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/no-repeated-paperwork-for-professional-course-scholarships-minister-101758221398673.html</t>
+          <t>https://indianexpress.com/article/cities/pune/not-giving-immediate-nod-for-faculty-hiring-due-to-fund-crunch-maharashtra-higher-education-minister-10249986/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-March-2026-says-minister-Chandrakant-Patil/2934478</t>
+          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-starts-direct-transfer-of-grants-to-over-10-000-public-libraries/2930525</t>
+          <t>https://www.timesnownews.com/education/5500-assistant-professors-to-be-recruited-in-maharashtra-before-march-2026-chandrakant-patil-article-152869876</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/higher-edu-dept-to-host-lecture-series-vikasit-bharat-sanvad-from-sept-17-101757963146391.html</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-to-recruit-5500-assistant-professors-by-march-2026/ar-AA1MZ5pj</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/india-targets-5-pc-share-in-global-shipbuilding-market-by-2030-minister/2916379</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/no-repeated-paperwork-for-professional-course-scholarships-minister-101758221398673.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%B5-%E0%A4%B0-%E0%A4%A7%E0%A4%95-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%9F-%E0%A4%95/vi-AA1MAx0W?ocid=hpmsn</t>
+          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179160/</t>
+          <t>https://mahasamvad.in/179266/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DO3HFhNjGpE/</t>
+          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/chandrakant-patil-assures-to-follow-up-at-the-ministerial-level-135978085.html</t>
+          <t>https://zeenews.india.com/marathi/video/minister-chandrakant-patil-criticized-the-opposition/939518</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178560/</t>
+          <t>https://mahasamvad.in/179160/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178569/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-nanded-news-education-is-not-our-country-priority-but-two-meals-a-day-is-says-minister-chandrakant-patil-1385473</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/minister-chandrakant-patil-criticized-the-opposition/939518</t>
+          <t>https://mahasamvad.in/179154/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178557/</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-statement-on-pm-narendra-modis-2047-plans-pune-print-news-sud-02-5390729/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/lifestyle/topstories/ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%9C-%E0%A4%A3%E0%A5%82%E0%A4%A8-%E0%A4%98%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%89%E0%A4%9A%E0%A5%8D%E0%A4%9A-%E0%A4%B5-%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%B6-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2/ar-AA1x59Ez?cvid=E5D2FC4919EC403B89F2CDD45BDCA942&amp;ocid=TIYLnav&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-social-fabric-minister-chandrakant-patil-expresses-concern-over-state-s-social-disintegration-citing-caste-issues-and-impact-on-development-1385630</t>
+          <t>https://mahasamvad.in/178560/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
+          <t>https://mahasamvad.in/178569/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
+          <t>https://mahasamvad.in/178654/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/amp/local/maharashtra/jalgaon/news/demand-for-200-crores-for-deepening-drains-and-protective-walls-in-the-affected-areas-inspection-by-guardian-minister-gulabrao-patil-and-minister-savkare-135956811.html</t>
+          <t>https://mahasamvad.in/178557/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://policenama.com/pm-modi-birthday-news-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-amol-balwadkar-foundation-launched-the-mission-nirmal-cleanliness-campaign-by-higher-technical-education-chan/</t>
+          <t>https://mahasamvad.in/178881/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-social-fabric-minister-chandrakant-patil-expresses-concern-over-state-s-social-disintegration-citing-caste-issues-and-impact-on-development-1385630</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/chandrakant-patil-criticized-of-rahul-gandhi/</t>
+          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891/amp</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-thackeray-alliance-chandrakant-patil-predicts-vote-bank-split-congress-exit-no-impact-on-mahayuti-1386136</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/income-certificate-now-available-only-once-scholarship-will-be-available-till-completion-of-course/117645/</t>
+          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263.html</t>
+          <t>https://policenama.com/pm-modi-birthday-news-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-amol-balwadkar-foundation-launched-the-mission-nirmal-cleanliness-campaign-by-higher-technical-education-chan/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379/amp</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/chandrakant-patil-criticized-of-rahul-gandhi/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477/amp</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%B8-%E0%A4%A0-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%A3-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/ar-AA1L2jvO?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.timemaharashtra.com/maharashtra/the-issue-of-loan-waiver-is-under-the-governments-consideration-what-exactly-did-chandrakant-patil-say/133526/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
+          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/national-international/uttar-pradesh-gorakhpur-crime-wife-caught-her-husband-red-handed-with-his-girlfriend-in-a-hotel-bdk97</t>
+          <t>https://dainikekmat.com/income-certificate-now-available-only-once-scholarship-will-be-available-till-completion-of-course/117645/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/sports/shahid-afridi-irfan-pathan-2006-pakistan-tour-dog-meat-remark-controversy-cricket-feud-ind-vs-pak-viral-video-latest-marathi-news-yps99</t>
+          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-recruit-5500-assistant-professors-for-senior-colleges-by-march-2026-5617</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/spacial/educational-news-now-students-will-have-to-provide-income-proof-only-once/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/higher-edu-dept-to-host-lecture-series-vikasit-bharat-sanvad-from-sept-17-101757963146391.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500/amp</t>
+          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-student-mahadbt-scholarship-simplified-chandrakant-patil-mumbai-print-news-ocd-94-5381828/lite/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-social-fabric-minister-chandrakant-patil-expresses-concern-over-state-s-social-disintegration-citing-caste-issues-and-impact-on-development-1385630/amp</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/action-will-be-taken-fancy-number-plate-co-operative-fan/?utm_source=Lokmat.com&amp;utm_medium=app_banner_amp_AfterArticle&amp;launch_url=https://www.lokmat.com/maharashtra/action-will-be-taken-fancy-number-plate-co-operative-fan/</t>
+          <t>https://www.dainikprabhat.com/chandrakant-patil-then-congress-will-leave-the-alliance-minister-chandrakant-patil-predicted/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
+          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-demand-for-subsidy-for-miraj-balgandharva-theatre-ssb-93-5386538/</t>
+          <t>https://www.dainikprabhat.com/big-relief-for-students-now-income-certificate-will-be-required-only-once-scholarship-will-be-available-till-completion-of-course/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
+          <t>https://theclearnews.com/gram-gaurav-foundation-to-hold-saksha-lakshmi-awareness-campaign-during-navratri/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/pune-thieves-broke-lock-of-flat-in-bibwewadi-kondhwa-area-and-stole-valuables-worth-over-rs-5-lakh-pune-print-news-sud-02-5389067/</t>
+          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-on-22-september-2025-breaking-marathi-batmya-997787.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/satara-electric-vehicles-will-now-run-on-the-kas-plateau-ssb-93-5386502/</t>
+          <t>https://marathi.indiatimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/navratri-festival-extra-msrtc-buses-to-saptashrungi-gad-msrtc-to-run-additional-buses-bbj88</t>
+          <t>https://www.navarashtra.com/business/8th-pay-commission-da-hike-diwali-bonus-central-government-employees-998599.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077/amp</t>
+          <t>https://www.navarashtra.com/business/government-schemes-old-pension-scheme-return-supreme-court-2026-news-in-marathi-995481.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://saralnama.in/education/16002/maharashtra-to-hire-5-500-assistant-professors-by-march-2026/</t>
+          <t>https://www.loksatta.com/pune/pune-thieves-broke-lock-of-flat-in-bibwewadi-kondhwa-area-and-stole-valuables-worth-over-rs-5-lakh-pune-print-news-sud-02-5389067/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/local/maharashtra/no-one-will-support-padalkars-language-chandrakant-patil-clearly-stated-4277808</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-demand-for-subsidy-for-miraj-balgandharva-theatre-ssb-93-5386538/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/education/maharashtra-to-recruit-5500-assistant-professors-by-2026-announces-minister-chandrakant-patil-article-13563810.html/amp</t>
+          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/karnataka-sslc-puc-2-time-table-2026-out-on-kseab-karnataka-gov-in-submit-objections-october-9-class-10-12-exam/amp</t>
+          <t>https://www.loksatta.com/maharashtra/satara-electric-vehicles-will-now-run-on-the-kas-plateau-ssb-93-5386502/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/chandigarh-news/inld-and-jjp-both-proxies-of-the-bjp-haryana-ex-cm-hooda-101758134956254.html</t>
+          <t>https://www.msn.com/en-in/news/India/5-500-assistant-professors-to-be-recruited-in-maharashtra-by-march-2026-says-minister/ar-AA1N2uUL?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/topics/election/page/1537/</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-polls-ex-bjp-leader-harshvardhan-patil-joins-ncp-sp/ar-AA1rOBQP?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A4%9F-%E0%A4%B2-%E0%A4%A7%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%98-%E0%A4%9F%E0%A4%97%E0%A5%87-%E0%A4%85%E0%A4%82%E0%A4%AC%E0%A4%B0-%E0%A4%B7-%E0%A4%98-%E0%A4%9F%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6/ar-AA1CXkyZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-starts-direct-transfer-of-grants-to-over-10000-public-libraries/amp_articleshow/123999758.cms</t>
+          <t>https://www.bweducation.com/article/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-572650</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
+          <t>https://mahasamvad.in/178877/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/5-500-assistant-professors-to-be-recruited-before-March-2026-says-minister-Chandrakant-Patil/2934478</t>
+          <t>https://mahasamvad.in/179132/</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/no-one-will-support-padalkars-language-chandrakant-patil-clearly-stated-4277808</t>
+          <t>https://www.bhaskar.com/amp/maharashtra/mumbai/bjp-maharashtra-president-chandrakant-patil-on-30-year-old-bjp-shiv-sena-alliance-126264710.html</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/why-did-the-family-split-and-become-separated-finally-ajit-pawar-revealed-the-true-chapter/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/autonomy-vital-for-researchers-to-pursue-innovation-says-cm-fadnavis-101757875592362.html</t>
         </is>
       </c>
     </row>
@@ -865,159 +865,82 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/ar-AA1MKOoA?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
+          <t>https://www.loksatta.com/pune/women-delaying-motherhood-increases-uterine-cancer-risk-experts-warn-pune-print-news-amy-95-5372589/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/exam-results/sc-allows-prosecutors-to-provisionally-appear-for-chhattisgarh-judicial-services-exam-101758289734023.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263-amp.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/news/govt-plans-to-introduce-skill-based-learning-in-class-11-12-curriculum-pradhan-101758507200271.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/mhalunge-police-arrest-four-for-theft-solve-two-more-robbery-cases/articleshow/124032928.cms</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%A6-%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%82%E0%A4%A4-%E0%A4%B8%E0%A4%AE-%E0%A4%B0%E0%A4%82%E0%A4%AD-%E0%A4%A4-11-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%AA%E0%A4%A6%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6-%E0%A4%A8/ar-AA1MQWcn</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-18-101758160005114.html</t>
+          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-17-101758074170050.html</t>
+          <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil/2934478</t>
+          <t>https://www.navarashtra.com/career/education-engineers-day-opinion-learn-these-skills-to-secure-engineering-job-in-10-years-990855.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/education/maharashtra-to-recruit-5500-assistant-professors-in-senior-colleges-by-march-2026-sarkari-naukri-article-152864646/amp</t>
+          <t>https://education.economictimes.indiatimes.com/news/higher-education/5500-assistant-professors-to-be-recruited-before-march-2026-says-maharashtra-higher-education-minister/124055248</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/education-jobs/maharashtra-professor-recruitment-2025-6200-teaching-vacancies-eligibility-application-details-mms21</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>https://www.dainikprabhat.com/big-relief-for-students-now-income-certificate-will-be-required-only-once-scholarship-will-be-available-till-completion-of-course/</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/education/3635306-paving-the-way-for-skill-based-learning-a-new-era-in-education?amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/education/3633673-mizoram-chief-ministers-call-to-action-for-mizo-students?amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>https://deshonnati.com/in-the-ubatha-meeting-contest-kalmanuri-np-election/</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
         <is>
           <t>https://annews.co.in/16508/</t>
         </is>

--- a/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A74"/>
+  <dimension ref="A1:A75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,28 +438,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/not-giving-immediate-nod-for-faculty-hiring-due-to-fund-crunch-maharashtra-higher-education-minister-10249986/</t>
+          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263.html</t>
+          <t>https://www.timesnownews.com/education/5500-assistant-professors-to-be-recruited-in-maharashtra-before-march-2026-chandrakant-patil-article-152869876</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/education/5500-assistant-professors-to-be-recruited-in-maharashtra-before-march-2026-chandrakant-patil-article-152869876</t>
+          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-March-2026-says-minister-Chandrakant-Patil/2934478</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-to-recruit-5500-assistant-professors-by-march-2026/ar-AA1MZ5pj</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
         </is>
       </c>
     </row>
@@ -473,91 +473,91 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379</t>
+          <t>https://www.patrika.com/en/education-news/maharashtra-announces-massive-recruitment-5500-assistant-professor-2900-non-teaching-posts-19963995</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179266/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/higher-edu-dept-to-host-lecture-series-vikasit-bharat-sanvad-from-sept-17-101757963146391.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
+          <t>https://www.devdiscourse.com/article/education/3635112-maharashtra-to-recruit-5500-assistant-professors-by-march-2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/minister-chandrakant-patil-criticized-the-opposition/939518</t>
+          <t>https://mahasamvad.in/179154/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179160/</t>
+          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-nanded-news-education-is-not-our-country-priority-but-two-meals-a-day-is-says-minister-chandrakant-patil-1385473</t>
+          <t>https://mahasamvad.in/178560/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179154/</t>
+          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-statement-on-pm-narendra-modis-2047-plans-pune-print-news-sud-02-5390729/</t>
+          <t>https://mahasamvad.in/178569/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-nanded-news-education-is-not-our-country-priority-but-two-meals-a-day-is-says-minister-chandrakant-patil-1385473</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178560/</t>
+          <t>https://mahasamvad.in/178654/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178569/</t>
+          <t>https://mahasamvad.in/178557/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178654/</t>
+          <t>https://www.etvbharat.com/mr/!state/income-certificate-once-submitted-for-scholarship-is-valid-till-the-end-of-college-relief-for-students-of-higher-and-technical-education-department-maharashtra-news-mhs25091705299</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178557/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-social-fabric-minister-chandrakant-patil-expresses-concern-over-state-s-social-disintegration-citing-caste-issues-and-impact-on-development-1385630</t>
         </is>
       </c>
     </row>
@@ -571,42 +571,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-social-fabric-minister-chandrakant-patil-expresses-concern-over-state-s-social-disintegration-citing-caste-issues-and-impact-on-development-1385630</t>
+          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
+          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-thackeray-alliance-chandrakant-patil-predicts-vote-bank-split-congress-exit-no-impact-on-mahayuti-1386136</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
+          <t>https://policenama.com/kothrud-missing-link-kothrud-constituency-moving-towards-traffic-congestion-relief-missing-link-work-underway-on-the-initiative-of-chandrakantdada-patil/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://policenama.com/pm-modi-birthday-news-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-amol-balwadkar-foundation-launched-the-mission-nirmal-cleanliness-campaign-by-higher-technical-education-chan/</t>
+          <t>https://policenama.com/chandrakant-patil-children-should-eat-nachni-foods-for-good-vitamins-needed-by-the-body-chandrakantdada-patils-advice-to-students/</t>
         </is>
       </c>
     </row>
@@ -620,21 +620,21 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
+          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/the-issue-of-loan-waiver-is-under-the-governments-consideration-what-exactly-did-chandrakant-patil-say/133526/</t>
+          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
+          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
         </is>
       </c>
     </row>
@@ -648,182 +648,182 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
+          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-recruit-5500-assistant-professors-for-senior-colleges-by-march-2026-5617</t>
+          <t>https://www.dainikprabhat.com/big-relief-for-students-now-income-certificate-will-be-required-only-once-scholarship-will-be-available-till-completion-of-course/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/higher-edu-dept-to-host-lecture-series-vikasit-bharat-sanvad-from-sept-17-101757963146391.html</t>
+          <t>https://telugu.getlokalapp.com/maharashtra-news/solapur/solapur-city-central/solapur-education-fee-waiver-for-girls-as-per-new-education-policy-15435274</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
+          <t>https://maharashtratimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
+          <t>https://www.mahasamvad.in/page/52/?m=0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
+          <t>https://www.lokmat.com/business/news/gst-rates-cheaper-items-marathi-many-items-will-be-cheaper-from-tomorrow-22-september-see-how-much-gst-will-be-charged-on-which-items-in-your-household-a-a607/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/chandrakant-patil-then-congress-will-leave-the-alliance-minister-chandrakant-patil-predicted/</t>
+          <t>https://www.mahasamvad.in/page/37/?m=0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891</t>
+          <t>https://www.lokmat.com/business/news/gst-reforms-22-sept-horlicks-vicks-zandu-balm-diapers-toothpaste-everything-is-cheaper-hul-emami-p-and-g-giant-companies-have-released-a-new-list-a-a720/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-relief-for-students-now-income-certificate-will-be-required-only-once-scholarship-will-be-available-till-completion-of-course/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://theclearnews.com/gram-gaurav-foundation-to-hold-saksha-lakshmi-awareness-campaign-during-navratri/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-on-22-september-2025-breaking-marathi-batmya-997787.html</t>
+          <t>https://www.msn.com/mr-in/lifestyle/topstories/student-scholarship-%E0%A4%B6-%E0%A4%B7%E0%A5%8D%E0%A4%AF%E0%A4%B5%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%B5%E0%A5%87%E0%A4%B3-%E0%A4%A6-%E0%A4%B2%E0%A5%87%E0%A4%B2-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4-%E0%A4%9A-%E0%A4%A0%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3-%E0%A4%AF%E0%A4%95/ar-AA1MKOjT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-demand-for-subsidy-for-miraj-balgandharva-theatre-ssb-93-5386538/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/business/8th-pay-commission-da-hike-diwali-bonus-central-government-employees-998599.html</t>
+          <t>https://maharashtratimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/business/government-schemes-old-pension-scheme-return-supreme-court-2026-news-in-marathi-995481.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/pune-thieves-broke-lock-of-flat-in-bibwewadi-kondhwa-area-and-stole-valuables-worth-over-rs-5-lakh-pune-print-news-sud-02-5389067/</t>
+          <t>https://www.loksatta.com/maharashtra/satara-electric-vehicles-will-now-run-on-the-kas-plateau-ssb-93-5386502/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-demand-for-subsidy-for-miraj-balgandharva-theatre-ssb-93-5386538/</t>
+          <t>https://www.timesnownews.com/education/maharashtra-to-recruit-5500-assistant-professors-in-senior-colleges-by-march-2026-sarkari-naukri-article-152864646</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
+          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/satara-electric-vehicles-will-now-run-on-the-kas-plateau-ssb-93-5386502/</t>
+          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%A4-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%A8-%E0%A4%B5%E0%A4%A1-%E0%A4%A8%E0%A4%82-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%AF-%E0%A4%AD%E0%A5%82%E0%A4%95%E0%A4%82%E0%A4%AA-%E0%A4%98%E0%A4%A1-%E0%A4%AE-%E0%A4%A1-%E0%A4%82%E0%A4%A8-%E0%A4%B5%E0%A5%87%E0%A4%97/ar-AA1MX7cq</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/5-500-assistant-professors-to-be-recruited-in-maharashtra-by-march-2026-says-minister/ar-AA1N2uUL?ocid=finance-verthp-feeds</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%B8%E0%A4%A6%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%A3-%E0%A4%A4-%E0%A4%B6%E0%A4%B9%E0%A4%B0-%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE/ar-AA1zoITs?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-polls-ex-bjp-leader-harshvardhan-patil-joins-ncp-sp/ar-AA1rOBQP?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.loksatta.com/politics/bjp-mla-randhir-savarkar-akola-nilkanth-cooperative-mill-gets-36-4-crore-grant-from-mahayuti-government-sdp-92-5381028/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A4%9F-%E0%A4%B2-%E0%A4%A7%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%98-%E0%A4%9F%E0%A4%97%E0%A5%87-%E0%A4%85%E0%A4%82%E0%A4%AC%E0%A4%B0-%E0%A4%B7-%E0%A4%98-%E0%A4%9F%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6/ar-AA1CXkyZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://maharashtranews1.com/Graduates--assembly-elections-are-also-being-prepared-by-BJP-and-Shiv-Sena-Thackeray-group-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.bweducation.com/article/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-572650</t>
+          <t>https://www.freepressjournal.in/pune/will-shut-your-business-in-pune-gangster-nilesh-ghaywal-threatens-dharashiv-businessman-over-whatsapp-call-video</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178877/</t>
+          <t>https://www.dainikprabhat.com/dhananjay-munde-on-ajit-pawar/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179132/</t>
+          <t>https://news.careers360.com/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-says-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
+          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/amp/maharashtra/mumbai/bjp-maharashtra-president-chandrakant-patil-on-30-year-old-bjp-shiv-sena-alliance-126264710.html</t>
+          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
@@ -837,110 +837,117 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/autonomy-vital-for-researchers-to-pursue-innovation-says-cm-fadnavis-101757875592362.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/autonomy-vital-for-researchers-to-pursue-innovation-says-cm-fadnavis-101757875592362.html</t>
+          <t>https://mahasamvad.in/178893/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
+          <t>https://www.loksatta.com/pune/women-delaying-motherhood-increases-uterine-cancer-risk-experts-warn-pune-print-news-amy-95-5372589/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
+          <t>https://mondaytomondaynews.com/dharna-protest-in-muktainagar-for-the-demands-of-the-dhangar-community-statewide-protest-if-no-decision-is-taken-within-15-days/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/women-delaying-motherhood-increases-uterine-cancer-risk-experts-warn-pune-print-news-amy-95-5372589/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
+          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-recruit-5500-assistant-professors-for-senior-colleges-by-march-2026-5617</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
+          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/mhalunge-police-arrest-four-for-theft-solve-two-more-robbery-cases/articleshow/124032928.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
+          <t>https://www.dainikprabhat.com/mega-recruitment-of-5500-assistant-professors-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/mhalunge-police-arrest-four-for-theft-solve-two-more-robbery-cases/articleshow/124032928.cms</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/career/education-engineers-day-opinion-learn-these-skills-to-secure-engineering-job-in-10-years-990855.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://education.economictimes.indiatimes.com/news/higher-education/5500-assistant-professors-to-be-recruited-before-march-2026-says-maharashtra-higher-education-minister/124055248</t>
+          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
+        <is>
+          <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>https://annews.co.in/16508/</t>
         </is>

--- a/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A75"/>
+  <dimension ref="A1:A72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,14 +452,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-March-2026-says-minister-Chandrakant-Patil/2934478</t>
+          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil/2934478</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
+          <t>https://www.oneindia.com/india/5500-assistant-professors-recruited-maharashtra-011-7866581.html</t>
         </is>
       </c>
     </row>
@@ -487,133 +487,133 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/education/3635112-maharashtra-to-recruit-5500-assistant-professors-by-march-2026</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-starts-direct-transfer-of-grants-to-over-10-000-public-libraries/2930525</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179154/</t>
+          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
+          <t>https://www.loksatta.com/maharashtra/nanded-chandrakant-patil-book-reading-abhang-library-student-council-activists-meet-ssb-93-5386464/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178560/</t>
+          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477</t>
+          <t>https://mahasamvad.in/178560/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178569/</t>
+          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-nanded-news-education-is-not-our-country-priority-but-two-meals-a-day-is-says-minister-chandrakant-patil-1385473</t>
+          <t>https://mahasamvad.in/178569/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178654/</t>
+          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178557/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-nanded-news-education-is-not-our-country-priority-but-two-meals-a-day-is-says-minister-chandrakant-patil-1385473</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/income-certificate-once-submitted-for-scholarship-is-valid-till-the-end-of-college-relief-for-students-of-higher-and-technical-education-department-maharashtra-news-mhs25091705299</t>
+          <t>https://mahasamvad.in/178557/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-social-fabric-minister-chandrakant-patil-expresses-concern-over-state-s-social-disintegration-citing-caste-issues-and-impact-on-development-1385630</t>
+          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178881/</t>
+          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
+          <t>https://maharashtratimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
+          <t>https://agrowon.esakal.com/agro-special/emphasis-on-pest-and-disease-control-along-with-strict-irrigation-in-banana-orchards-rat16</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://policenama.com/kothrud-missing-link-kothrud-constituency-moving-towards-traffic-congestion-relief-missing-link-work-underway-on-the-initiative-of-chandrakantdada-patil/</t>
+          <t>https://deshonnati.com/nanded-become-an-entrepreneur-who-strengthens-the-backbone-of-society/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
+          <t>https://policenama.com/kothrud-missing-link-kothrud-constituency-moving-towards-traffic-congestion-relief-missing-link-work-underway-on-the-initiative-of-chandrakantdada-patil/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-children-should-eat-nachni-foods-for-good-vitamins-needed-by-the-body-chandrakantdada-patils-advice-to-students/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/chandrakant-patil-criticized-of-rahul-gandhi/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/chandrakant-patil-criticized-of-rahul-gandhi/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
         </is>
       </c>
     </row>
@@ -634,322 +634,301 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
+          <t>https://ebatmidar.com/%E0%A4%85%E0%A4%A4%E0%A4%BF%E0%A4%B5%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%80%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/income-certificate-now-available-only-once-scholarship-will-be-available-till-completion-of-course/117645/</t>
+          <t>https://www.dainikprabhat.com/mega-recruitment-of-5500-assistant-professors-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
+          <t>https://theclearnews.com/gram-gaurav-foundation-to-hold-saksha-lakshmi-awareness-campaign-during-navratri/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-relief-for-students-now-income-certificate-will-be-required-only-once-scholarship-will-be-available-till-completion-of-course/</t>
+          <t>https://mahasamvad.in/178881/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/maharashtra-news/solapur/solapur-city-central/solapur-education-fee-waiver-for-girls-as-per-new-education-policy-15435274</t>
+          <t>https://www.esakal.com/education-jobs/maharashtra-professor-recruitment-2025-6200-teaching-vacancies-eligibility-application-details-mms21</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
+          <t>https://www.mahasamvad.in/page/52/?m=0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/52/?m=0</t>
+          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-on-22-september-2025-breaking-marathi-batmya-997787.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/business/news/gst-rates-cheaper-items-marathi-many-items-will-be-cheaper-from-tomorrow-22-september-see-how-much-gst-will-be-charged-on-which-items-in-your-household-a-a607/</t>
+          <t>https://maharashtratimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/37/?m=0</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/business/news/gst-reforms-22-sept-horlicks-vicks-zandu-balm-diapers-toothpaste-everything-is-cheaper-hul-emami-p-and-g-giant-companies-have-released-a-new-list-a-a720/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
+          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
+          <t>https://maharashtratimes.com/maharashtra/pune-news/union-minister-nitin-gadkari-comments-on-agriculture-and-water-problems-in-maharashtra/articleshow/123889927.cms</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/lifestyle/topstories/student-scholarship-%E0%A4%B6-%E0%A4%B7%E0%A5%8D%E0%A4%AF%E0%A4%B5%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%B5%E0%A5%87%E0%A4%B3-%E0%A4%A6-%E0%A4%B2%E0%A5%87%E0%A4%B2-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4-%E0%A4%9A-%E0%A4%A0%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3-%E0%A4%AF%E0%A4%95/ar-AA1MKOjT</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-demand-for-subsidy-for-miraj-balgandharva-theatre-ssb-93-5386538/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-demand-for-subsidy-for-miraj-balgandharva-theatre-ssb-93-5386538/</t>
+          <t>https://www.loksatta.com/pune/pune-thieves-broke-lock-of-flat-in-bibwewadi-kondhwa-area-and-stole-valuables-worth-over-rs-5-lakh-pune-print-news-sud-02-5389067/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/spontaneous-response-to-cancer-screening-camp.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/satara-electric-vehicles-will-now-run-on-the-kas-plateau-ssb-93-5386502/</t>
+          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/education/maharashtra-to-recruit-5500-assistant-professors-in-senior-colleges-by-march-2026-sarkari-naukri-article-152864646</t>
+          <t>https://maharashtratimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/anti-naxal-public-safety-bill-support-meeting-in-pune-today.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%A4-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%A8-%E0%A4%B5%E0%A4%A1-%E0%A4%A8%E0%A4%82-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%AF-%E0%A4%AD%E0%A5%82%E0%A4%95%E0%A4%82%E0%A4%AA-%E0%A4%98%E0%A4%A1-%E0%A4%AE-%E0%A4%A1-%E0%A4%82%E0%A4%A8-%E0%A4%B5%E0%A5%87%E0%A4%97/ar-AA1MX7cq</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/supreme-court-orders-to-hold-local-body-elections-before-january-31-2026.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%B8%E0%A4%A6%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%A3-%E0%A4%A4-%E0%A4%B6%E0%A4%B9%E0%A4%B0-%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE/ar-AA1zoITs?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.loksatta.com/maharashtra/satara-electric-vehicles-will-now-run-on-the-kas-plateau-ssb-93-5386502/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/bjp-mla-randhir-savarkar-akola-nilkanth-cooperative-mill-gets-36-4-crore-grant-from-mahayuti-government-sdp-92-5381028/</t>
+          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Graduates--assembly-elections-are-also-being-prepared-by-BJP-and-Shiv-Sena-Thackeray-group-</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/will-shut-your-business-in-pune-gangster-nilesh-ghaywal-threatens-dharashiv-businessman-over-whatsapp-call-video</t>
+          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-March-2026-says-minister-Chandrakant-Patil/2934478</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/dhananjay-munde-on-ajit-pawar/</t>
+          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-recruit-5500-assistant-professors-for-senior-colleges-by-march-2026-5617</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-says-minister-chandrakant-patil</t>
+          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
+          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/interpretation-of-the-interim-order-of-the-waqf-amendment-act.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/autonomy-vital-for-researchers-to-pursue-innovation-says-cm-fadnavis-101757875592362.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
+          <t>https://mahasamvad.in/178777/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178893/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/maharashtra-animation-visual-effects-gaming-comics-and-extended-reality-policy-2025-announced-decision-taken-i.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/women-delaying-motherhood-increases-uterine-cancer-risk-experts-warn-pune-print-news-amy-95-5372589/</t>
+          <t>https://www.navarashtra.com/world/nepals-interim-cabinet-to-expand-with-three-new-ministers-today-990664.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://mondaytomondaynews.com/dharna-protest-in-muktainagar-for-the-demands-of-the-dhangar-community-statewide-protest-if-no-decision-is-taken-within-15-days/</t>
+          <t>https://punemirror.com/city/power-play-over-water/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
+          <t>https://www.heraldgoa.in/top-stories/ed-investigates-bhutani-group-over-%E2%82%B93500-crore-real-estate-fraud/13588/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-recruit-5500-assistant-professors-for-senior-colleges-by-march-2026-5617</t>
+          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/mega-recruitment-of-5500-assistant-professors-in-the-state/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/mhalunge-police-arrest-four-for-theft-solve-two-more-robbery-cases/articleshow/124032928.cms</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/mhalunge-police-arrest-four-for-theft-solve-two-more-robbery-cases/articleshow/124032928.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
+          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
           <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>https://annews.co.in/16508/</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A72"/>
+  <dimension ref="A1:A54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,42 +438,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263.html</t>
+          <t>https://www.timesnownews.com/education/5500-assistant-professors-to-be-recruited-in-maharashtra-before-march-2026-chandrakant-patil-article-152869876</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/education/5500-assistant-professors-to-be-recruited-in-maharashtra-before-march-2026-chandrakant-patil-article-152869876</t>
+          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil/2934478</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.oneindia.com/india/5500-assistant-professors-recruited-maharashtra-011-7866581.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/no-repeated-paperwork-for-professional-course-scholarships-minister-101758221398673.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/no-repeated-paperwork-for-professional-course-scholarships-minister-101758221398673.html</t>
+          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/en/education-news/maharashtra-announces-massive-recruitment-5500-assistant-professor-2900-non-teaching-posts-19963995</t>
+          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-recruit-5500-assistant-professors-for-senior-colleges-by-march-2026-5617</t>
         </is>
       </c>
     </row>
@@ -487,448 +487,322 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-starts-direct-transfer-of-grants-to-over-10-000-public-libraries/2930525</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-to-recruit-5500-assistant-professors-by-march-2026/ar-AA1MZ5pj</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
+          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/nanded-chandrakant-patil-book-reading-abhang-library-student-council-activists-meet-ssb-93-5386464/</t>
+          <t>https://www.etvbharat.com/mr/!state/income-certificate-once-submitted-for-scholarship-is-valid-till-the-end-of-college-relief-for-students-of-higher-and-technical-education-department-maharashtra-news-mhs25091705299</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379</t>
+          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178560/</t>
+          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
+          <t>https://maharashtratimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178569/</t>
+          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477</t>
+          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-nanded-news-education-is-not-our-country-priority-but-two-meals-a-day-is-says-minister-chandrakant-patil-1385473</t>
+          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178557/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
+          <t>https://policenama.com/kothrud-missing-link-kothrud-constituency-moving-towards-traffic-congestion-relief-missing-link-work-underway-on-the-initiative-of-chandrakantdada-patil/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
+          <t>https://www.dainikprabhat.com/mega-recruitment-of-5500-assistant-professors-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
+          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/emphasis-on-pest-and-disease-control-along-with-strict-irrigation-in-banana-orchards-rat16</t>
+          <t>https://theclearnews.com/gram-gaurav-foundation-to-hold-saksha-lakshmi-awareness-campaign-during-navratri/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/nanded-become-an-entrepreneur-who-strengthens-the-backbone-of-society/</t>
+          <t>https://lokmat.news18.com/videos/video/nagpur-news-is-it-right-to-check-religion-by-showing-adhar-card-what-do-the-youth-think-listen-n18v-1075647.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://policenama.com/kothrud-missing-link-kothrud-constituency-moving-towards-traffic-congestion-relief-missing-link-work-underway-on-the-initiative-of-chandrakantdada-patil/</t>
+          <t>https://maharashtratimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/chandrakant-patil-criticized-of-rahul-gandhi/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891</t>
+          <t>https://maharashtratimes.com/maharashtra/pune-news/union-minister-nitin-gadkari-comments-on-agriculture-and-water-problems-in-maharashtra/articleshow/123889927.cms</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
+          <t>https://marathi.abplive.com/news/politics/dhananjay-munde-demand-to-sunil-tatkare-for-some-work-ncp-ajit-pawar-maharashtra-politics-marathi-news-1385972</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://ebatmidar.com/%E0%A4%85%E0%A4%A4%E0%A4%BF%E0%A4%B5%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%80%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF/</t>
+          <t>https://www.timesnownews.com/education/maharashtra-to-recruit-5500-assistant-professors-in-senior-colleges-by-march-2026-sarkari-naukri-article-152864646</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/mega-recruitment-of-5500-assistant-professors-in-the-state/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://theclearnews.com/gram-gaurav-foundation-to-hold-saksha-lakshmi-awareness-campaign-during-navratri/</t>
+          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178881/</t>
+          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/education-jobs/maharashtra-professor-recruitment-2025-6200-teaching-vacancies-eligibility-application-details-mms21</t>
+          <t>https://www.msn.com/en-in/news/India/5-500-assistant-professors-to-be-recruited-in-maharashtra-by-march-2026-says-minister/ar-AA1N2uUL?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/52/?m=0</t>
+          <t>https://www.bweducation.com/article/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-572650</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-on-22-september-2025-breaking-marathi-batmya-997787.html</t>
+          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
+          <t>https://news.careers360.com/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-says-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
+          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
+          <t>https://ndtv.in/maharashtra-news/chandrakant-patil-statement-education-vs-food-priority-9314731</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
+          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/pune-news/union-minister-nitin-gadkari-comments-on-agriculture-and-water-problems-in-maharashtra/articleshow/123889927.cms</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-demand-for-subsidy-for-miraj-balgandharva-theatre-ssb-93-5386538/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/interpretation-of-the-interim-order-of-the-waqf-amendment-act.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/pune-thieves-broke-lock-of-flat-in-bibwewadi-kondhwa-area-and-stole-valuables-worth-over-rs-5-lakh-pune-print-news-sud-02-5389067/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/spontaneous-response-to-cancer-screening-camp.html</t>
+          <t>https://punemirror.com/city/power-play-over-water/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
+          <t>https://www.heraldgoa.in/top-stories/ed-investigates-bhutani-group-over-%E2%82%B93500-crore-real-estate-fraud/13588/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
+          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/anti-naxal-public-safety-bill-support-meeting-in-pune-today.html</t>
+          <t>https://agrowon.esakal.com/agro-special/gadkari-water-conservation-key-to-abundant-irrigation-and-farmer-as-energy-contributor-mj18</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/supreme-court-orders-to-hold-local-body-elections-before-january-31-2026.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/satara-electric-vehicles-will-now-run-on-the-kas-plateau-ssb-93-5386502/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/mhalunge-police-arrest-four-for-theft-solve-two-more-robbery-cases/articleshow/124032928.cms</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-March-2026-says-minister-Chandrakant-Patil/2934478</t>
+          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-recruit-5500-assistant-professors-for-senior-colleges-by-march-2026-5617</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/interpretation-of-the-interim-order-of-the-waqf-amendment-act.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178777/</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/maharashtra-animation-visual-effects-gaming-comics-and-extended-reality-policy-2025-announced-decision-taken-i.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>https://www.navarashtra.com/world/nepals-interim-cabinet-to-expand-with-three-new-ministers-today-990664.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>https://punemirror.com/city/power-play-over-water/</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>https://www.heraldgoa.in/top-stories/ed-investigates-bhutani-group-over-%E2%82%B93500-crore-real-estate-fraud/13588/</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/mhalunge-police-arrest-four-for-theft-solve-two-more-robbery-cases/articleshow/124032928.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses</t>
+          <t>https://www.dainikprabhat.com/santosh-yadav-gets-krantijyoti-savitribai-phule-state-teacher-award/</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links_Chandrakant Patil_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/no-repeated-paperwork-for-professional-course-scholarships-minister-101758221398673.html</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/no-repeated-paperwork-for-professional-course-scholarships-minister-101758221398673.html</t>
+          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263.html</t>
         </is>
       </c>
     </row>
@@ -487,63 +487,63 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-to-recruit-5500-assistant-professors-by-march-2026/ar-AA1MZ5pj</t>
+          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379</t>
+          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/income-certificate-once-submitted-for-scholarship-is-valid-till-the-end-of-college-relief-for-students-of-higher-and-technical-education-department-maharashtra-news-mhs25091705299</t>
+          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
+          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
+          <t>https://www.nagpurtoday.in/devendra-fadnavis-has-qualities-of-prime-minister-says-chandrakant-patil/09221309</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
+          <t>https://policenama.com/kothrud-missing-link-kothrud-constituency-moving-towards-traffic-congestion-relief-missing-link-work-underway-on-the-initiative-of-chandrakantdada-patil/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
+          <t>https://www.dainikprabhat.com/mega-recruitment-of-5500-assistant-professors-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
+          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
         </is>
       </c>
     </row>
@@ -557,252 +557,203 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
+          <t>https://maharashtratimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://policenama.com/kothrud-missing-link-kothrud-constituency-moving-towards-traffic-congestion-relief-missing-link-work-underway-on-the-initiative-of-chandrakantdada-patil/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/mega-recruitment-of-5500-assistant-professors-in-the-state/</t>
+          <t>https://maharashtratimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://theclearnews.com/gram-gaurav-foundation-to-hold-saksha-lakshmi-awareness-campaign-during-navratri/</t>
+          <t>https://maharashtratimes.com/maharashtra/pune-news/union-minister-nitin-gadkari-comments-on-agriculture-and-water-problems-in-maharashtra/articleshow/123889927.cms</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/nagpur-news-is-it-right-to-check-religion-by-showing-adhar-card-what-do-the-youth-think-listen-n18v-1075647.html</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
+          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/pune-news/union-minister-nitin-gadkari-comments-on-agriculture-and-water-problems-in-maharashtra/articleshow/123889927.cms</t>
+          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/dhananjay-munde-demand-to-sunil-tatkare-for-some-work-ncp-ajit-pawar-maharashtra-politics-marathi-news-1385972</t>
+          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/education/maharashtra-to-recruit-5500-assistant-professors-in-senior-colleges-by-march-2026-sarkari-naukri-article-152864646</t>
+          <t>https://www.loksatta.com/pune/pune-thieves-broke-lock-of-flat-in-bibwewadi-kondhwa-area-and-stole-valuables-worth-over-rs-5-lakh-pune-print-news-sud-02-5389067/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
+          <t>https://www.bweducation.com/article/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-572650</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077</t>
+          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
+          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/5-500-assistant-professors-to-be-recruited-in-maharashtra-by-march-2026-says-minister/ar-AA1N2uUL?ocid=finance-verthp-feeds</t>
+          <t>https://news.careers360.com/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-says-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.bweducation.com/article/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-572650</t>
+          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
+          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-says-minister-chandrakant-patil</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/anti-naxal-public-safety-bill-support-meeting-in-pune-today.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/chandrakant-patil-statement-education-vs-food-priority-9314731</t>
+          <t>https://www.freepressjournal.in/pune/pune-rotten-foodgrain-supplied-to-citizens-for-contractors-benefit-claim-activists</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/interpretation-of-the-interim-order-of-the-waqf-amendment-act.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/interpretation-of-the-interim-order-of-the-waqf-amendment-act.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
+          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/power-play-over-water/</t>
+          <t>https://agrowon.esakal.com/agro-special/gadkari-water-conservation-key-to-abundant-irrigation-and-farmer-as-energy-contributor-mj18</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.heraldgoa.in/top-stories/ed-investigates-bhutani-group-over-%E2%82%B93500-crore-real-estate-fraud/13588/</t>
+          <t>https://education.economictimes.indiatimes.com/news/higher-education/5500-assistant-professors-to-be-recruited-before-march-2026-says-maharashtra-higher-education-minister/124055248</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>https://agrowon.esakal.com/agro-special/gadkari-water-conservation-key-to-abundant-irrigation-and-farmer-as-energy-contributor-mj18</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/mhalunge-police-arrest-four-for-theft-solve-two-more-robbery-cases/articleshow/124032928.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>https://www.dainikprabhat.com/santosh-yadav-gets-krantijyoti-savitribai-phule-state-teacher-award/</t>
+          <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses</t>
         </is>
       </c>
     </row>
